--- a/templates/forms/LTC_Certification_Change_R8.4-.xlsx
+++ b/templates/forms/LTC_Certification_Change_R8.4-.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CareManagementTool\templates\forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7A3D33-7FAA-432C-8531-A5F90DA5F1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB2FE2E-FD93-4500-8B44-B16558DF33F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="介護保険 要介護・要支援 （認定区分変更） 申請書 " sheetId="2" r:id="rId1"/>
@@ -18,12 +18,12 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'介護保険 要介護・要支援 （認定区分変更） 申請書 '!$A$1:$AF$57</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="73">
   <si>
     <t>第29条･第30条･第33条の2･第33条の3関係</t>
     <rPh sb="0" eb="1">
@@ -202,48 +202,12 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>男　・　女</t>
-    <rPh sb="0" eb="1">
-      <t>オトコ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>オンナ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>生年月日</t>
     <rPh sb="0" eb="2">
       <t>セイネン</t>
     </rPh>
     <rPh sb="2" eb="4">
       <t>ガッピ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>明・大・昭　</t>
-    <rPh sb="0" eb="1">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>オオ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>アキラ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>年　　　　月　　　　日</t>
-    <rPh sb="0" eb="1">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ガツ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ニチ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2194,7 +2158,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="326">
+  <cellXfs count="319">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2399,6 +2363,581 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -2504,623 +3043,27 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - アクセント 1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -3576,9 +3519,9 @@
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
-      <c r="AD1" s="174"/>
-      <c r="AE1" s="174"/>
-      <c r="AF1" s="174"/>
+      <c r="AD1" s="213"/>
+      <c r="AE1" s="213"/>
+      <c r="AF1" s="213"/>
     </row>
     <row r="2" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
@@ -3605,62 +3548,62 @@
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
-      <c r="AD2" s="174"/>
-      <c r="AE2" s="174"/>
-      <c r="AF2" s="174"/>
+      <c r="AD2" s="213"/>
+      <c r="AE2" s="213"/>
+      <c r="AF2" s="213"/>
     </row>
     <row r="3" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C3" s="178" t="s">
+      <c r="C3" s="214" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="178"/>
-      <c r="I3" s="178"/>
-      <c r="J3" s="178"/>
-      <c r="K3" s="178"/>
-      <c r="L3" s="178"/>
-      <c r="M3" s="178"/>
-      <c r="N3" s="178"/>
-      <c r="O3" s="178"/>
-      <c r="P3" s="178"/>
-      <c r="Q3" s="178"/>
-      <c r="R3" s="178"/>
-      <c r="S3" s="178"/>
-      <c r="T3" s="178"/>
-      <c r="U3" s="178"/>
-      <c r="V3" s="178"/>
-      <c r="W3" s="178"/>
-      <c r="X3" s="178"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+      <c r="L3" s="214"/>
+      <c r="M3" s="214"/>
+      <c r="N3" s="214"/>
+      <c r="O3" s="214"/>
+      <c r="P3" s="214"/>
+      <c r="Q3" s="214"/>
+      <c r="R3" s="214"/>
+      <c r="S3" s="214"/>
+      <c r="T3" s="214"/>
+      <c r="U3" s="214"/>
+      <c r="V3" s="214"/>
+      <c r="W3" s="214"/>
+      <c r="X3" s="214"/>
       <c r="AD3" s="5"/>
       <c r="AE3" s="5"/>
       <c r="AF3" s="5"/>
     </row>
     <row r="4" spans="1:37" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C4" s="178"/>
-      <c r="D4" s="178"/>
-      <c r="E4" s="178"/>
-      <c r="F4" s="178"/>
-      <c r="G4" s="178"/>
-      <c r="H4" s="178"/>
-      <c r="I4" s="178"/>
-      <c r="J4" s="178"/>
-      <c r="K4" s="178"/>
-      <c r="L4" s="178"/>
-      <c r="M4" s="178"/>
-      <c r="N4" s="178"/>
-      <c r="O4" s="178"/>
-      <c r="P4" s="178"/>
-      <c r="Q4" s="178"/>
-      <c r="R4" s="178"/>
-      <c r="S4" s="178"/>
-      <c r="T4" s="178"/>
-      <c r="U4" s="178"/>
-      <c r="V4" s="178"/>
-      <c r="W4" s="178"/>
-      <c r="X4" s="178"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="214"/>
+      <c r="E4" s="214"/>
+      <c r="F4" s="214"/>
+      <c r="G4" s="214"/>
+      <c r="H4" s="214"/>
+      <c r="I4" s="214"/>
+      <c r="J4" s="214"/>
+      <c r="K4" s="214"/>
+      <c r="L4" s="214"/>
+      <c r="M4" s="214"/>
+      <c r="N4" s="214"/>
+      <c r="O4" s="214"/>
+      <c r="P4" s="214"/>
+      <c r="Q4" s="214"/>
+      <c r="R4" s="214"/>
+      <c r="S4" s="214"/>
+      <c r="T4" s="214"/>
+      <c r="U4" s="214"/>
+      <c r="V4" s="214"/>
+      <c r="W4" s="214"/>
+      <c r="X4" s="214"/>
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
       <c r="AC4" s="7"/>
@@ -3761,208 +3704,208 @@
       <c r="Q7" s="20"/>
       <c r="R7" s="20"/>
       <c r="S7" s="21"/>
-      <c r="T7" s="179" t="s">
+      <c r="T7" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="U7" s="179"/>
-      <c r="V7" s="179"/>
-      <c r="W7" s="180"/>
-      <c r="X7" s="187"/>
-      <c r="Y7" s="188"/>
-      <c r="Z7" s="188"/>
-      <c r="AA7" s="188"/>
-      <c r="AB7" s="188"/>
-      <c r="AC7" s="188"/>
-      <c r="AD7" s="188"/>
-      <c r="AE7" s="188"/>
-      <c r="AF7" s="189"/>
+      <c r="U7" s="124"/>
+      <c r="V7" s="124"/>
+      <c r="W7" s="125"/>
+      <c r="X7" s="191"/>
+      <c r="Y7" s="192"/>
+      <c r="Z7" s="192"/>
+      <c r="AA7" s="192"/>
+      <c r="AB7" s="192"/>
+      <c r="AC7" s="192"/>
+      <c r="AD7" s="192"/>
+      <c r="AE7" s="192"/>
+      <c r="AF7" s="193"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="83"/>
     </row>
     <row r="8" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="175" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="123"/>
-      <c r="C8" s="129"/>
-      <c r="D8" s="185" t="s">
+      <c r="A8" s="184" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="185"/>
+      <c r="C8" s="186"/>
+      <c r="D8" s="182" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="186"/>
-      <c r="F8" s="186"/>
-      <c r="G8" s="190"/>
-      <c r="H8" s="191"/>
-      <c r="I8" s="191"/>
-      <c r="J8" s="191"/>
-      <c r="K8" s="191"/>
-      <c r="L8" s="191"/>
-      <c r="M8" s="191"/>
-      <c r="N8" s="191"/>
-      <c r="O8" s="191"/>
-      <c r="P8" s="191"/>
-      <c r="Q8" s="191"/>
-      <c r="R8" s="191"/>
-      <c r="S8" s="192"/>
-      <c r="T8" s="124"/>
-      <c r="U8" s="124"/>
-      <c r="V8" s="124"/>
-      <c r="W8" s="181"/>
-      <c r="X8" s="193"/>
-      <c r="Y8" s="194"/>
-      <c r="Z8" s="194"/>
-      <c r="AA8" s="194"/>
-      <c r="AB8" s="194"/>
-      <c r="AC8" s="194"/>
-      <c r="AD8" s="194"/>
-      <c r="AE8" s="194"/>
-      <c r="AF8" s="195"/>
+      <c r="E8" s="183"/>
+      <c r="F8" s="183"/>
+      <c r="G8" s="175"/>
+      <c r="H8" s="176"/>
+      <c r="I8" s="176"/>
+      <c r="J8" s="176"/>
+      <c r="K8" s="176"/>
+      <c r="L8" s="176"/>
+      <c r="M8" s="176"/>
+      <c r="N8" s="176"/>
+      <c r="O8" s="176"/>
+      <c r="P8" s="176"/>
+      <c r="Q8" s="176"/>
+      <c r="R8" s="176"/>
+      <c r="S8" s="177"/>
+      <c r="T8" s="101"/>
+      <c r="U8" s="101"/>
+      <c r="V8" s="101"/>
+      <c r="W8" s="102"/>
+      <c r="X8" s="194"/>
+      <c r="Y8" s="195"/>
+      <c r="Z8" s="195"/>
+      <c r="AA8" s="195"/>
+      <c r="AB8" s="195"/>
+      <c r="AC8" s="195"/>
+      <c r="AD8" s="195"/>
+      <c r="AE8" s="195"/>
+      <c r="AF8" s="196"/>
       <c r="AI8" s="3"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="83"/>
     </row>
     <row r="9" spans="1:37" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="176"/>
-      <c r="B9" s="130"/>
-      <c r="C9" s="131"/>
-      <c r="D9" s="196" t="s">
+      <c r="A9" s="187"/>
+      <c r="B9" s="188"/>
+      <c r="C9" s="189"/>
+      <c r="D9" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="197"/>
-      <c r="F9" s="197"/>
-      <c r="G9" s="198"/>
-      <c r="H9" s="198"/>
-      <c r="I9" s="198"/>
-      <c r="J9" s="198"/>
-      <c r="K9" s="198"/>
-      <c r="L9" s="198"/>
-      <c r="M9" s="198"/>
-      <c r="N9" s="198"/>
-      <c r="O9" s="198"/>
-      <c r="P9" s="198"/>
-      <c r="Q9" s="198"/>
-      <c r="R9" s="198"/>
-      <c r="S9" s="198"/>
-      <c r="T9" s="199" t="s">
+      <c r="E9" s="205"/>
+      <c r="F9" s="205"/>
+      <c r="G9" s="178"/>
+      <c r="H9" s="178"/>
+      <c r="I9" s="178"/>
+      <c r="J9" s="178"/>
+      <c r="K9" s="178"/>
+      <c r="L9" s="178"/>
+      <c r="M9" s="178"/>
+      <c r="N9" s="178"/>
+      <c r="O9" s="178"/>
+      <c r="P9" s="178"/>
+      <c r="Q9" s="178"/>
+      <c r="R9" s="178"/>
+      <c r="S9" s="178"/>
+      <c r="T9" s="173" t="s">
         <v>8</v>
       </c>
-      <c r="U9" s="199"/>
-      <c r="V9" s="199"/>
-      <c r="W9" s="199"/>
-      <c r="X9" s="200"/>
-      <c r="Y9" s="200"/>
-      <c r="Z9" s="200"/>
-      <c r="AA9" s="200"/>
-      <c r="AB9" s="200"/>
-      <c r="AC9" s="200"/>
-      <c r="AD9" s="200"/>
-      <c r="AE9" s="200"/>
-      <c r="AF9" s="200"/>
+      <c r="U9" s="173"/>
+      <c r="V9" s="173"/>
+      <c r="W9" s="173"/>
+      <c r="X9" s="174"/>
+      <c r="Y9" s="174"/>
+      <c r="Z9" s="174"/>
+      <c r="AA9" s="174"/>
+      <c r="AB9" s="174"/>
+      <c r="AC9" s="174"/>
+      <c r="AD9" s="174"/>
+      <c r="AE9" s="174"/>
+      <c r="AF9" s="174"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="22"/>
       <c r="AK9" s="22"/>
     </row>
     <row r="10" spans="1:37" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="176"/>
-      <c r="B10" s="130"/>
-      <c r="C10" s="131"/>
-      <c r="D10" s="201" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="202"/>
-      <c r="F10" s="203"/>
-      <c r="G10" s="198"/>
-      <c r="H10" s="198"/>
-      <c r="I10" s="198"/>
-      <c r="J10" s="198"/>
-      <c r="K10" s="198"/>
-      <c r="L10" s="198"/>
-      <c r="M10" s="198"/>
-      <c r="N10" s="198"/>
-      <c r="O10" s="198"/>
-      <c r="P10" s="198"/>
-      <c r="Q10" s="198"/>
-      <c r="R10" s="198"/>
-      <c r="S10" s="198"/>
-      <c r="T10" s="199"/>
-      <c r="U10" s="199"/>
-      <c r="V10" s="199"/>
-      <c r="W10" s="199"/>
-      <c r="X10" s="200"/>
-      <c r="Y10" s="200"/>
-      <c r="Z10" s="200"/>
-      <c r="AA10" s="200"/>
-      <c r="AB10" s="200"/>
-      <c r="AC10" s="200"/>
-      <c r="AD10" s="200"/>
-      <c r="AE10" s="200"/>
-      <c r="AF10" s="200"/>
+      <c r="A10" s="187"/>
+      <c r="B10" s="188"/>
+      <c r="C10" s="189"/>
+      <c r="D10" s="179" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="180"/>
+      <c r="F10" s="181"/>
+      <c r="G10" s="178"/>
+      <c r="H10" s="178"/>
+      <c r="I10" s="178"/>
+      <c r="J10" s="178"/>
+      <c r="K10" s="178"/>
+      <c r="L10" s="178"/>
+      <c r="M10" s="178"/>
+      <c r="N10" s="178"/>
+      <c r="O10" s="178"/>
+      <c r="P10" s="178"/>
+      <c r="Q10" s="178"/>
+      <c r="R10" s="178"/>
+      <c r="S10" s="178"/>
+      <c r="T10" s="173"/>
+      <c r="U10" s="173"/>
+      <c r="V10" s="173"/>
+      <c r="W10" s="173"/>
+      <c r="X10" s="174"/>
+      <c r="Y10" s="174"/>
+      <c r="Z10" s="174"/>
+      <c r="AA10" s="174"/>
+      <c r="AB10" s="174"/>
+      <c r="AC10" s="174"/>
+      <c r="AD10" s="174"/>
+      <c r="AE10" s="174"/>
+      <c r="AF10" s="174"/>
       <c r="AI10" s="3"/>
       <c r="AJ10" s="22"/>
       <c r="AK10" s="22"/>
     </row>
     <row r="11" spans="1:37" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="176"/>
-      <c r="B11" s="130"/>
-      <c r="C11" s="131"/>
-      <c r="D11" s="196" t="s">
+      <c r="A11" s="187"/>
+      <c r="B11" s="188"/>
+      <c r="C11" s="189"/>
+      <c r="D11" s="204" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="204"/>
-      <c r="F11" s="205"/>
-      <c r="G11" s="206" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="207"/>
-      <c r="I11" s="207"/>
-      <c r="J11" s="207"/>
-      <c r="K11" s="207"/>
-      <c r="L11" s="207"/>
-      <c r="M11" s="207"/>
+      <c r="E11" s="209"/>
+      <c r="F11" s="210"/>
+      <c r="G11" s="97" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="98"/>
+      <c r="I11" s="98"/>
+      <c r="J11" s="98"/>
+      <c r="K11" s="98"/>
+      <c r="L11" s="98"/>
+      <c r="M11" s="98"/>
       <c r="N11" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="O11" s="208"/>
-      <c r="P11" s="208"/>
-      <c r="Q11" s="209"/>
-      <c r="R11" s="209"/>
-      <c r="S11" s="209"/>
-      <c r="T11" s="209"/>
-      <c r="U11" s="209"/>
-      <c r="V11" s="209"/>
-      <c r="W11" s="209"/>
-      <c r="X11" s="209"/>
-      <c r="Y11" s="209"/>
-      <c r="Z11" s="209"/>
-      <c r="AA11" s="209"/>
-      <c r="AB11" s="209"/>
-      <c r="AC11" s="209"/>
-      <c r="AD11" s="209"/>
-      <c r="AE11" s="209"/>
-      <c r="AF11" s="210"/>
+        <v>62</v>
+      </c>
+      <c r="O11" s="85"/>
+      <c r="P11" s="85"/>
+      <c r="Q11" s="84"/>
+      <c r="R11" s="84"/>
+      <c r="S11" s="84"/>
+      <c r="T11" s="84"/>
+      <c r="U11" s="84"/>
+      <c r="V11" s="84"/>
+      <c r="W11" s="84"/>
+      <c r="X11" s="84"/>
+      <c r="Y11" s="84"/>
+      <c r="Z11" s="84"/>
+      <c r="AA11" s="84"/>
+      <c r="AB11" s="84"/>
+      <c r="AC11" s="84"/>
+      <c r="AD11" s="84"/>
+      <c r="AE11" s="84"/>
+      <c r="AF11" s="86"/>
       <c r="AK11" s="22"/>
     </row>
     <row r="12" spans="1:37" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="177"/>
-      <c r="B12" s="132"/>
-      <c r="C12" s="133"/>
-      <c r="D12" s="201" t="s">
-        <v>66</v>
+      <c r="A12" s="190"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="179" t="s">
+        <v>63</v>
       </c>
       <c r="E12" s="211"/>
       <c r="F12" s="212"/>
-      <c r="G12" s="183"/>
-      <c r="H12" s="124"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="124"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="124"/>
-      <c r="M12" s="124"/>
-      <c r="N12" s="124"/>
-      <c r="O12" s="124"/>
-      <c r="P12" s="124"/>
-      <c r="Q12" s="124"/>
-      <c r="R12" s="124"/>
+      <c r="G12" s="100"/>
+      <c r="H12" s="101"/>
+      <c r="I12" s="101"/>
+      <c r="J12" s="101"/>
+      <c r="K12" s="101"/>
+      <c r="L12" s="101"/>
+      <c r="M12" s="101"/>
+      <c r="N12" s="101"/>
+      <c r="O12" s="101"/>
+      <c r="P12" s="101"/>
+      <c r="Q12" s="101"/>
+      <c r="R12" s="101"/>
       <c r="S12" s="74"/>
       <c r="T12" s="74"/>
       <c r="U12" s="74" t="s">
@@ -3970,92 +3913,92 @@
       </c>
       <c r="V12" s="74"/>
       <c r="W12" s="74"/>
-      <c r="X12" s="124"/>
-      <c r="Y12" s="124"/>
-      <c r="Z12" s="124"/>
-      <c r="AA12" s="124"/>
-      <c r="AB12" s="124"/>
-      <c r="AC12" s="124"/>
-      <c r="AD12" s="124"/>
-      <c r="AE12" s="124"/>
-      <c r="AF12" s="184"/>
+      <c r="X12" s="101"/>
+      <c r="Y12" s="101"/>
+      <c r="Z12" s="101"/>
+      <c r="AA12" s="101"/>
+      <c r="AB12" s="101"/>
+      <c r="AC12" s="101"/>
+      <c r="AD12" s="101"/>
+      <c r="AE12" s="101"/>
+      <c r="AF12" s="169"/>
       <c r="AK12" s="22"/>
     </row>
     <row r="13" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="213" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="214"/>
-      <c r="C13" s="214"/>
-      <c r="D13" s="214"/>
-      <c r="E13" s="214"/>
-      <c r="F13" s="215"/>
-      <c r="G13" s="168" t="s">
-        <v>52</v>
-      </c>
-      <c r="H13" s="169"/>
-      <c r="I13" s="169"/>
-      <c r="J13" s="169"/>
-      <c r="K13" s="169"/>
-      <c r="L13" s="169"/>
-      <c r="M13" s="169"/>
-      <c r="N13" s="169"/>
-      <c r="O13" s="169"/>
-      <c r="P13" s="169"/>
-      <c r="Q13" s="169"/>
-      <c r="R13" s="169"/>
-      <c r="S13" s="169"/>
-      <c r="T13" s="169"/>
-      <c r="U13" s="169"/>
-      <c r="V13" s="169"/>
-      <c r="W13" s="169"/>
-      <c r="X13" s="169"/>
-      <c r="Y13" s="169"/>
-      <c r="Z13" s="169"/>
-      <c r="AA13" s="169"/>
-      <c r="AB13" s="169"/>
-      <c r="AC13" s="169"/>
-      <c r="AD13" s="169"/>
-      <c r="AE13" s="169"/>
-      <c r="AF13" s="170"/>
+      <c r="A13" s="215" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="216"/>
+      <c r="C13" s="216"/>
+      <c r="D13" s="216"/>
+      <c r="E13" s="216"/>
+      <c r="F13" s="217"/>
+      <c r="G13" s="206" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="207"/>
+      <c r="I13" s="207"/>
+      <c r="J13" s="207"/>
+      <c r="K13" s="207"/>
+      <c r="L13" s="207"/>
+      <c r="M13" s="207"/>
+      <c r="N13" s="207"/>
+      <c r="O13" s="207"/>
+      <c r="P13" s="207"/>
+      <c r="Q13" s="207"/>
+      <c r="R13" s="207"/>
+      <c r="S13" s="207"/>
+      <c r="T13" s="207"/>
+      <c r="U13" s="207"/>
+      <c r="V13" s="207"/>
+      <c r="W13" s="207"/>
+      <c r="X13" s="207"/>
+      <c r="Y13" s="207"/>
+      <c r="Z13" s="207"/>
+      <c r="AA13" s="207"/>
+      <c r="AB13" s="207"/>
+      <c r="AC13" s="207"/>
+      <c r="AD13" s="207"/>
+      <c r="AE13" s="207"/>
+      <c r="AF13" s="208"/>
     </row>
     <row r="14" spans="1:37" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="216" t="s">
+      <c r="A14" s="197" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="172"/>
-      <c r="C14" s="172"/>
-      <c r="D14" s="172"/>
-      <c r="E14" s="172"/>
-      <c r="F14" s="173"/>
-      <c r="G14" s="171"/>
-      <c r="H14" s="172"/>
-      <c r="I14" s="172"/>
-      <c r="J14" s="172"/>
-      <c r="K14" s="172"/>
-      <c r="L14" s="172"/>
-      <c r="M14" s="172"/>
-      <c r="N14" s="172"/>
-      <c r="O14" s="172"/>
-      <c r="P14" s="173"/>
-      <c r="Q14" s="171" t="s">
+      <c r="B14" s="198"/>
+      <c r="C14" s="198"/>
+      <c r="D14" s="198"/>
+      <c r="E14" s="198"/>
+      <c r="F14" s="199"/>
+      <c r="G14" s="200"/>
+      <c r="H14" s="198"/>
+      <c r="I14" s="198"/>
+      <c r="J14" s="198"/>
+      <c r="K14" s="198"/>
+      <c r="L14" s="198"/>
+      <c r="M14" s="198"/>
+      <c r="N14" s="198"/>
+      <c r="O14" s="198"/>
+      <c r="P14" s="199"/>
+      <c r="Q14" s="200" t="s">
         <v>12</v>
       </c>
-      <c r="R14" s="172"/>
-      <c r="S14" s="172"/>
-      <c r="T14" s="172"/>
-      <c r="U14" s="172"/>
-      <c r="V14" s="173"/>
-      <c r="W14" s="217"/>
-      <c r="X14" s="218"/>
-      <c r="Y14" s="218"/>
-      <c r="Z14" s="218"/>
-      <c r="AA14" s="218"/>
-      <c r="AB14" s="218"/>
-      <c r="AC14" s="218"/>
-      <c r="AD14" s="218"/>
-      <c r="AE14" s="218"/>
-      <c r="AF14" s="219"/>
+      <c r="R14" s="198"/>
+      <c r="S14" s="198"/>
+      <c r="T14" s="198"/>
+      <c r="U14" s="198"/>
+      <c r="V14" s="199"/>
+      <c r="W14" s="201"/>
+      <c r="X14" s="202"/>
+      <c r="Y14" s="202"/>
+      <c r="Z14" s="202"/>
+      <c r="AA14" s="202"/>
+      <c r="AB14" s="202"/>
+      <c r="AC14" s="202"/>
+      <c r="AD14" s="202"/>
+      <c r="AE14" s="202"/>
+      <c r="AF14" s="203"/>
     </row>
     <row r="15" spans="1:37" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="19"/>
@@ -4094,192 +4037,186 @@
       <c r="AK15" s="26"/>
     </row>
     <row r="16" spans="1:37" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="154" t="s">
+      <c r="A16" s="221" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="223" t="s">
+      <c r="B16" s="224" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="156"/>
-      <c r="D16" s="156"/>
-      <c r="E16" s="156"/>
-      <c r="F16" s="224"/>
-      <c r="G16" s="259"/>
-      <c r="H16" s="260"/>
-      <c r="I16" s="260"/>
-      <c r="J16" s="260"/>
-      <c r="K16" s="260"/>
-      <c r="L16" s="260"/>
-      <c r="M16" s="260"/>
-      <c r="N16" s="260"/>
-      <c r="O16" s="260"/>
-      <c r="P16" s="261"/>
-      <c r="Q16" s="321" t="s">
+      <c r="C16" s="225"/>
+      <c r="D16" s="225"/>
+      <c r="E16" s="225"/>
+      <c r="F16" s="226"/>
+      <c r="G16" s="170"/>
+      <c r="H16" s="171"/>
+      <c r="I16" s="171"/>
+      <c r="J16" s="171"/>
+      <c r="K16" s="171"/>
+      <c r="L16" s="171"/>
+      <c r="M16" s="171"/>
+      <c r="N16" s="171"/>
+      <c r="O16" s="171"/>
+      <c r="P16" s="172"/>
+      <c r="Q16" s="227" t="s">
         <v>15</v>
       </c>
-      <c r="R16" s="322"/>
-      <c r="S16" s="322"/>
-      <c r="T16" s="323"/>
-      <c r="U16" s="324"/>
-      <c r="V16" s="324"/>
-      <c r="W16" s="324"/>
-      <c r="X16" s="324"/>
-      <c r="Y16" s="324"/>
-      <c r="Z16" s="324"/>
-      <c r="AA16" s="324"/>
-      <c r="AB16" s="324"/>
-      <c r="AC16" s="324"/>
-      <c r="AD16" s="324"/>
-      <c r="AE16" s="324"/>
-      <c r="AF16" s="325"/>
+      <c r="R16" s="228"/>
+      <c r="S16" s="228"/>
+      <c r="T16" s="229"/>
+      <c r="U16" s="89"/>
+      <c r="V16" s="89"/>
+      <c r="W16" s="89"/>
+      <c r="X16" s="89"/>
+      <c r="Y16" s="89"/>
+      <c r="Z16" s="89"/>
+      <c r="AA16" s="89"/>
+      <c r="AB16" s="89"/>
+      <c r="AC16" s="89"/>
+      <c r="AD16" s="89"/>
+      <c r="AE16" s="89"/>
+      <c r="AF16" s="90"/>
       <c r="AJ16" s="33"/>
       <c r="AK16" s="26"/>
     </row>
     <row r="17" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="155"/>
-      <c r="B17" s="257" t="s">
+      <c r="A17" s="222"/>
+      <c r="B17" s="230" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="258"/>
-      <c r="D17" s="258"/>
-      <c r="E17" s="258"/>
-      <c r="F17" s="157"/>
-      <c r="G17" s="225"/>
-      <c r="H17" s="226"/>
-      <c r="I17" s="226"/>
-      <c r="J17" s="226"/>
-      <c r="K17" s="226"/>
-      <c r="L17" s="226"/>
-      <c r="M17" s="226"/>
-      <c r="N17" s="226"/>
-      <c r="O17" s="226"/>
-      <c r="P17" s="227"/>
-      <c r="Q17" s="254" t="s">
+      <c r="C17" s="231"/>
+      <c r="D17" s="231"/>
+      <c r="E17" s="231"/>
+      <c r="F17" s="232"/>
+      <c r="G17" s="155"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="156"/>
+      <c r="J17" s="156"/>
+      <c r="K17" s="156"/>
+      <c r="L17" s="156"/>
+      <c r="M17" s="156"/>
+      <c r="N17" s="156"/>
+      <c r="O17" s="156"/>
+      <c r="P17" s="251"/>
+      <c r="Q17" s="224" t="s">
         <v>16</v>
       </c>
-      <c r="R17" s="255"/>
-      <c r="S17" s="255"/>
-      <c r="T17" s="256"/>
-      <c r="U17" s="244" t="s">
-        <v>17</v>
-      </c>
-      <c r="V17" s="245"/>
-      <c r="W17" s="245"/>
-      <c r="X17" s="245"/>
-      <c r="Y17" s="245"/>
-      <c r="Z17" s="245"/>
-      <c r="AA17" s="245"/>
-      <c r="AB17" s="245"/>
-      <c r="AC17" s="245"/>
-      <c r="AD17" s="245"/>
-      <c r="AE17" s="245"/>
-      <c r="AF17" s="246"/>
+      <c r="R17" s="225"/>
+      <c r="S17" s="225"/>
+      <c r="T17" s="226"/>
+      <c r="U17" s="170"/>
+      <c r="V17" s="171"/>
+      <c r="W17" s="171"/>
+      <c r="X17" s="171"/>
+      <c r="Y17" s="171"/>
+      <c r="Z17" s="171"/>
+      <c r="AA17" s="171"/>
+      <c r="AB17" s="171"/>
+      <c r="AC17" s="171"/>
+      <c r="AD17" s="171"/>
+      <c r="AE17" s="171"/>
+      <c r="AF17" s="172"/>
     </row>
     <row r="18" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="155"/>
-      <c r="B18" s="150" t="s">
+      <c r="A18" s="222"/>
+      <c r="B18" s="219" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="225"/>
-      <c r="H18" s="226"/>
-      <c r="I18" s="226"/>
-      <c r="J18" s="226"/>
-      <c r="K18" s="226"/>
-      <c r="L18" s="226"/>
-      <c r="M18" s="226"/>
-      <c r="N18" s="226"/>
-      <c r="O18" s="226"/>
-      <c r="P18" s="227"/>
-      <c r="Q18" s="150" t="s">
-        <v>18</v>
-      </c>
-      <c r="R18" s="125"/>
-      <c r="S18" s="125"/>
-      <c r="T18" s="138"/>
-      <c r="U18" s="151" t="s">
-        <v>19</v>
-      </c>
-      <c r="V18" s="152"/>
-      <c r="W18" s="152"/>
-      <c r="X18" s="152"/>
-      <c r="Y18" s="139" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z18" s="139"/>
-      <c r="AA18" s="139"/>
-      <c r="AB18" s="139"/>
-      <c r="AC18" s="139"/>
-      <c r="AD18" s="139"/>
-      <c r="AE18" s="139"/>
-      <c r="AF18" s="140"/>
+      <c r="C18" s="248"/>
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="218"/>
+      <c r="G18" s="155"/>
+      <c r="H18" s="156"/>
+      <c r="I18" s="156"/>
+      <c r="J18" s="156"/>
+      <c r="K18" s="156"/>
+      <c r="L18" s="156"/>
+      <c r="M18" s="156"/>
+      <c r="N18" s="156"/>
+      <c r="O18" s="156"/>
+      <c r="P18" s="251"/>
+      <c r="Q18" s="219" t="s">
+        <v>17</v>
+      </c>
+      <c r="R18" s="248"/>
+      <c r="S18" s="248"/>
+      <c r="T18" s="218"/>
+      <c r="U18" s="249"/>
+      <c r="V18" s="250"/>
+      <c r="W18" s="250"/>
+      <c r="X18" s="250"/>
+      <c r="Y18" s="250"/>
+      <c r="Z18" s="250"/>
+      <c r="AA18" s="250"/>
+      <c r="AB18" s="250"/>
+      <c r="AC18" s="250"/>
+      <c r="AD18" s="250"/>
+      <c r="AE18" s="250"/>
+      <c r="AF18" s="312"/>
     </row>
     <row r="19" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="155"/>
-      <c r="B19" s="138" t="s">
+      <c r="A19" s="222"/>
+      <c r="B19" s="218" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="153"/>
-      <c r="G19" s="228" t="s">
-        <v>64</v>
-      </c>
-      <c r="H19" s="159"/>
-      <c r="I19" s="159"/>
-      <c r="J19" s="159"/>
-      <c r="K19" s="159"/>
-      <c r="L19" s="159"/>
+      <c r="C19" s="219"/>
+      <c r="D19" s="219"/>
+      <c r="E19" s="219"/>
+      <c r="F19" s="220"/>
+      <c r="G19" s="87" t="s">
+        <v>61</v>
+      </c>
+      <c r="H19" s="164"/>
+      <c r="I19" s="164"/>
+      <c r="J19" s="164"/>
+      <c r="K19" s="164"/>
+      <c r="L19" s="164"/>
       <c r="M19" s="33" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="N19" s="24"/>
-      <c r="O19" s="229" t="s">
-        <v>69</v>
-      </c>
-      <c r="P19" s="229"/>
-      <c r="Q19" s="229"/>
-      <c r="R19" s="229"/>
-      <c r="S19" s="229"/>
-      <c r="T19" s="229"/>
-      <c r="U19" s="229"/>
-      <c r="V19" s="229"/>
-      <c r="W19" s="229"/>
-      <c r="X19" s="229"/>
-      <c r="Y19" s="229"/>
-      <c r="Z19" s="229"/>
-      <c r="AA19" s="229"/>
-      <c r="AB19" s="229"/>
-      <c r="AC19" s="229"/>
-      <c r="AD19" s="229"/>
-      <c r="AE19" s="229"/>
-      <c r="AF19" s="230"/>
+      <c r="O19" s="165" t="s">
+        <v>66</v>
+      </c>
+      <c r="P19" s="165"/>
+      <c r="Q19" s="165"/>
+      <c r="R19" s="165"/>
+      <c r="S19" s="165"/>
+      <c r="T19" s="165"/>
+      <c r="U19" s="165"/>
+      <c r="V19" s="165"/>
+      <c r="W19" s="165"/>
+      <c r="X19" s="165"/>
+      <c r="Y19" s="165"/>
+      <c r="Z19" s="165"/>
+      <c r="AA19" s="165"/>
+      <c r="AB19" s="165"/>
+      <c r="AC19" s="165"/>
+      <c r="AD19" s="165"/>
+      <c r="AE19" s="165"/>
+      <c r="AF19" s="166"/>
     </row>
     <row r="20" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="155"/>
-      <c r="B20" s="138"/>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="153"/>
-      <c r="G20" s="231"/>
-      <c r="H20" s="232"/>
-      <c r="I20" s="232"/>
-      <c r="J20" s="232"/>
-      <c r="K20" s="232"/>
-      <c r="L20" s="232"/>
-      <c r="M20" s="232"/>
-      <c r="N20" s="232"/>
-      <c r="O20" s="232"/>
-      <c r="P20" s="232"/>
-      <c r="Q20" s="232"/>
-      <c r="R20" s="232"/>
-      <c r="S20" s="232"/>
-      <c r="T20" s="232"/>
+      <c r="A20" s="222"/>
+      <c r="B20" s="218"/>
+      <c r="C20" s="219"/>
+      <c r="D20" s="219"/>
+      <c r="E20" s="219"/>
+      <c r="F20" s="220"/>
+      <c r="G20" s="167"/>
+      <c r="H20" s="168"/>
+      <c r="I20" s="168"/>
+      <c r="J20" s="168"/>
+      <c r="K20" s="168"/>
+      <c r="L20" s="168"/>
+      <c r="M20" s="168"/>
+      <c r="N20" s="168"/>
+      <c r="O20" s="168"/>
+      <c r="P20" s="168"/>
+      <c r="Q20" s="168"/>
+      <c r="R20" s="168"/>
+      <c r="S20" s="168"/>
+      <c r="T20" s="168"/>
       <c r="U20" s="34"/>
       <c r="V20" s="34"/>
       <c r="W20" s="34"/>
@@ -4293,346 +4230,346 @@
       <c r="AF20" s="27"/>
     </row>
     <row r="21" spans="1:37" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="155"/>
-      <c r="B21" s="138"/>
-      <c r="C21" s="150"/>
-      <c r="D21" s="150"/>
-      <c r="E21" s="150"/>
-      <c r="F21" s="153"/>
-      <c r="G21" s="183"/>
-      <c r="H21" s="124"/>
-      <c r="I21" s="124"/>
-      <c r="J21" s="124"/>
-      <c r="K21" s="124"/>
-      <c r="L21" s="124"/>
-      <c r="M21" s="124"/>
-      <c r="N21" s="124"/>
-      <c r="O21" s="124"/>
-      <c r="P21" s="124"/>
-      <c r="Q21" s="124"/>
-      <c r="R21" s="124"/>
-      <c r="S21" s="124"/>
-      <c r="T21" s="124"/>
-      <c r="U21" s="124" t="s">
+      <c r="A21" s="222"/>
+      <c r="B21" s="218"/>
+      <c r="C21" s="219"/>
+      <c r="D21" s="219"/>
+      <c r="E21" s="219"/>
+      <c r="F21" s="220"/>
+      <c r="G21" s="100"/>
+      <c r="H21" s="101"/>
+      <c r="I21" s="101"/>
+      <c r="J21" s="101"/>
+      <c r="K21" s="101"/>
+      <c r="L21" s="101"/>
+      <c r="M21" s="101"/>
+      <c r="N21" s="101"/>
+      <c r="O21" s="101"/>
+      <c r="P21" s="101"/>
+      <c r="Q21" s="101"/>
+      <c r="R21" s="101"/>
+      <c r="S21" s="101"/>
+      <c r="T21" s="101"/>
+      <c r="U21" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="V21" s="124"/>
-      <c r="W21" s="124"/>
-      <c r="X21" s="124"/>
-      <c r="Y21" s="124"/>
-      <c r="Z21" s="124"/>
-      <c r="AA21" s="124"/>
-      <c r="AB21" s="124"/>
-      <c r="AC21" s="124"/>
-      <c r="AD21" s="124"/>
-      <c r="AE21" s="124"/>
-      <c r="AF21" s="184"/>
+      <c r="V21" s="101"/>
+      <c r="W21" s="101"/>
+      <c r="X21" s="101"/>
+      <c r="Y21" s="101"/>
+      <c r="Z21" s="101"/>
+      <c r="AA21" s="101"/>
+      <c r="AB21" s="101"/>
+      <c r="AC21" s="101"/>
+      <c r="AD21" s="101"/>
+      <c r="AE21" s="101"/>
+      <c r="AF21" s="169"/>
     </row>
     <row r="22" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="155"/>
-      <c r="B22" s="141" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="142"/>
-      <c r="D22" s="142"/>
-      <c r="E22" s="142"/>
-      <c r="F22" s="143"/>
-      <c r="G22" s="147" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="148"/>
-      <c r="I22" s="149"/>
-      <c r="J22" s="225"/>
-      <c r="K22" s="226"/>
-      <c r="L22" s="226"/>
-      <c r="M22" s="226"/>
-      <c r="N22" s="226"/>
-      <c r="O22" s="226"/>
-      <c r="P22" s="226"/>
-      <c r="Q22" s="226"/>
-      <c r="R22" s="226"/>
-      <c r="S22" s="226"/>
-      <c r="T22" s="226"/>
-      <c r="U22" s="226"/>
-      <c r="V22" s="226"/>
-      <c r="W22" s="226"/>
-      <c r="X22" s="226"/>
-      <c r="Y22" s="226"/>
-      <c r="Z22" s="226"/>
-      <c r="AA22" s="226"/>
-      <c r="AB22" s="226"/>
-      <c r="AC22" s="226"/>
-      <c r="AD22" s="226"/>
-      <c r="AE22" s="226"/>
-      <c r="AF22" s="262"/>
+      <c r="A22" s="222"/>
+      <c r="B22" s="108" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="109"/>
+      <c r="D22" s="109"/>
+      <c r="E22" s="109"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="252" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="154"/>
+      <c r="I22" s="253"/>
+      <c r="J22" s="155"/>
+      <c r="K22" s="156"/>
+      <c r="L22" s="156"/>
+      <c r="M22" s="156"/>
+      <c r="N22" s="156"/>
+      <c r="O22" s="156"/>
+      <c r="P22" s="156"/>
+      <c r="Q22" s="156"/>
+      <c r="R22" s="156"/>
+      <c r="S22" s="156"/>
+      <c r="T22" s="156"/>
+      <c r="U22" s="156"/>
+      <c r="V22" s="156"/>
+      <c r="W22" s="156"/>
+      <c r="X22" s="156"/>
+      <c r="Y22" s="156"/>
+      <c r="Z22" s="156"/>
+      <c r="AA22" s="156"/>
+      <c r="AB22" s="156"/>
+      <c r="AC22" s="156"/>
+      <c r="AD22" s="156"/>
+      <c r="AE22" s="156"/>
+      <c r="AF22" s="157"/>
     </row>
     <row r="23" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="155"/>
-      <c r="B23" s="144"/>
-      <c r="C23" s="145"/>
-      <c r="D23" s="145"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="146"/>
-      <c r="G23" s="147" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="148"/>
-      <c r="I23" s="149"/>
-      <c r="J23" s="225"/>
-      <c r="K23" s="226"/>
-      <c r="L23" s="226"/>
-      <c r="M23" s="226"/>
-      <c r="N23" s="226"/>
-      <c r="O23" s="226"/>
-      <c r="P23" s="226"/>
-      <c r="Q23" s="226"/>
-      <c r="R23" s="148" t="s">
-        <v>71</v>
-      </c>
-      <c r="S23" s="148"/>
-      <c r="T23" s="226"/>
-      <c r="U23" s="226"/>
-      <c r="V23" s="226"/>
-      <c r="W23" s="226"/>
-      <c r="X23" s="226"/>
-      <c r="Y23" s="226"/>
-      <c r="Z23" s="226"/>
-      <c r="AA23" s="226"/>
-      <c r="AB23" s="226"/>
-      <c r="AC23" s="226"/>
-      <c r="AD23" s="226"/>
-      <c r="AE23" s="226"/>
-      <c r="AF23" s="262"/>
+      <c r="A23" s="222"/>
+      <c r="B23" s="134"/>
+      <c r="C23" s="135"/>
+      <c r="D23" s="135"/>
+      <c r="E23" s="135"/>
+      <c r="F23" s="136"/>
+      <c r="G23" s="252" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="154"/>
+      <c r="I23" s="253"/>
+      <c r="J23" s="155"/>
+      <c r="K23" s="156"/>
+      <c r="L23" s="156"/>
+      <c r="M23" s="156"/>
+      <c r="N23" s="156"/>
+      <c r="O23" s="156"/>
+      <c r="P23" s="156"/>
+      <c r="Q23" s="156"/>
+      <c r="R23" s="154" t="s">
+        <v>68</v>
+      </c>
+      <c r="S23" s="154"/>
+      <c r="T23" s="156"/>
+      <c r="U23" s="156"/>
+      <c r="V23" s="156"/>
+      <c r="W23" s="156"/>
+      <c r="X23" s="156"/>
+      <c r="Y23" s="156"/>
+      <c r="Z23" s="156"/>
+      <c r="AA23" s="156"/>
+      <c r="AB23" s="156"/>
+      <c r="AC23" s="156"/>
+      <c r="AD23" s="156"/>
+      <c r="AE23" s="156"/>
+      <c r="AF23" s="157"/>
     </row>
     <row r="24" spans="1:37" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="155"/>
-      <c r="B24" s="158" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="166"/>
-      <c r="D24" s="166"/>
-      <c r="E24" s="166"/>
-      <c r="F24" s="167"/>
-      <c r="G24" s="263"/>
-      <c r="H24" s="264"/>
-      <c r="I24" s="264"/>
-      <c r="J24" s="264"/>
-      <c r="K24" s="264"/>
-      <c r="L24" s="264"/>
-      <c r="M24" s="264"/>
-      <c r="N24" s="264"/>
-      <c r="O24" s="264"/>
-      <c r="P24" s="264"/>
-      <c r="Q24" s="264"/>
-      <c r="R24" s="264"/>
-      <c r="S24" s="264"/>
-      <c r="T24" s="264"/>
-      <c r="U24" s="264"/>
-      <c r="V24" s="264"/>
-      <c r="W24" s="264"/>
-      <c r="X24" s="264"/>
-      <c r="Y24" s="264"/>
-      <c r="Z24" s="264"/>
-      <c r="AA24" s="264"/>
-      <c r="AB24" s="264"/>
-      <c r="AC24" s="264"/>
-      <c r="AD24" s="264"/>
-      <c r="AE24" s="264"/>
-      <c r="AF24" s="265"/>
+      <c r="A24" s="222"/>
+      <c r="B24" s="233" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="234"/>
+      <c r="D24" s="234"/>
+      <c r="E24" s="234"/>
+      <c r="F24" s="235"/>
+      <c r="G24" s="313"/>
+      <c r="H24" s="314"/>
+      <c r="I24" s="314"/>
+      <c r="J24" s="314"/>
+      <c r="K24" s="314"/>
+      <c r="L24" s="314"/>
+      <c r="M24" s="314"/>
+      <c r="N24" s="314"/>
+      <c r="O24" s="314"/>
+      <c r="P24" s="314"/>
+      <c r="Q24" s="314"/>
+      <c r="R24" s="314"/>
+      <c r="S24" s="314"/>
+      <c r="T24" s="314"/>
+      <c r="U24" s="314"/>
+      <c r="V24" s="314"/>
+      <c r="W24" s="314"/>
+      <c r="X24" s="314"/>
+      <c r="Y24" s="314"/>
+      <c r="Z24" s="314"/>
+      <c r="AA24" s="314"/>
+      <c r="AB24" s="314"/>
+      <c r="AC24" s="314"/>
+      <c r="AD24" s="314"/>
+      <c r="AE24" s="314"/>
+      <c r="AF24" s="315"/>
       <c r="AJ24" s="33"/>
     </row>
     <row r="25" spans="1:37" s="18" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="155"/>
-      <c r="B25" s="251"/>
-      <c r="C25" s="252"/>
-      <c r="D25" s="252"/>
-      <c r="E25" s="252"/>
-      <c r="F25" s="253"/>
-      <c r="G25" s="266"/>
-      <c r="H25" s="267"/>
-      <c r="I25" s="267"/>
-      <c r="J25" s="267"/>
-      <c r="K25" s="267"/>
-      <c r="L25" s="267"/>
-      <c r="M25" s="267"/>
-      <c r="N25" s="267"/>
-      <c r="O25" s="267"/>
-      <c r="P25" s="267"/>
-      <c r="Q25" s="267"/>
-      <c r="R25" s="267"/>
-      <c r="S25" s="267"/>
-      <c r="T25" s="267"/>
-      <c r="U25" s="267"/>
-      <c r="V25" s="267"/>
-      <c r="W25" s="267"/>
-      <c r="X25" s="267"/>
-      <c r="Y25" s="267"/>
-      <c r="Z25" s="267"/>
-      <c r="AA25" s="267"/>
-      <c r="AB25" s="267"/>
-      <c r="AC25" s="267"/>
-      <c r="AD25" s="267"/>
-      <c r="AE25" s="267"/>
-      <c r="AF25" s="268"/>
+      <c r="A25" s="222"/>
+      <c r="B25" s="236"/>
+      <c r="C25" s="237"/>
+      <c r="D25" s="237"/>
+      <c r="E25" s="237"/>
+      <c r="F25" s="238"/>
+      <c r="G25" s="316"/>
+      <c r="H25" s="317"/>
+      <c r="I25" s="317"/>
+      <c r="J25" s="317"/>
+      <c r="K25" s="317"/>
+      <c r="L25" s="317"/>
+      <c r="M25" s="317"/>
+      <c r="N25" s="317"/>
+      <c r="O25" s="317"/>
+      <c r="P25" s="317"/>
+      <c r="Q25" s="317"/>
+      <c r="R25" s="317"/>
+      <c r="S25" s="317"/>
+      <c r="T25" s="317"/>
+      <c r="U25" s="317"/>
+      <c r="V25" s="317"/>
+      <c r="W25" s="317"/>
+      <c r="X25" s="317"/>
+      <c r="Y25" s="317"/>
+      <c r="Z25" s="317"/>
+      <c r="AA25" s="317"/>
+      <c r="AB25" s="317"/>
+      <c r="AC25" s="317"/>
+      <c r="AD25" s="317"/>
+      <c r="AE25" s="317"/>
+      <c r="AF25" s="318"/>
       <c r="AJ25" s="33"/>
     </row>
     <row r="26" spans="1:37" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="155"/>
-      <c r="B26" s="161" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="220"/>
-      <c r="D26" s="220"/>
-      <c r="E26" s="220"/>
-      <c r="F26" s="221"/>
-      <c r="G26" s="162" t="s">
-        <v>54</v>
-      </c>
-      <c r="H26" s="247"/>
-      <c r="I26" s="247"/>
-      <c r="J26" s="247"/>
-      <c r="K26" s="247"/>
-      <c r="L26" s="248"/>
-      <c r="M26" s="165"/>
-      <c r="N26" s="233"/>
-      <c r="O26" s="233"/>
-      <c r="P26" s="233"/>
-      <c r="Q26" s="233"/>
-      <c r="R26" s="233"/>
-      <c r="S26" s="233"/>
-      <c r="T26" s="233"/>
-      <c r="U26" s="234"/>
-      <c r="V26" s="163" t="s">
-        <v>55</v>
-      </c>
-      <c r="W26" s="249"/>
-      <c r="X26" s="249"/>
-      <c r="Y26" s="249"/>
-      <c r="Z26" s="250"/>
-      <c r="AA26" s="269"/>
-      <c r="AB26" s="164"/>
-      <c r="AC26" s="164"/>
-      <c r="AD26" s="164"/>
-      <c r="AE26" s="164"/>
-      <c r="AF26" s="270"/>
+      <c r="A26" s="222"/>
+      <c r="B26" s="91" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="93"/>
+      <c r="G26" s="239" t="s">
+        <v>51</v>
+      </c>
+      <c r="H26" s="240"/>
+      <c r="I26" s="240"/>
+      <c r="J26" s="240"/>
+      <c r="K26" s="240"/>
+      <c r="L26" s="241"/>
+      <c r="M26" s="158"/>
+      <c r="N26" s="159"/>
+      <c r="O26" s="159"/>
+      <c r="P26" s="159"/>
+      <c r="Q26" s="159"/>
+      <c r="R26" s="159"/>
+      <c r="S26" s="159"/>
+      <c r="T26" s="159"/>
+      <c r="U26" s="160"/>
+      <c r="V26" s="242" t="s">
+        <v>52</v>
+      </c>
+      <c r="W26" s="243"/>
+      <c r="X26" s="243"/>
+      <c r="Y26" s="243"/>
+      <c r="Z26" s="244"/>
+      <c r="AA26" s="161"/>
+      <c r="AB26" s="162"/>
+      <c r="AC26" s="162"/>
+      <c r="AD26" s="162"/>
+      <c r="AE26" s="162"/>
+      <c r="AF26" s="163"/>
       <c r="AJ26" s="33"/>
       <c r="AK26" s="18"/>
     </row>
     <row r="27" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="155"/>
-      <c r="B27" s="222"/>
-      <c r="C27" s="132"/>
-      <c r="D27" s="132"/>
-      <c r="E27" s="132"/>
-      <c r="F27" s="133"/>
-      <c r="G27" s="162" t="s">
-        <v>56</v>
-      </c>
-      <c r="H27" s="247"/>
-      <c r="I27" s="247"/>
-      <c r="J27" s="247"/>
-      <c r="K27" s="247"/>
-      <c r="L27" s="248"/>
-      <c r="M27" s="165" t="s">
-        <v>57</v>
-      </c>
-      <c r="N27" s="234"/>
-      <c r="O27" s="165"/>
-      <c r="P27" s="233"/>
-      <c r="Q27" s="233"/>
-      <c r="R27" s="233"/>
-      <c r="S27" s="233"/>
-      <c r="T27" s="233"/>
-      <c r="U27" s="234"/>
-      <c r="V27" s="165" t="s">
-        <v>58</v>
-      </c>
-      <c r="W27" s="233"/>
-      <c r="X27" s="234"/>
-      <c r="Y27" s="269"/>
-      <c r="Z27" s="164"/>
-      <c r="AA27" s="164"/>
-      <c r="AB27" s="164"/>
-      <c r="AC27" s="164"/>
-      <c r="AD27" s="164"/>
-      <c r="AE27" s="164"/>
-      <c r="AF27" s="270"/>
+      <c r="A27" s="222"/>
+      <c r="B27" s="94"/>
+      <c r="C27" s="95"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="95"/>
+      <c r="F27" s="96"/>
+      <c r="G27" s="239" t="s">
+        <v>53</v>
+      </c>
+      <c r="H27" s="240"/>
+      <c r="I27" s="240"/>
+      <c r="J27" s="240"/>
+      <c r="K27" s="240"/>
+      <c r="L27" s="241"/>
+      <c r="M27" s="158" t="s">
+        <v>54</v>
+      </c>
+      <c r="N27" s="160"/>
+      <c r="O27" s="158"/>
+      <c r="P27" s="159"/>
+      <c r="Q27" s="159"/>
+      <c r="R27" s="159"/>
+      <c r="S27" s="159"/>
+      <c r="T27" s="159"/>
+      <c r="U27" s="160"/>
+      <c r="V27" s="158" t="s">
+        <v>55</v>
+      </c>
+      <c r="W27" s="159"/>
+      <c r="X27" s="160"/>
+      <c r="Y27" s="161"/>
+      <c r="Z27" s="162"/>
+      <c r="AA27" s="162"/>
+      <c r="AB27" s="162"/>
+      <c r="AC27" s="162"/>
+      <c r="AD27" s="162"/>
+      <c r="AE27" s="162"/>
+      <c r="AF27" s="163"/>
       <c r="AJ27" s="33"/>
       <c r="AK27" s="18"/>
     </row>
     <row r="28" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="155"/>
-      <c r="B28" s="220" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="220"/>
-      <c r="D28" s="220"/>
-      <c r="E28" s="220"/>
-      <c r="F28" s="221"/>
-      <c r="G28" s="235"/>
-      <c r="H28" s="236"/>
-      <c r="I28" s="236"/>
-      <c r="J28" s="236"/>
-      <c r="K28" s="236"/>
-      <c r="L28" s="236"/>
-      <c r="M28" s="236"/>
-      <c r="N28" s="236"/>
-      <c r="O28" s="236"/>
-      <c r="P28" s="236"/>
-      <c r="Q28" s="236"/>
-      <c r="R28" s="236"/>
-      <c r="S28" s="236"/>
-      <c r="T28" s="236"/>
-      <c r="U28" s="236"/>
-      <c r="V28" s="236"/>
-      <c r="W28" s="236"/>
-      <c r="X28" s="236"/>
-      <c r="Y28" s="236"/>
-      <c r="Z28" s="236"/>
-      <c r="AA28" s="236"/>
-      <c r="AB28" s="236"/>
-      <c r="AC28" s="236"/>
-      <c r="AD28" s="236"/>
-      <c r="AE28" s="236"/>
-      <c r="AF28" s="237"/>
+      <c r="A28" s="222"/>
+      <c r="B28" s="92" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="92"/>
+      <c r="D28" s="92"/>
+      <c r="E28" s="92"/>
+      <c r="F28" s="93"/>
+      <c r="G28" s="151"/>
+      <c r="H28" s="152"/>
+      <c r="I28" s="152"/>
+      <c r="J28" s="152"/>
+      <c r="K28" s="152"/>
+      <c r="L28" s="152"/>
+      <c r="M28" s="152"/>
+      <c r="N28" s="152"/>
+      <c r="O28" s="152"/>
+      <c r="P28" s="152"/>
+      <c r="Q28" s="152"/>
+      <c r="R28" s="152"/>
+      <c r="S28" s="152"/>
+      <c r="T28" s="152"/>
+      <c r="U28" s="152"/>
+      <c r="V28" s="152"/>
+      <c r="W28" s="152"/>
+      <c r="X28" s="152"/>
+      <c r="Y28" s="152"/>
+      <c r="Z28" s="152"/>
+      <c r="AA28" s="152"/>
+      <c r="AB28" s="152"/>
+      <c r="AC28" s="152"/>
+      <c r="AD28" s="152"/>
+      <c r="AE28" s="152"/>
+      <c r="AF28" s="153"/>
       <c r="AJ28" s="33"/>
       <c r="AK28" s="18"/>
     </row>
     <row r="29" spans="1:37" s="3" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="238"/>
-      <c r="B29" s="239"/>
-      <c r="C29" s="239"/>
-      <c r="D29" s="239"/>
-      <c r="E29" s="239"/>
-      <c r="F29" s="240"/>
-      <c r="G29" s="241" t="s">
-        <v>70</v>
-      </c>
-      <c r="H29" s="242"/>
-      <c r="I29" s="242"/>
-      <c r="J29" s="242"/>
-      <c r="K29" s="242"/>
-      <c r="L29" s="242"/>
-      <c r="M29" s="242"/>
-      <c r="N29" s="242"/>
-      <c r="O29" s="242"/>
-      <c r="P29" s="242"/>
-      <c r="Q29" s="242"/>
-      <c r="R29" s="242"/>
-      <c r="S29" s="242"/>
-      <c r="T29" s="242"/>
-      <c r="U29" s="242"/>
-      <c r="V29" s="242"/>
-      <c r="W29" s="242"/>
-      <c r="X29" s="242"/>
-      <c r="Y29" s="242"/>
-      <c r="Z29" s="242"/>
-      <c r="AA29" s="242"/>
-      <c r="AB29" s="242"/>
-      <c r="AC29" s="242"/>
-      <c r="AD29" s="242"/>
-      <c r="AE29" s="242"/>
-      <c r="AF29" s="243"/>
+      <c r="A29" s="223"/>
+      <c r="B29" s="149"/>
+      <c r="C29" s="149"/>
+      <c r="D29" s="149"/>
+      <c r="E29" s="149"/>
+      <c r="F29" s="150"/>
+      <c r="G29" s="245" t="s">
+        <v>67</v>
+      </c>
+      <c r="H29" s="246"/>
+      <c r="I29" s="246"/>
+      <c r="J29" s="246"/>
+      <c r="K29" s="246"/>
+      <c r="L29" s="246"/>
+      <c r="M29" s="246"/>
+      <c r="N29" s="246"/>
+      <c r="O29" s="246"/>
+      <c r="P29" s="246"/>
+      <c r="Q29" s="246"/>
+      <c r="R29" s="246"/>
+      <c r="S29" s="246"/>
+      <c r="T29" s="246"/>
+      <c r="U29" s="246"/>
+      <c r="V29" s="246"/>
+      <c r="W29" s="246"/>
+      <c r="X29" s="246"/>
+      <c r="Y29" s="246"/>
+      <c r="Z29" s="246"/>
+      <c r="AA29" s="246"/>
+      <c r="AB29" s="246"/>
+      <c r="AC29" s="246"/>
+      <c r="AD29" s="246"/>
+      <c r="AE29" s="246"/>
+      <c r="AF29" s="247"/>
       <c r="AG29" s="1"/>
       <c r="AH29" s="1"/>
       <c r="AI29" s="1"/>
@@ -4676,18 +4613,18 @@
       <c r="AK30" s="26"/>
     </row>
     <row r="31" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="126" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="271" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" s="272"/>
-      <c r="D31" s="272"/>
-      <c r="E31" s="272"/>
-      <c r="F31" s="273"/>
+      <c r="A31" s="264" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="274" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="275"/>
+      <c r="D31" s="275"/>
+      <c r="E31" s="275"/>
+      <c r="F31" s="276"/>
       <c r="G31" s="42" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
@@ -4696,23 +4633,23 @@
       <c r="L31" s="32"/>
       <c r="M31" s="26"/>
       <c r="N31" s="43"/>
-      <c r="O31" s="182" t="s">
-        <v>26</v>
-      </c>
-      <c r="P31" s="179"/>
-      <c r="Q31" s="274" t="s">
-        <v>64</v>
-      </c>
-      <c r="R31" s="274"/>
-      <c r="S31" s="179"/>
-      <c r="T31" s="179"/>
-      <c r="U31" s="179"/>
-      <c r="V31" s="179"/>
-      <c r="W31" s="179"/>
-      <c r="X31" s="179"/>
-      <c r="Y31" s="179"/>
-      <c r="Z31" s="228" t="s">
-        <v>68</v>
+      <c r="O31" s="123" t="s">
+        <v>23</v>
+      </c>
+      <c r="P31" s="124"/>
+      <c r="Q31" s="137" t="s">
+        <v>61</v>
+      </c>
+      <c r="R31" s="137"/>
+      <c r="S31" s="124"/>
+      <c r="T31" s="124"/>
+      <c r="U31" s="124"/>
+      <c r="V31" s="124"/>
+      <c r="W31" s="124"/>
+      <c r="X31" s="124"/>
+      <c r="Y31" s="124"/>
+      <c r="Z31" s="87" t="s">
+        <v>65</v>
       </c>
       <c r="AA31" s="26"/>
       <c r="AB31" s="44"/>
@@ -4724,100 +4661,100 @@
       <c r="AK31" s="26"/>
     </row>
     <row r="32" spans="1:37" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="127"/>
-      <c r="B32" s="275" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="276"/>
-      <c r="D32" s="276"/>
-      <c r="E32" s="276"/>
-      <c r="F32" s="277"/>
-      <c r="G32" s="278"/>
-      <c r="H32" s="279"/>
-      <c r="I32" s="279"/>
-      <c r="J32" s="279"/>
-      <c r="K32" s="279"/>
-      <c r="L32" s="279"/>
-      <c r="M32" s="279"/>
-      <c r="N32" s="280"/>
-      <c r="O32" s="278"/>
-      <c r="P32" s="279"/>
-      <c r="Q32" s="279"/>
-      <c r="R32" s="279"/>
-      <c r="S32" s="279"/>
-      <c r="T32" s="279"/>
-      <c r="U32" s="279"/>
-      <c r="V32" s="279"/>
-      <c r="W32" s="279"/>
-      <c r="X32" s="279"/>
-      <c r="Y32" s="279"/>
-      <c r="Z32" s="279"/>
-      <c r="AA32" s="279"/>
-      <c r="AB32" s="279"/>
-      <c r="AC32" s="279"/>
-      <c r="AD32" s="279"/>
-      <c r="AE32" s="279"/>
-      <c r="AF32" s="281"/>
+      <c r="A32" s="265"/>
+      <c r="B32" s="138" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="139"/>
+      <c r="D32" s="139"/>
+      <c r="E32" s="139"/>
+      <c r="F32" s="140"/>
+      <c r="G32" s="103"/>
+      <c r="H32" s="104"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="104"/>
+      <c r="K32" s="104"/>
+      <c r="L32" s="104"/>
+      <c r="M32" s="104"/>
+      <c r="N32" s="144"/>
+      <c r="O32" s="103"/>
+      <c r="P32" s="104"/>
+      <c r="Q32" s="104"/>
+      <c r="R32" s="104"/>
+      <c r="S32" s="104"/>
+      <c r="T32" s="104"/>
+      <c r="U32" s="104"/>
+      <c r="V32" s="104"/>
+      <c r="W32" s="104"/>
+      <c r="X32" s="104"/>
+      <c r="Y32" s="104"/>
+      <c r="Z32" s="104"/>
+      <c r="AA32" s="104"/>
+      <c r="AB32" s="104"/>
+      <c r="AC32" s="104"/>
+      <c r="AD32" s="104"/>
+      <c r="AE32" s="104"/>
+      <c r="AF32" s="105"/>
       <c r="AJ32" s="32"/>
       <c r="AK32" s="26"/>
     </row>
     <row r="33" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="127"/>
-      <c r="B33" s="282"/>
-      <c r="C33" s="283"/>
-      <c r="D33" s="283"/>
-      <c r="E33" s="283"/>
-      <c r="F33" s="284"/>
-      <c r="G33" s="285"/>
-      <c r="H33" s="286"/>
-      <c r="I33" s="286"/>
-      <c r="J33" s="286"/>
-      <c r="K33" s="286"/>
-      <c r="L33" s="286"/>
-      <c r="M33" s="286"/>
-      <c r="N33" s="287"/>
+      <c r="A33" s="265"/>
+      <c r="B33" s="141"/>
+      <c r="C33" s="142"/>
+      <c r="D33" s="142"/>
+      <c r="E33" s="142"/>
+      <c r="F33" s="143"/>
+      <c r="G33" s="145"/>
+      <c r="H33" s="146"/>
+      <c r="I33" s="146"/>
+      <c r="J33" s="146"/>
+      <c r="K33" s="146"/>
+      <c r="L33" s="146"/>
+      <c r="M33" s="146"/>
+      <c r="N33" s="147"/>
       <c r="O33" s="47"/>
       <c r="P33" s="48"/>
       <c r="Q33" s="35"/>
       <c r="R33" s="5"/>
       <c r="S33" s="5"/>
-      <c r="T33" s="160" t="s">
+      <c r="T33" s="148" t="s">
         <v>10</v>
       </c>
-      <c r="U33" s="160"/>
-      <c r="V33" s="160"/>
-      <c r="W33" s="288"/>
-      <c r="X33" s="288"/>
-      <c r="Y33" s="288"/>
-      <c r="Z33" s="288"/>
-      <c r="AA33" s="288"/>
-      <c r="AB33" s="288"/>
-      <c r="AC33" s="288"/>
-      <c r="AD33" s="288"/>
-      <c r="AE33" s="288"/>
-      <c r="AF33" s="289"/>
+      <c r="U33" s="148"/>
+      <c r="V33" s="148"/>
+      <c r="W33" s="106"/>
+      <c r="X33" s="106"/>
+      <c r="Y33" s="106"/>
+      <c r="Z33" s="106"/>
+      <c r="AA33" s="106"/>
+      <c r="AB33" s="106"/>
+      <c r="AC33" s="106"/>
+      <c r="AD33" s="106"/>
+      <c r="AE33" s="106"/>
+      <c r="AF33" s="107"/>
       <c r="AJ33" s="32"/>
       <c r="AK33" s="26"/>
     </row>
     <row r="34" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="127"/>
-      <c r="B34" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" s="134"/>
-      <c r="D34" s="134"/>
-      <c r="E34" s="134"/>
-      <c r="F34" s="135"/>
-      <c r="G34" s="290" t="s">
+      <c r="A34" s="265"/>
+      <c r="B34" s="267" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="267"/>
+      <c r="D34" s="267"/>
+      <c r="E34" s="267"/>
+      <c r="F34" s="268"/>
+      <c r="G34" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="H34" s="291"/>
-      <c r="I34" s="292"/>
-      <c r="J34" s="292"/>
-      <c r="K34" s="292"/>
-      <c r="L34" s="292"/>
-      <c r="M34" s="292"/>
-      <c r="N34" s="293"/>
+      <c r="H34" s="127"/>
+      <c r="I34" s="128"/>
+      <c r="J34" s="128"/>
+      <c r="K34" s="128"/>
+      <c r="L34" s="128"/>
+      <c r="M34" s="128"/>
+      <c r="N34" s="129"/>
       <c r="O34" s="50" t="s">
         <v>8</v>
       </c>
@@ -4826,7 +4763,7 @@
       <c r="R34" s="51"/>
       <c r="S34" s="52"/>
       <c r="T34" s="23" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="U34" s="53"/>
       <c r="V34" s="23"/>
@@ -4839,82 +4776,82 @@
       <c r="AK34" s="26"/>
     </row>
     <row r="35" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="127"/>
-      <c r="B35" s="136" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="136"/>
-      <c r="D35" s="136"/>
-      <c r="E35" s="136"/>
-      <c r="F35" s="137"/>
-      <c r="G35" s="294" t="s">
-        <v>74</v>
-      </c>
-      <c r="H35" s="295"/>
-      <c r="I35" s="296"/>
-      <c r="J35" s="296"/>
-      <c r="K35" s="296"/>
-      <c r="L35" s="296"/>
-      <c r="M35" s="296"/>
-      <c r="N35" s="297"/>
-      <c r="O35" s="144"/>
-      <c r="P35" s="145"/>
-      <c r="Q35" s="145"/>
-      <c r="R35" s="145"/>
-      <c r="S35" s="146"/>
-      <c r="T35" s="298"/>
-      <c r="U35" s="299"/>
-      <c r="V35" s="299"/>
-      <c r="W35" s="299"/>
-      <c r="X35" s="299"/>
-      <c r="Y35" s="299"/>
-      <c r="Z35" s="299"/>
-      <c r="AA35" s="299"/>
-      <c r="AB35" s="299"/>
-      <c r="AC35" s="299"/>
-      <c r="AD35" s="299"/>
-      <c r="AE35" s="299"/>
-      <c r="AF35" s="300"/>
+      <c r="A35" s="265"/>
+      <c r="B35" s="269" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="269"/>
+      <c r="D35" s="269"/>
+      <c r="E35" s="269"/>
+      <c r="F35" s="270"/>
+      <c r="G35" s="130" t="s">
+        <v>71</v>
+      </c>
+      <c r="H35" s="131"/>
+      <c r="I35" s="132"/>
+      <c r="J35" s="132"/>
+      <c r="K35" s="132"/>
+      <c r="L35" s="132"/>
+      <c r="M35" s="132"/>
+      <c r="N35" s="133"/>
+      <c r="O35" s="134"/>
+      <c r="P35" s="135"/>
+      <c r="Q35" s="135"/>
+      <c r="R35" s="135"/>
+      <c r="S35" s="136"/>
+      <c r="T35" s="115"/>
+      <c r="U35" s="116"/>
+      <c r="V35" s="116"/>
+      <c r="W35" s="116"/>
+      <c r="X35" s="116"/>
+      <c r="Y35" s="116"/>
+      <c r="Z35" s="116"/>
+      <c r="AA35" s="116"/>
+      <c r="AB35" s="116"/>
+      <c r="AC35" s="116"/>
+      <c r="AD35" s="116"/>
+      <c r="AE35" s="116"/>
+      <c r="AF35" s="117"/>
       <c r="AJ35" s="32"/>
       <c r="AK35" s="26"/>
     </row>
     <row r="36" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="127"/>
-      <c r="B36" s="125" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="125"/>
-      <c r="D36" s="125"/>
-      <c r="E36" s="125"/>
-      <c r="F36" s="138"/>
-      <c r="G36" s="301" t="s">
-        <v>75</v>
-      </c>
-      <c r="H36" s="302"/>
-      <c r="I36" s="302"/>
-      <c r="J36" s="302"/>
-      <c r="K36" s="302"/>
-      <c r="L36" s="302"/>
-      <c r="M36" s="302"/>
-      <c r="N36" s="302"/>
-      <c r="O36" s="302"/>
-      <c r="P36" s="302"/>
-      <c r="Q36" s="302"/>
-      <c r="R36" s="302"/>
-      <c r="S36" s="302"/>
-      <c r="T36" s="302"/>
-      <c r="U36" s="302"/>
-      <c r="V36" s="302"/>
-      <c r="W36" s="302"/>
-      <c r="X36" s="302"/>
-      <c r="Y36" s="302"/>
-      <c r="Z36" s="302"/>
-      <c r="AA36" s="302"/>
-      <c r="AB36" s="302"/>
-      <c r="AC36" s="302"/>
-      <c r="AD36" s="302"/>
-      <c r="AE36" s="302"/>
-      <c r="AF36" s="303"/>
+      <c r="A36" s="265"/>
+      <c r="B36" s="248" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="248"/>
+      <c r="D36" s="248"/>
+      <c r="E36" s="248"/>
+      <c r="F36" s="218"/>
+      <c r="G36" s="271" t="s">
+        <v>72</v>
+      </c>
+      <c r="H36" s="272"/>
+      <c r="I36" s="272"/>
+      <c r="J36" s="272"/>
+      <c r="K36" s="272"/>
+      <c r="L36" s="272"/>
+      <c r="M36" s="272"/>
+      <c r="N36" s="272"/>
+      <c r="O36" s="272"/>
+      <c r="P36" s="272"/>
+      <c r="Q36" s="272"/>
+      <c r="R36" s="272"/>
+      <c r="S36" s="272"/>
+      <c r="T36" s="272"/>
+      <c r="U36" s="272"/>
+      <c r="V36" s="272"/>
+      <c r="W36" s="272"/>
+      <c r="X36" s="272"/>
+      <c r="Y36" s="272"/>
+      <c r="Z36" s="272"/>
+      <c r="AA36" s="272"/>
+      <c r="AB36" s="272"/>
+      <c r="AC36" s="272"/>
+      <c r="AD36" s="272"/>
+      <c r="AE36" s="272"/>
+      <c r="AF36" s="273"/>
       <c r="AG36" s="18"/>
       <c r="AH36" s="18"/>
       <c r="AI36" s="18"/>
@@ -4922,40 +4859,40 @@
       <c r="AK36" s="18"/>
     </row>
     <row r="37" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="127"/>
-      <c r="B37" s="141" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="142"/>
-      <c r="D37" s="142"/>
-      <c r="E37" s="142"/>
-      <c r="F37" s="143"/>
-      <c r="G37" s="304"/>
-      <c r="H37" s="305"/>
-      <c r="I37" s="305"/>
-      <c r="J37" s="305"/>
-      <c r="K37" s="305"/>
-      <c r="L37" s="305"/>
-      <c r="M37" s="305"/>
-      <c r="N37" s="305"/>
-      <c r="O37" s="305"/>
-      <c r="P37" s="305"/>
-      <c r="Q37" s="305"/>
-      <c r="R37" s="305"/>
-      <c r="S37" s="305"/>
-      <c r="T37" s="305"/>
-      <c r="U37" s="305"/>
-      <c r="V37" s="305"/>
-      <c r="W37" s="305"/>
-      <c r="X37" s="305"/>
-      <c r="Y37" s="305"/>
-      <c r="Z37" s="305"/>
-      <c r="AA37" s="305"/>
-      <c r="AB37" s="305"/>
-      <c r="AC37" s="305"/>
-      <c r="AD37" s="305"/>
-      <c r="AE37" s="305"/>
-      <c r="AF37" s="306"/>
+      <c r="A37" s="265"/>
+      <c r="B37" s="108" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="109"/>
+      <c r="D37" s="109"/>
+      <c r="E37" s="109"/>
+      <c r="F37" s="118"/>
+      <c r="G37" s="120"/>
+      <c r="H37" s="121"/>
+      <c r="I37" s="121"/>
+      <c r="J37" s="121"/>
+      <c r="K37" s="121"/>
+      <c r="L37" s="121"/>
+      <c r="M37" s="121"/>
+      <c r="N37" s="121"/>
+      <c r="O37" s="121"/>
+      <c r="P37" s="121"/>
+      <c r="Q37" s="121"/>
+      <c r="R37" s="121"/>
+      <c r="S37" s="121"/>
+      <c r="T37" s="121"/>
+      <c r="U37" s="121"/>
+      <c r="V37" s="121"/>
+      <c r="W37" s="121"/>
+      <c r="X37" s="121"/>
+      <c r="Y37" s="121"/>
+      <c r="Z37" s="121"/>
+      <c r="AA37" s="121"/>
+      <c r="AB37" s="121"/>
+      <c r="AC37" s="121"/>
+      <c r="AD37" s="121"/>
+      <c r="AE37" s="121"/>
+      <c r="AF37" s="122"/>
       <c r="AG37" s="18"/>
       <c r="AH37" s="18"/>
       <c r="AI37" s="18"/>
@@ -4963,40 +4900,40 @@
       <c r="AK37" s="18"/>
     </row>
     <row r="38" spans="1:37" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="128"/>
-      <c r="B38" s="307"/>
-      <c r="C38" s="308"/>
-      <c r="D38" s="308"/>
-      <c r="E38" s="308"/>
-      <c r="F38" s="309"/>
-      <c r="G38" s="310" t="s">
-        <v>32</v>
-      </c>
-      <c r="H38" s="311"/>
-      <c r="I38" s="311"/>
-      <c r="J38" s="311"/>
-      <c r="K38" s="311"/>
-      <c r="L38" s="311"/>
-      <c r="M38" s="311"/>
-      <c r="N38" s="311"/>
-      <c r="O38" s="311"/>
-      <c r="P38" s="311"/>
-      <c r="Q38" s="311"/>
-      <c r="R38" s="311"/>
-      <c r="S38" s="311"/>
-      <c r="T38" s="311"/>
-      <c r="U38" s="311"/>
-      <c r="V38" s="311"/>
-      <c r="W38" s="311"/>
-      <c r="X38" s="311"/>
-      <c r="Y38" s="311"/>
-      <c r="Z38" s="311"/>
-      <c r="AA38" s="311"/>
-      <c r="AB38" s="311"/>
-      <c r="AC38" s="311"/>
-      <c r="AD38" s="311"/>
-      <c r="AE38" s="311"/>
-      <c r="AF38" s="312"/>
+      <c r="A38" s="266"/>
+      <c r="B38" s="110"/>
+      <c r="C38" s="111"/>
+      <c r="D38" s="111"/>
+      <c r="E38" s="111"/>
+      <c r="F38" s="119"/>
+      <c r="G38" s="254" t="s">
+        <v>29</v>
+      </c>
+      <c r="H38" s="255"/>
+      <c r="I38" s="255"/>
+      <c r="J38" s="255"/>
+      <c r="K38" s="255"/>
+      <c r="L38" s="255"/>
+      <c r="M38" s="255"/>
+      <c r="N38" s="255"/>
+      <c r="O38" s="255"/>
+      <c r="P38" s="255"/>
+      <c r="Q38" s="255"/>
+      <c r="R38" s="255"/>
+      <c r="S38" s="255"/>
+      <c r="T38" s="255"/>
+      <c r="U38" s="255"/>
+      <c r="V38" s="255"/>
+      <c r="W38" s="255"/>
+      <c r="X38" s="255"/>
+      <c r="Y38" s="255"/>
+      <c r="Z38" s="255"/>
+      <c r="AA38" s="255"/>
+      <c r="AB38" s="255"/>
+      <c r="AC38" s="255"/>
+      <c r="AD38" s="255"/>
+      <c r="AE38" s="255"/>
+      <c r="AF38" s="256"/>
       <c r="AG38" s="18"/>
       <c r="AH38" s="18"/>
       <c r="AI38" s="18"/>
@@ -5038,28 +4975,28 @@
       <c r="AF39" s="28"/>
     </row>
     <row r="40" spans="1:37" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="119" t="s">
-        <v>33</v>
-      </c>
-      <c r="B40" s="123" t="s">
-        <v>34</v>
-      </c>
-      <c r="C40" s="123"/>
-      <c r="D40" s="123"/>
-      <c r="E40" s="123"/>
-      <c r="F40" s="123"/>
-      <c r="G40" s="182"/>
-      <c r="H40" s="179"/>
-      <c r="I40" s="179"/>
-      <c r="J40" s="179"/>
-      <c r="K40" s="179"/>
-      <c r="L40" s="179"/>
-      <c r="M40" s="179"/>
-      <c r="N40" s="179"/>
-      <c r="O40" s="179"/>
-      <c r="P40" s="180"/>
+      <c r="A40" s="257" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="185" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="185"/>
+      <c r="D40" s="185"/>
+      <c r="E40" s="185"/>
+      <c r="F40" s="185"/>
+      <c r="G40" s="123"/>
+      <c r="H40" s="124"/>
+      <c r="I40" s="124"/>
+      <c r="J40" s="124"/>
+      <c r="K40" s="124"/>
+      <c r="L40" s="124"/>
+      <c r="M40" s="124"/>
+      <c r="N40" s="124"/>
+      <c r="O40" s="124"/>
+      <c r="P40" s="125"/>
       <c r="Q40" s="59" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="R40" s="60"/>
       <c r="S40" s="60"/>
@@ -5083,33 +5020,33 @@
       <c r="AK40" s="18"/>
     </row>
     <row r="41" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="120"/>
-      <c r="B41" s="124"/>
-      <c r="C41" s="124"/>
-      <c r="D41" s="124"/>
-      <c r="E41" s="124"/>
-      <c r="F41" s="124"/>
-      <c r="G41" s="183"/>
-      <c r="H41" s="124"/>
-      <c r="I41" s="124"/>
-      <c r="J41" s="124"/>
-      <c r="K41" s="124"/>
-      <c r="L41" s="124"/>
-      <c r="M41" s="124"/>
-      <c r="N41" s="124"/>
-      <c r="O41" s="124"/>
-      <c r="P41" s="181"/>
-      <c r="Q41" s="206" t="s">
-        <v>64</v>
-      </c>
-      <c r="R41" s="207"/>
-      <c r="S41" s="207"/>
-      <c r="T41" s="207"/>
-      <c r="U41" s="207"/>
-      <c r="V41" s="207"/>
-      <c r="W41" s="207"/>
+      <c r="A41" s="258"/>
+      <c r="B41" s="101"/>
+      <c r="C41" s="101"/>
+      <c r="D41" s="101"/>
+      <c r="E41" s="101"/>
+      <c r="F41" s="101"/>
+      <c r="G41" s="100"/>
+      <c r="H41" s="101"/>
+      <c r="I41" s="101"/>
+      <c r="J41" s="101"/>
+      <c r="K41" s="101"/>
+      <c r="L41" s="101"/>
+      <c r="M41" s="101"/>
+      <c r="N41" s="101"/>
+      <c r="O41" s="101"/>
+      <c r="P41" s="102"/>
+      <c r="Q41" s="97" t="s">
+        <v>61</v>
+      </c>
+      <c r="R41" s="98"/>
+      <c r="S41" s="98"/>
+      <c r="T41" s="98"/>
+      <c r="U41" s="98"/>
+      <c r="V41" s="98"/>
+      <c r="W41" s="98"/>
       <c r="X41" s="36" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="Y41" s="36"/>
       <c r="Z41" s="36"/>
@@ -5118,86 +5055,86 @@
       <c r="AC41" s="36"/>
       <c r="AD41" s="36"/>
       <c r="AE41" s="36"/>
-      <c r="AF41" s="313"/>
+      <c r="AF41" s="88"/>
       <c r="AK41" s="23"/>
     </row>
     <row r="42" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="121"/>
-      <c r="B42" s="161" t="s">
-        <v>36</v>
-      </c>
-      <c r="C42" s="220"/>
-      <c r="D42" s="220"/>
-      <c r="E42" s="220"/>
-      <c r="F42" s="221"/>
-      <c r="G42" s="206"/>
-      <c r="H42" s="207"/>
-      <c r="I42" s="207"/>
-      <c r="J42" s="207"/>
-      <c r="K42" s="207"/>
-      <c r="L42" s="207"/>
-      <c r="M42" s="207"/>
-      <c r="N42" s="207"/>
-      <c r="O42" s="207"/>
-      <c r="P42" s="314"/>
-      <c r="Q42" s="278"/>
-      <c r="R42" s="279"/>
-      <c r="S42" s="279"/>
-      <c r="T42" s="279"/>
-      <c r="U42" s="279"/>
-      <c r="V42" s="279"/>
-      <c r="W42" s="279"/>
-      <c r="X42" s="279"/>
-      <c r="Y42" s="279"/>
-      <c r="Z42" s="279"/>
-      <c r="AA42" s="279"/>
-      <c r="AB42" s="279"/>
-      <c r="AC42" s="279"/>
-      <c r="AD42" s="279"/>
-      <c r="AE42" s="279"/>
-      <c r="AF42" s="281"/>
+      <c r="A42" s="259"/>
+      <c r="B42" s="91" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="92"/>
+      <c r="D42" s="92"/>
+      <c r="E42" s="92"/>
+      <c r="F42" s="93"/>
+      <c r="G42" s="97"/>
+      <c r="H42" s="98"/>
+      <c r="I42" s="98"/>
+      <c r="J42" s="98"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="98"/>
+      <c r="M42" s="98"/>
+      <c r="N42" s="98"/>
+      <c r="O42" s="98"/>
+      <c r="P42" s="99"/>
+      <c r="Q42" s="103"/>
+      <c r="R42" s="104"/>
+      <c r="S42" s="104"/>
+      <c r="T42" s="104"/>
+      <c r="U42" s="104"/>
+      <c r="V42" s="104"/>
+      <c r="W42" s="104"/>
+      <c r="X42" s="104"/>
+      <c r="Y42" s="104"/>
+      <c r="Z42" s="104"/>
+      <c r="AA42" s="104"/>
+      <c r="AB42" s="104"/>
+      <c r="AC42" s="104"/>
+      <c r="AD42" s="104"/>
+      <c r="AE42" s="104"/>
+      <c r="AF42" s="105"/>
       <c r="AK42" s="23"/>
     </row>
     <row r="43" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="121"/>
-      <c r="B43" s="222"/>
-      <c r="C43" s="132"/>
-      <c r="D43" s="132"/>
-      <c r="E43" s="132"/>
-      <c r="F43" s="133"/>
-      <c r="G43" s="183"/>
-      <c r="H43" s="124"/>
-      <c r="I43" s="124"/>
-      <c r="J43" s="124"/>
-      <c r="K43" s="124"/>
-      <c r="L43" s="124"/>
-      <c r="M43" s="124"/>
-      <c r="N43" s="124"/>
-      <c r="O43" s="124"/>
-      <c r="P43" s="181"/>
+      <c r="A43" s="259"/>
+      <c r="B43" s="94"/>
+      <c r="C43" s="95"/>
+      <c r="D43" s="95"/>
+      <c r="E43" s="95"/>
+      <c r="F43" s="96"/>
+      <c r="G43" s="100"/>
+      <c r="H43" s="101"/>
+      <c r="I43" s="101"/>
+      <c r="J43" s="101"/>
+      <c r="K43" s="101"/>
+      <c r="L43" s="101"/>
+      <c r="M43" s="101"/>
+      <c r="N43" s="101"/>
+      <c r="O43" s="101"/>
+      <c r="P43" s="102"/>
       <c r="Q43" s="64" t="s">
         <v>10</v>
       </c>
       <c r="R43" s="62"/>
       <c r="S43" s="62"/>
       <c r="T43" s="62"/>
-      <c r="U43" s="288"/>
-      <c r="V43" s="288"/>
-      <c r="W43" s="288"/>
-      <c r="X43" s="288"/>
-      <c r="Y43" s="288"/>
-      <c r="Z43" s="288"/>
-      <c r="AA43" s="288"/>
-      <c r="AB43" s="288"/>
-      <c r="AC43" s="288"/>
-      <c r="AD43" s="288"/>
-      <c r="AE43" s="288"/>
-      <c r="AF43" s="289"/>
+      <c r="U43" s="106"/>
+      <c r="V43" s="106"/>
+      <c r="W43" s="106"/>
+      <c r="X43" s="106"/>
+      <c r="Y43" s="106"/>
+      <c r="Z43" s="106"/>
+      <c r="AA43" s="106"/>
+      <c r="AB43" s="106"/>
+      <c r="AC43" s="106"/>
+      <c r="AD43" s="106"/>
+      <c r="AE43" s="106"/>
+      <c r="AF43" s="107"/>
     </row>
     <row r="44" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="121"/>
+      <c r="A44" s="259"/>
       <c r="B44" s="36" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C44" s="66"/>
       <c r="D44" s="66"/>
@@ -5230,9 +5167,9 @@
       <c r="AJ44" s="33"/>
     </row>
     <row r="45" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="121"/>
+      <c r="A45" s="259"/>
       <c r="B45" s="69" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C45" s="70"/>
       <c r="D45" s="70"/>
@@ -5266,76 +5203,76 @@
       <c r="AF45" s="49"/>
     </row>
     <row r="46" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="121"/>
-      <c r="B46" s="141" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="142"/>
-      <c r="D46" s="142"/>
-      <c r="E46" s="142"/>
-      <c r="F46" s="142"/>
-      <c r="G46" s="315"/>
-      <c r="H46" s="316"/>
-      <c r="I46" s="316"/>
-      <c r="J46" s="316"/>
-      <c r="K46" s="316"/>
-      <c r="L46" s="316"/>
-      <c r="M46" s="316"/>
-      <c r="N46" s="316"/>
-      <c r="O46" s="316"/>
-      <c r="P46" s="316"/>
-      <c r="Q46" s="316"/>
-      <c r="R46" s="316"/>
-      <c r="S46" s="316"/>
-      <c r="T46" s="316"/>
-      <c r="U46" s="316"/>
-      <c r="V46" s="316"/>
-      <c r="W46" s="316"/>
-      <c r="X46" s="316"/>
-      <c r="Y46" s="316"/>
-      <c r="Z46" s="316"/>
-      <c r="AA46" s="316"/>
-      <c r="AB46" s="316"/>
-      <c r="AC46" s="316"/>
-      <c r="AD46" s="316"/>
-      <c r="AE46" s="316"/>
-      <c r="AF46" s="317"/>
+      <c r="A46" s="259"/>
+      <c r="B46" s="108" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" s="109"/>
+      <c r="D46" s="109"/>
+      <c r="E46" s="109"/>
+      <c r="F46" s="109"/>
+      <c r="G46" s="112"/>
+      <c r="H46" s="113"/>
+      <c r="I46" s="113"/>
+      <c r="J46" s="113"/>
+      <c r="K46" s="113"/>
+      <c r="L46" s="113"/>
+      <c r="M46" s="113"/>
+      <c r="N46" s="113"/>
+      <c r="O46" s="113"/>
+      <c r="P46" s="113"/>
+      <c r="Q46" s="113"/>
+      <c r="R46" s="113"/>
+      <c r="S46" s="113"/>
+      <c r="T46" s="113"/>
+      <c r="U46" s="113"/>
+      <c r="V46" s="113"/>
+      <c r="W46" s="113"/>
+      <c r="X46" s="113"/>
+      <c r="Y46" s="113"/>
+      <c r="Z46" s="113"/>
+      <c r="AA46" s="113"/>
+      <c r="AB46" s="113"/>
+      <c r="AC46" s="113"/>
+      <c r="AD46" s="113"/>
+      <c r="AE46" s="113"/>
+      <c r="AF46" s="114"/>
     </row>
     <row r="47" spans="1:37" s="72" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="122"/>
-      <c r="B47" s="307"/>
-      <c r="C47" s="308"/>
-      <c r="D47" s="308"/>
-      <c r="E47" s="308"/>
-      <c r="F47" s="308"/>
-      <c r="G47" s="318" t="s">
-        <v>39</v>
-      </c>
-      <c r="H47" s="319"/>
-      <c r="I47" s="319"/>
-      <c r="J47" s="319"/>
-      <c r="K47" s="319"/>
-      <c r="L47" s="319"/>
-      <c r="M47" s="319"/>
-      <c r="N47" s="319"/>
-      <c r="O47" s="319"/>
-      <c r="P47" s="319"/>
-      <c r="Q47" s="319"/>
-      <c r="R47" s="319"/>
-      <c r="S47" s="319"/>
-      <c r="T47" s="319"/>
-      <c r="U47" s="319"/>
-      <c r="V47" s="319"/>
-      <c r="W47" s="319"/>
-      <c r="X47" s="319"/>
-      <c r="Y47" s="319"/>
-      <c r="Z47" s="319"/>
-      <c r="AA47" s="319"/>
-      <c r="AB47" s="319"/>
-      <c r="AC47" s="319"/>
-      <c r="AD47" s="319"/>
-      <c r="AE47" s="319"/>
-      <c r="AF47" s="320"/>
+      <c r="A47" s="260"/>
+      <c r="B47" s="110"/>
+      <c r="C47" s="111"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="111"/>
+      <c r="F47" s="111"/>
+      <c r="G47" s="261" t="s">
+        <v>36</v>
+      </c>
+      <c r="H47" s="262"/>
+      <c r="I47" s="262"/>
+      <c r="J47" s="262"/>
+      <c r="K47" s="262"/>
+      <c r="L47" s="262"/>
+      <c r="M47" s="262"/>
+      <c r="N47" s="262"/>
+      <c r="O47" s="262"/>
+      <c r="P47" s="262"/>
+      <c r="Q47" s="262"/>
+      <c r="R47" s="262"/>
+      <c r="S47" s="262"/>
+      <c r="T47" s="262"/>
+      <c r="U47" s="262"/>
+      <c r="V47" s="262"/>
+      <c r="W47" s="262"/>
+      <c r="X47" s="262"/>
+      <c r="Y47" s="262"/>
+      <c r="Z47" s="262"/>
+      <c r="AA47" s="262"/>
+      <c r="AB47" s="262"/>
+      <c r="AC47" s="262"/>
+      <c r="AD47" s="262"/>
+      <c r="AE47" s="262"/>
+      <c r="AF47" s="263"/>
       <c r="AJ47" s="73"/>
     </row>
     <row r="48" spans="1:37" s="3" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -5376,305 +5313,305 @@
       <c r="D49" s="77"/>
       <c r="E49" s="77"/>
       <c r="F49" s="78"/>
-      <c r="G49" s="84" t="s">
-        <v>60</v>
-      </c>
-      <c r="H49" s="85"/>
-      <c r="I49" s="85"/>
-      <c r="J49" s="85"/>
-      <c r="K49" s="85"/>
-      <c r="L49" s="85"/>
-      <c r="M49" s="85"/>
-      <c r="N49" s="85"/>
-      <c r="O49" s="85"/>
-      <c r="P49" s="85"/>
-      <c r="Q49" s="85"/>
-      <c r="R49" s="85"/>
-      <c r="S49" s="85"/>
-      <c r="T49" s="85"/>
-      <c r="U49" s="85"/>
-      <c r="V49" s="85"/>
-      <c r="W49" s="85"/>
-      <c r="X49" s="85"/>
-      <c r="Y49" s="85"/>
-      <c r="Z49" s="85"/>
-      <c r="AA49" s="85"/>
-      <c r="AB49" s="85"/>
-      <c r="AC49" s="85"/>
-      <c r="AD49" s="85"/>
-      <c r="AE49" s="85"/>
-      <c r="AF49" s="86"/>
+      <c r="G49" s="277" t="s">
+        <v>57</v>
+      </c>
+      <c r="H49" s="278"/>
+      <c r="I49" s="278"/>
+      <c r="J49" s="278"/>
+      <c r="K49" s="278"/>
+      <c r="L49" s="278"/>
+      <c r="M49" s="278"/>
+      <c r="N49" s="278"/>
+      <c r="O49" s="278"/>
+      <c r="P49" s="278"/>
+      <c r="Q49" s="278"/>
+      <c r="R49" s="278"/>
+      <c r="S49" s="278"/>
+      <c r="T49" s="278"/>
+      <c r="U49" s="278"/>
+      <c r="V49" s="278"/>
+      <c r="W49" s="278"/>
+      <c r="X49" s="278"/>
+      <c r="Y49" s="278"/>
+      <c r="Z49" s="278"/>
+      <c r="AA49" s="278"/>
+      <c r="AB49" s="278"/>
+      <c r="AC49" s="278"/>
+      <c r="AD49" s="278"/>
+      <c r="AE49" s="278"/>
+      <c r="AF49" s="279"/>
       <c r="AG49" s="76"/>
     </row>
     <row r="50" spans="1:33" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="79" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="99" t="s">
-        <v>41</v>
-      </c>
-      <c r="C50" s="100"/>
-      <c r="D50" s="100"/>
-      <c r="E50" s="101"/>
+        <v>37</v>
+      </c>
+      <c r="B50" s="292" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50" s="293"/>
+      <c r="D50" s="293"/>
+      <c r="E50" s="294"/>
       <c r="F50" s="78"/>
-      <c r="G50" s="87"/>
-      <c r="H50" s="88"/>
-      <c r="I50" s="88"/>
-      <c r="J50" s="88"/>
-      <c r="K50" s="88"/>
-      <c r="L50" s="88"/>
-      <c r="M50" s="88"/>
-      <c r="N50" s="88"/>
-      <c r="O50" s="88"/>
-      <c r="P50" s="88"/>
-      <c r="Q50" s="88"/>
-      <c r="R50" s="88"/>
-      <c r="S50" s="88"/>
-      <c r="T50" s="88"/>
-      <c r="U50" s="88"/>
-      <c r="V50" s="88"/>
-      <c r="W50" s="88"/>
-      <c r="X50" s="88"/>
-      <c r="Y50" s="88"/>
-      <c r="Z50" s="88"/>
-      <c r="AA50" s="88"/>
-      <c r="AB50" s="88"/>
-      <c r="AC50" s="88"/>
-      <c r="AD50" s="88"/>
-      <c r="AE50" s="88"/>
-      <c r="AF50" s="89"/>
+      <c r="G50" s="280"/>
+      <c r="H50" s="281"/>
+      <c r="I50" s="281"/>
+      <c r="J50" s="281"/>
+      <c r="K50" s="281"/>
+      <c r="L50" s="281"/>
+      <c r="M50" s="281"/>
+      <c r="N50" s="281"/>
+      <c r="O50" s="281"/>
+      <c r="P50" s="281"/>
+      <c r="Q50" s="281"/>
+      <c r="R50" s="281"/>
+      <c r="S50" s="281"/>
+      <c r="T50" s="281"/>
+      <c r="U50" s="281"/>
+      <c r="V50" s="281"/>
+      <c r="W50" s="281"/>
+      <c r="X50" s="281"/>
+      <c r="Y50" s="281"/>
+      <c r="Z50" s="281"/>
+      <c r="AA50" s="281"/>
+      <c r="AB50" s="281"/>
+      <c r="AC50" s="281"/>
+      <c r="AD50" s="281"/>
+      <c r="AE50" s="281"/>
+      <c r="AF50" s="282"/>
       <c r="AG50" s="76"/>
     </row>
     <row r="51" spans="1:33" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="102" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="105" t="s">
-        <v>43</v>
-      </c>
-      <c r="C51" s="107" t="s">
-        <v>44</v>
-      </c>
-      <c r="D51" s="108"/>
-      <c r="E51" s="109"/>
+      <c r="A51" s="295" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="298" t="s">
+        <v>40</v>
+      </c>
+      <c r="C51" s="300" t="s">
+        <v>41</v>
+      </c>
+      <c r="D51" s="301"/>
+      <c r="E51" s="302"/>
       <c r="F51" s="78"/>
-      <c r="G51" s="87"/>
-      <c r="H51" s="88"/>
-      <c r="I51" s="88"/>
-      <c r="J51" s="88"/>
-      <c r="K51" s="88"/>
-      <c r="L51" s="88"/>
-      <c r="M51" s="88"/>
-      <c r="N51" s="88"/>
-      <c r="O51" s="88"/>
-      <c r="P51" s="88"/>
-      <c r="Q51" s="88"/>
-      <c r="R51" s="88"/>
-      <c r="S51" s="88"/>
-      <c r="T51" s="88"/>
-      <c r="U51" s="88"/>
-      <c r="V51" s="88"/>
-      <c r="W51" s="88"/>
-      <c r="X51" s="88"/>
-      <c r="Y51" s="88"/>
-      <c r="Z51" s="88"/>
-      <c r="AA51" s="88"/>
-      <c r="AB51" s="88"/>
-      <c r="AC51" s="88"/>
-      <c r="AD51" s="88"/>
-      <c r="AE51" s="88"/>
-      <c r="AF51" s="89"/>
+      <c r="G51" s="280"/>
+      <c r="H51" s="281"/>
+      <c r="I51" s="281"/>
+      <c r="J51" s="281"/>
+      <c r="K51" s="281"/>
+      <c r="L51" s="281"/>
+      <c r="M51" s="281"/>
+      <c r="N51" s="281"/>
+      <c r="O51" s="281"/>
+      <c r="P51" s="281"/>
+      <c r="Q51" s="281"/>
+      <c r="R51" s="281"/>
+      <c r="S51" s="281"/>
+      <c r="T51" s="281"/>
+      <c r="U51" s="281"/>
+      <c r="V51" s="281"/>
+      <c r="W51" s="281"/>
+      <c r="X51" s="281"/>
+      <c r="Y51" s="281"/>
+      <c r="Z51" s="281"/>
+      <c r="AA51" s="281"/>
+      <c r="AB51" s="281"/>
+      <c r="AC51" s="281"/>
+      <c r="AD51" s="281"/>
+      <c r="AE51" s="281"/>
+      <c r="AF51" s="282"/>
       <c r="AG51" s="76"/>
     </row>
     <row r="52" spans="1:33" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="103"/>
-      <c r="B52" s="106"/>
-      <c r="C52" s="110"/>
-      <c r="D52" s="111"/>
-      <c r="E52" s="112"/>
+      <c r="A52" s="296"/>
+      <c r="B52" s="299"/>
+      <c r="C52" s="303"/>
+      <c r="D52" s="304"/>
+      <c r="E52" s="305"/>
       <c r="F52" s="78"/>
-      <c r="G52" s="87"/>
-      <c r="H52" s="88"/>
-      <c r="I52" s="88"/>
-      <c r="J52" s="88"/>
-      <c r="K52" s="88"/>
-      <c r="L52" s="88"/>
-      <c r="M52" s="88"/>
-      <c r="N52" s="88"/>
-      <c r="O52" s="88"/>
-      <c r="P52" s="88"/>
-      <c r="Q52" s="88"/>
-      <c r="R52" s="88"/>
-      <c r="S52" s="88"/>
-      <c r="T52" s="88"/>
-      <c r="U52" s="88"/>
-      <c r="V52" s="88"/>
-      <c r="W52" s="88"/>
-      <c r="X52" s="88"/>
-      <c r="Y52" s="88"/>
-      <c r="Z52" s="88"/>
-      <c r="AA52" s="88"/>
-      <c r="AB52" s="88"/>
-      <c r="AC52" s="88"/>
-      <c r="AD52" s="88"/>
-      <c r="AE52" s="88"/>
-      <c r="AF52" s="89"/>
+      <c r="G52" s="280"/>
+      <c r="H52" s="281"/>
+      <c r="I52" s="281"/>
+      <c r="J52" s="281"/>
+      <c r="K52" s="281"/>
+      <c r="L52" s="281"/>
+      <c r="M52" s="281"/>
+      <c r="N52" s="281"/>
+      <c r="O52" s="281"/>
+      <c r="P52" s="281"/>
+      <c r="Q52" s="281"/>
+      <c r="R52" s="281"/>
+      <c r="S52" s="281"/>
+      <c r="T52" s="281"/>
+      <c r="U52" s="281"/>
+      <c r="V52" s="281"/>
+      <c r="W52" s="281"/>
+      <c r="X52" s="281"/>
+      <c r="Y52" s="281"/>
+      <c r="Z52" s="281"/>
+      <c r="AA52" s="281"/>
+      <c r="AB52" s="281"/>
+      <c r="AC52" s="281"/>
+      <c r="AD52" s="281"/>
+      <c r="AE52" s="281"/>
+      <c r="AF52" s="282"/>
       <c r="AG52" s="76"/>
     </row>
     <row r="53" spans="1:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="103"/>
-      <c r="B53" s="105" t="s">
-        <v>45</v>
-      </c>
-      <c r="C53" s="107" t="s">
-        <v>46</v>
-      </c>
-      <c r="D53" s="108"/>
-      <c r="E53" s="109"/>
+      <c r="A53" s="296"/>
+      <c r="B53" s="298" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="300" t="s">
+        <v>43</v>
+      </c>
+      <c r="D53" s="301"/>
+      <c r="E53" s="302"/>
       <c r="F53" s="78"/>
-      <c r="G53" s="87"/>
-      <c r="H53" s="88"/>
-      <c r="I53" s="88"/>
-      <c r="J53" s="88"/>
-      <c r="K53" s="88"/>
-      <c r="L53" s="88"/>
-      <c r="M53" s="88"/>
-      <c r="N53" s="88"/>
-      <c r="O53" s="88"/>
-      <c r="P53" s="88"/>
-      <c r="Q53" s="88"/>
-      <c r="R53" s="88"/>
-      <c r="S53" s="88"/>
-      <c r="T53" s="88"/>
-      <c r="U53" s="88"/>
-      <c r="V53" s="88"/>
-      <c r="W53" s="88"/>
-      <c r="X53" s="88"/>
-      <c r="Y53" s="88"/>
-      <c r="Z53" s="88"/>
-      <c r="AA53" s="88"/>
-      <c r="AB53" s="88"/>
-      <c r="AC53" s="88"/>
-      <c r="AD53" s="88"/>
-      <c r="AE53" s="88"/>
-      <c r="AF53" s="89"/>
+      <c r="G53" s="280"/>
+      <c r="H53" s="281"/>
+      <c r="I53" s="281"/>
+      <c r="J53" s="281"/>
+      <c r="K53" s="281"/>
+      <c r="L53" s="281"/>
+      <c r="M53" s="281"/>
+      <c r="N53" s="281"/>
+      <c r="O53" s="281"/>
+      <c r="P53" s="281"/>
+      <c r="Q53" s="281"/>
+      <c r="R53" s="281"/>
+      <c r="S53" s="281"/>
+      <c r="T53" s="281"/>
+      <c r="U53" s="281"/>
+      <c r="V53" s="281"/>
+      <c r="W53" s="281"/>
+      <c r="X53" s="281"/>
+      <c r="Y53" s="281"/>
+      <c r="Z53" s="281"/>
+      <c r="AA53" s="281"/>
+      <c r="AB53" s="281"/>
+      <c r="AC53" s="281"/>
+      <c r="AD53" s="281"/>
+      <c r="AE53" s="281"/>
+      <c r="AF53" s="282"/>
       <c r="AG53" s="76"/>
     </row>
     <row r="54" spans="1:33" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="103"/>
-      <c r="B54" s="113"/>
-      <c r="C54" s="110"/>
-      <c r="D54" s="111"/>
-      <c r="E54" s="112"/>
+      <c r="A54" s="296"/>
+      <c r="B54" s="306"/>
+      <c r="C54" s="303"/>
+      <c r="D54" s="304"/>
+      <c r="E54" s="305"/>
       <c r="F54" s="78"/>
-      <c r="G54" s="90" t="s">
-        <v>50</v>
-      </c>
-      <c r="H54" s="91"/>
-      <c r="I54" s="91"/>
-      <c r="J54" s="91"/>
-      <c r="K54" s="91"/>
-      <c r="L54" s="91"/>
-      <c r="M54" s="91"/>
-      <c r="N54" s="91"/>
-      <c r="O54" s="91"/>
-      <c r="P54" s="91"/>
-      <c r="Q54" s="91"/>
-      <c r="R54" s="91"/>
-      <c r="S54" s="91"/>
-      <c r="T54" s="91"/>
-      <c r="U54" s="91"/>
-      <c r="V54" s="91"/>
-      <c r="W54" s="91"/>
-      <c r="X54" s="91"/>
-      <c r="Y54" s="91"/>
-      <c r="Z54" s="91"/>
-      <c r="AA54" s="91"/>
-      <c r="AB54" s="91"/>
-      <c r="AC54" s="91"/>
-      <c r="AD54" s="91"/>
-      <c r="AE54" s="91"/>
-      <c r="AF54" s="92"/>
+      <c r="G54" s="283" t="s">
+        <v>47</v>
+      </c>
+      <c r="H54" s="284"/>
+      <c r="I54" s="284"/>
+      <c r="J54" s="284"/>
+      <c r="K54" s="284"/>
+      <c r="L54" s="284"/>
+      <c r="M54" s="284"/>
+      <c r="N54" s="284"/>
+      <c r="O54" s="284"/>
+      <c r="P54" s="284"/>
+      <c r="Q54" s="284"/>
+      <c r="R54" s="284"/>
+      <c r="S54" s="284"/>
+      <c r="T54" s="284"/>
+      <c r="U54" s="284"/>
+      <c r="V54" s="284"/>
+      <c r="W54" s="284"/>
+      <c r="X54" s="284"/>
+      <c r="Y54" s="284"/>
+      <c r="Z54" s="284"/>
+      <c r="AA54" s="284"/>
+      <c r="AB54" s="284"/>
+      <c r="AC54" s="284"/>
+      <c r="AD54" s="284"/>
+      <c r="AE54" s="284"/>
+      <c r="AF54" s="285"/>
       <c r="AG54" s="76"/>
     </row>
     <row r="55" spans="1:33" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="103"/>
-      <c r="B55" s="114" t="s">
-        <v>47</v>
-      </c>
-      <c r="C55" s="116" t="s">
-        <v>48</v>
-      </c>
-      <c r="D55" s="117"/>
-      <c r="E55" s="118"/>
+      <c r="A55" s="296"/>
+      <c r="B55" s="307" t="s">
+        <v>44</v>
+      </c>
+      <c r="C55" s="309" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" s="310"/>
+      <c r="E55" s="311"/>
       <c r="F55" s="78"/>
-      <c r="G55" s="93"/>
-      <c r="H55" s="94"/>
-      <c r="I55" s="94"/>
-      <c r="J55" s="94"/>
-      <c r="K55" s="94"/>
-      <c r="L55" s="94"/>
-      <c r="M55" s="94"/>
-      <c r="N55" s="94"/>
-      <c r="O55" s="94"/>
-      <c r="P55" s="94"/>
-      <c r="Q55" s="94"/>
-      <c r="R55" s="94"/>
-      <c r="S55" s="94"/>
-      <c r="T55" s="94"/>
-      <c r="U55" s="94"/>
-      <c r="V55" s="94"/>
-      <c r="W55" s="94"/>
-      <c r="X55" s="94"/>
-      <c r="Y55" s="94"/>
-      <c r="Z55" s="94"/>
-      <c r="AA55" s="94"/>
-      <c r="AB55" s="94"/>
-      <c r="AC55" s="94"/>
-      <c r="AD55" s="94"/>
-      <c r="AE55" s="94"/>
-      <c r="AF55" s="95"/>
+      <c r="G55" s="286"/>
+      <c r="H55" s="287"/>
+      <c r="I55" s="287"/>
+      <c r="J55" s="287"/>
+      <c r="K55" s="287"/>
+      <c r="L55" s="287"/>
+      <c r="M55" s="287"/>
+      <c r="N55" s="287"/>
+      <c r="O55" s="287"/>
+      <c r="P55" s="287"/>
+      <c r="Q55" s="287"/>
+      <c r="R55" s="287"/>
+      <c r="S55" s="287"/>
+      <c r="T55" s="287"/>
+      <c r="U55" s="287"/>
+      <c r="V55" s="287"/>
+      <c r="W55" s="287"/>
+      <c r="X55" s="287"/>
+      <c r="Y55" s="287"/>
+      <c r="Z55" s="287"/>
+      <c r="AA55" s="287"/>
+      <c r="AB55" s="287"/>
+      <c r="AC55" s="287"/>
+      <c r="AD55" s="287"/>
+      <c r="AE55" s="287"/>
+      <c r="AF55" s="288"/>
       <c r="AG55" s="76"/>
     </row>
     <row r="56" spans="1:33" ht="30.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="104"/>
-      <c r="B56" s="115"/>
-      <c r="C56" s="110"/>
-      <c r="D56" s="111"/>
-      <c r="E56" s="112"/>
+      <c r="A56" s="297"/>
+      <c r="B56" s="308"/>
+      <c r="C56" s="303"/>
+      <c r="D56" s="304"/>
+      <c r="E56" s="305"/>
       <c r="F56" s="80"/>
-      <c r="G56" s="96" t="s">
-        <v>51</v>
-      </c>
-      <c r="H56" s="97"/>
-      <c r="I56" s="97"/>
-      <c r="J56" s="97"/>
-      <c r="K56" s="97"/>
-      <c r="L56" s="97"/>
-      <c r="M56" s="97"/>
-      <c r="N56" s="97"/>
-      <c r="O56" s="97"/>
-      <c r="P56" s="97"/>
-      <c r="Q56" s="97"/>
-      <c r="R56" s="97"/>
-      <c r="S56" s="97"/>
-      <c r="T56" s="97"/>
-      <c r="U56" s="97"/>
-      <c r="V56" s="97"/>
-      <c r="W56" s="97"/>
-      <c r="X56" s="97"/>
-      <c r="Y56" s="97"/>
-      <c r="Z56" s="97"/>
-      <c r="AA56" s="97"/>
-      <c r="AB56" s="97"/>
-      <c r="AC56" s="97"/>
-      <c r="AD56" s="97"/>
-      <c r="AE56" s="97"/>
-      <c r="AF56" s="98"/>
+      <c r="G56" s="289" t="s">
+        <v>48</v>
+      </c>
+      <c r="H56" s="290"/>
+      <c r="I56" s="290"/>
+      <c r="J56" s="290"/>
+      <c r="K56" s="290"/>
+      <c r="L56" s="290"/>
+      <c r="M56" s="290"/>
+      <c r="N56" s="290"/>
+      <c r="O56" s="290"/>
+      <c r="P56" s="290"/>
+      <c r="Q56" s="290"/>
+      <c r="R56" s="290"/>
+      <c r="S56" s="290"/>
+      <c r="T56" s="290"/>
+      <c r="U56" s="290"/>
+      <c r="V56" s="290"/>
+      <c r="W56" s="290"/>
+      <c r="X56" s="290"/>
+      <c r="Y56" s="290"/>
+      <c r="Z56" s="290"/>
+      <c r="AA56" s="290"/>
+      <c r="AB56" s="290"/>
+      <c r="AC56" s="290"/>
+      <c r="AD56" s="290"/>
+      <c r="AE56" s="290"/>
+      <c r="AF56" s="291"/>
     </row>
     <row r="57" spans="1:33" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="81" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B57" s="82"/>
       <c r="C57" s="82"/>
@@ -5698,69 +5635,27 @@
       <c r="AF57" s="82"/>
     </row>
   </sheetData>
-  <mergeCells count="111">
-    <mergeCell ref="B42:F43"/>
-    <mergeCell ref="G42:P43"/>
-    <mergeCell ref="Q42:AF42"/>
-    <mergeCell ref="U43:AF43"/>
-    <mergeCell ref="B46:F47"/>
-    <mergeCell ref="G46:AF46"/>
-    <mergeCell ref="T35:AF35"/>
-    <mergeCell ref="B37:F38"/>
-    <mergeCell ref="G37:AF37"/>
-    <mergeCell ref="G40:P41"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="S41:W41"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="I34:N34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="I35:N35"/>
-    <mergeCell ref="O35:S35"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="S31:Y31"/>
-    <mergeCell ref="B32:F33"/>
-    <mergeCell ref="G32:N33"/>
-    <mergeCell ref="O32:AF32"/>
-    <mergeCell ref="T33:V33"/>
-    <mergeCell ref="W33:AF33"/>
-    <mergeCell ref="B28:F29"/>
-    <mergeCell ref="G28:AF28"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="J23:Q23"/>
-    <mergeCell ref="T23:AF23"/>
-    <mergeCell ref="G24:AF25"/>
-    <mergeCell ref="M26:U26"/>
-    <mergeCell ref="AA26:AF26"/>
-    <mergeCell ref="O27:U27"/>
-    <mergeCell ref="Y27:AF27"/>
-    <mergeCell ref="H19:L19"/>
-    <mergeCell ref="O19:AF19"/>
-    <mergeCell ref="G20:T21"/>
-    <mergeCell ref="U21:X21"/>
-    <mergeCell ref="Y21:AF21"/>
-    <mergeCell ref="G16:P16"/>
-    <mergeCell ref="T9:W10"/>
-    <mergeCell ref="X9:AF10"/>
-    <mergeCell ref="G8:S8"/>
-    <mergeCell ref="G9:S10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="A8:C12"/>
-    <mergeCell ref="X7:AF8"/>
-    <mergeCell ref="T7:W8"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="G14:P14"/>
-    <mergeCell ref="Q14:V14"/>
-    <mergeCell ref="W14:AF14"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="X12:AF12"/>
-    <mergeCell ref="G13:AF13"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:M11"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:R12"/>
+  <mergeCells count="110">
+    <mergeCell ref="G49:AF53"/>
+    <mergeCell ref="G54:AF55"/>
+    <mergeCell ref="G56:AF56"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="A51:A56"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:E52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:E54"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:E56"/>
+    <mergeCell ref="A40:A47"/>
+    <mergeCell ref="B40:F41"/>
+    <mergeCell ref="G47:AF47"/>
+    <mergeCell ref="A31:A38"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="G36:AF36"/>
+    <mergeCell ref="B31:F31"/>
     <mergeCell ref="AD1:AF2"/>
     <mergeCell ref="C3:X4"/>
     <mergeCell ref="A13:F13"/>
@@ -5781,35 +5676,76 @@
     <mergeCell ref="U17:AF17"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="Q18:T18"/>
-    <mergeCell ref="U18:X18"/>
-    <mergeCell ref="Y18:AF18"/>
     <mergeCell ref="G17:P17"/>
     <mergeCell ref="G18:P18"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="A8:C12"/>
+    <mergeCell ref="X7:AF8"/>
+    <mergeCell ref="T7:W8"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="G14:P14"/>
+    <mergeCell ref="Q14:V14"/>
+    <mergeCell ref="W14:AF14"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="X12:AF12"/>
+    <mergeCell ref="G13:AF13"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:M11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:R12"/>
+    <mergeCell ref="H19:L19"/>
+    <mergeCell ref="O19:AF19"/>
+    <mergeCell ref="G20:T21"/>
+    <mergeCell ref="U21:X21"/>
+    <mergeCell ref="Y21:AF21"/>
+    <mergeCell ref="G16:P16"/>
+    <mergeCell ref="T9:W10"/>
+    <mergeCell ref="X9:AF10"/>
+    <mergeCell ref="G8:S8"/>
+    <mergeCell ref="G9:S10"/>
+    <mergeCell ref="U18:AF18"/>
+    <mergeCell ref="B28:F29"/>
+    <mergeCell ref="G28:AF28"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="J23:Q23"/>
+    <mergeCell ref="T23:AF23"/>
+    <mergeCell ref="G24:AF25"/>
+    <mergeCell ref="M26:U26"/>
+    <mergeCell ref="AA26:AF26"/>
+    <mergeCell ref="O27:U27"/>
+    <mergeCell ref="Y27:AF27"/>
     <mergeCell ref="B22:F23"/>
     <mergeCell ref="G22:I22"/>
     <mergeCell ref="J22:AF22"/>
     <mergeCell ref="G23:I23"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I34:N34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:N35"/>
+    <mergeCell ref="O35:S35"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="S31:Y31"/>
+    <mergeCell ref="B32:F33"/>
+    <mergeCell ref="G32:N33"/>
+    <mergeCell ref="O32:AF32"/>
+    <mergeCell ref="T33:V33"/>
+    <mergeCell ref="W33:AF33"/>
+    <mergeCell ref="B42:F43"/>
+    <mergeCell ref="G42:P43"/>
+    <mergeCell ref="Q42:AF42"/>
+    <mergeCell ref="U43:AF43"/>
+    <mergeCell ref="B46:F47"/>
+    <mergeCell ref="G46:AF46"/>
+    <mergeCell ref="T35:AF35"/>
+    <mergeCell ref="B37:F38"/>
+    <mergeCell ref="G37:AF37"/>
+    <mergeCell ref="G40:P41"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="S41:W41"/>
     <mergeCell ref="G38:AF38"/>
-    <mergeCell ref="A40:A47"/>
-    <mergeCell ref="B40:F41"/>
-    <mergeCell ref="G47:AF47"/>
-    <mergeCell ref="A31:A38"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="G36:AF36"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="G49:AF53"/>
-    <mergeCell ref="G54:AF55"/>
-    <mergeCell ref="G56:AF56"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="A51:A56"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:E52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:E54"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:E56"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/templates/forms/LTC_Certification_Change_R8.4-.xlsx
+++ b/templates/forms/LTC_Certification_Change_R8.4-.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CareManagementTool\templates\forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB2FE2E-FD93-4500-8B44-B16558DF33F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8D6C8A-A091-4453-96DE-FDDC9866047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2380,6 +2380,258 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2398,23 +2650,332 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -2422,19 +2983,31 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2461,9 +3034,6 @@
     <xf numFmtId="177" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2476,399 +3046,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -2878,191 +3055,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -3519,9 +3519,9 @@
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
-      <c r="AD1" s="213"/>
-      <c r="AE1" s="213"/>
-      <c r="AF1" s="213"/>
+      <c r="AD1" s="150"/>
+      <c r="AE1" s="150"/>
+      <c r="AF1" s="150"/>
     </row>
     <row r="2" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
@@ -3548,62 +3548,62 @@
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
-      <c r="AD2" s="213"/>
-      <c r="AE2" s="213"/>
-      <c r="AF2" s="213"/>
+      <c r="AD2" s="150"/>
+      <c r="AE2" s="150"/>
+      <c r="AF2" s="150"/>
     </row>
     <row r="3" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C3" s="214" t="s">
+      <c r="C3" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="214"/>
-      <c r="E3" s="214"/>
-      <c r="F3" s="214"/>
-      <c r="G3" s="214"/>
-      <c r="H3" s="214"/>
-      <c r="I3" s="214"/>
-      <c r="J3" s="214"/>
-      <c r="K3" s="214"/>
-      <c r="L3" s="214"/>
-      <c r="M3" s="214"/>
-      <c r="N3" s="214"/>
-      <c r="O3" s="214"/>
-      <c r="P3" s="214"/>
-      <c r="Q3" s="214"/>
-      <c r="R3" s="214"/>
-      <c r="S3" s="214"/>
-      <c r="T3" s="214"/>
-      <c r="U3" s="214"/>
-      <c r="V3" s="214"/>
-      <c r="W3" s="214"/>
-      <c r="X3" s="214"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="151"/>
+      <c r="G3" s="151"/>
+      <c r="H3" s="151"/>
+      <c r="I3" s="151"/>
+      <c r="J3" s="151"/>
+      <c r="K3" s="151"/>
+      <c r="L3" s="151"/>
+      <c r="M3" s="151"/>
+      <c r="N3" s="151"/>
+      <c r="O3" s="151"/>
+      <c r="P3" s="151"/>
+      <c r="Q3" s="151"/>
+      <c r="R3" s="151"/>
+      <c r="S3" s="151"/>
+      <c r="T3" s="151"/>
+      <c r="U3" s="151"/>
+      <c r="V3" s="151"/>
+      <c r="W3" s="151"/>
+      <c r="X3" s="151"/>
       <c r="AD3" s="5"/>
       <c r="AE3" s="5"/>
       <c r="AF3" s="5"/>
     </row>
     <row r="4" spans="1:37" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C4" s="214"/>
-      <c r="D4" s="214"/>
-      <c r="E4" s="214"/>
-      <c r="F4" s="214"/>
-      <c r="G4" s="214"/>
-      <c r="H4" s="214"/>
-      <c r="I4" s="214"/>
-      <c r="J4" s="214"/>
-      <c r="K4" s="214"/>
-      <c r="L4" s="214"/>
-      <c r="M4" s="214"/>
-      <c r="N4" s="214"/>
-      <c r="O4" s="214"/>
-      <c r="P4" s="214"/>
-      <c r="Q4" s="214"/>
-      <c r="R4" s="214"/>
-      <c r="S4" s="214"/>
-      <c r="T4" s="214"/>
-      <c r="U4" s="214"/>
-      <c r="V4" s="214"/>
-      <c r="W4" s="214"/>
-      <c r="X4" s="214"/>
+      <c r="C4" s="151"/>
+      <c r="D4" s="151"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="151"/>
+      <c r="G4" s="151"/>
+      <c r="H4" s="151"/>
+      <c r="I4" s="151"/>
+      <c r="J4" s="151"/>
+      <c r="K4" s="151"/>
+      <c r="L4" s="151"/>
+      <c r="M4" s="151"/>
+      <c r="N4" s="151"/>
+      <c r="O4" s="151"/>
+      <c r="P4" s="151"/>
+      <c r="Q4" s="151"/>
+      <c r="R4" s="151"/>
+      <c r="S4" s="151"/>
+      <c r="T4" s="151"/>
+      <c r="U4" s="151"/>
+      <c r="V4" s="151"/>
+      <c r="W4" s="151"/>
+      <c r="X4" s="151"/>
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
       <c r="AC4" s="7"/>
@@ -3704,164 +3704,164 @@
       <c r="Q7" s="20"/>
       <c r="R7" s="20"/>
       <c r="S7" s="21"/>
-      <c r="T7" s="124" t="s">
+      <c r="T7" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="U7" s="124"/>
-      <c r="V7" s="124"/>
-      <c r="W7" s="125"/>
-      <c r="X7" s="191"/>
-      <c r="Y7" s="192"/>
-      <c r="Z7" s="192"/>
-      <c r="AA7" s="192"/>
-      <c r="AB7" s="192"/>
-      <c r="AC7" s="192"/>
-      <c r="AD7" s="192"/>
-      <c r="AE7" s="192"/>
-      <c r="AF7" s="193"/>
+      <c r="U7" s="216"/>
+      <c r="V7" s="216"/>
+      <c r="W7" s="217"/>
+      <c r="X7" s="210"/>
+      <c r="Y7" s="211"/>
+      <c r="Z7" s="211"/>
+      <c r="AA7" s="211"/>
+      <c r="AB7" s="211"/>
+      <c r="AC7" s="211"/>
+      <c r="AD7" s="211"/>
+      <c r="AE7" s="211"/>
+      <c r="AF7" s="212"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="83"/>
     </row>
     <row r="8" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="184" t="s">
+      <c r="A8" s="204" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="185"/>
-      <c r="C8" s="186"/>
-      <c r="D8" s="182" t="s">
+      <c r="B8" s="130"/>
+      <c r="C8" s="205"/>
+      <c r="D8" s="202" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="183"/>
-      <c r="F8" s="183"/>
-      <c r="G8" s="175"/>
-      <c r="H8" s="176"/>
-      <c r="I8" s="176"/>
-      <c r="J8" s="176"/>
-      <c r="K8" s="176"/>
-      <c r="L8" s="176"/>
-      <c r="M8" s="176"/>
-      <c r="N8" s="176"/>
-      <c r="O8" s="176"/>
-      <c r="P8" s="176"/>
-      <c r="Q8" s="176"/>
-      <c r="R8" s="176"/>
-      <c r="S8" s="177"/>
-      <c r="T8" s="101"/>
-      <c r="U8" s="101"/>
-      <c r="V8" s="101"/>
-      <c r="W8" s="102"/>
-      <c r="X8" s="194"/>
-      <c r="Y8" s="195"/>
-      <c r="Z8" s="195"/>
-      <c r="AA8" s="195"/>
-      <c r="AB8" s="195"/>
-      <c r="AC8" s="195"/>
-      <c r="AD8" s="195"/>
-      <c r="AE8" s="195"/>
-      <c r="AF8" s="196"/>
+      <c r="E8" s="203"/>
+      <c r="F8" s="203"/>
+      <c r="G8" s="243"/>
+      <c r="H8" s="244"/>
+      <c r="I8" s="244"/>
+      <c r="J8" s="244"/>
+      <c r="K8" s="244"/>
+      <c r="L8" s="244"/>
+      <c r="M8" s="244"/>
+      <c r="N8" s="244"/>
+      <c r="O8" s="244"/>
+      <c r="P8" s="244"/>
+      <c r="Q8" s="244"/>
+      <c r="R8" s="244"/>
+      <c r="S8" s="245"/>
+      <c r="T8" s="131"/>
+      <c r="U8" s="131"/>
+      <c r="V8" s="131"/>
+      <c r="W8" s="218"/>
+      <c r="X8" s="213"/>
+      <c r="Y8" s="214"/>
+      <c r="Z8" s="214"/>
+      <c r="AA8" s="214"/>
+      <c r="AB8" s="214"/>
+      <c r="AC8" s="214"/>
+      <c r="AD8" s="214"/>
+      <c r="AE8" s="214"/>
+      <c r="AF8" s="215"/>
       <c r="AI8" s="3"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="83"/>
     </row>
     <row r="9" spans="1:37" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="187"/>
-      <c r="B9" s="188"/>
-      <c r="C9" s="189"/>
-      <c r="D9" s="204" t="s">
+      <c r="A9" s="206"/>
+      <c r="B9" s="207"/>
+      <c r="C9" s="208"/>
+      <c r="D9" s="226" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="205"/>
-      <c r="F9" s="205"/>
-      <c r="G9" s="178"/>
-      <c r="H9" s="178"/>
-      <c r="I9" s="178"/>
-      <c r="J9" s="178"/>
-      <c r="K9" s="178"/>
-      <c r="L9" s="178"/>
-      <c r="M9" s="178"/>
-      <c r="N9" s="178"/>
-      <c r="O9" s="178"/>
-      <c r="P9" s="178"/>
-      <c r="Q9" s="178"/>
-      <c r="R9" s="178"/>
-      <c r="S9" s="178"/>
-      <c r="T9" s="173" t="s">
+      <c r="E9" s="227"/>
+      <c r="F9" s="227"/>
+      <c r="G9" s="246"/>
+      <c r="H9" s="246"/>
+      <c r="I9" s="246"/>
+      <c r="J9" s="246"/>
+      <c r="K9" s="246"/>
+      <c r="L9" s="246"/>
+      <c r="M9" s="246"/>
+      <c r="N9" s="246"/>
+      <c r="O9" s="246"/>
+      <c r="P9" s="246"/>
+      <c r="Q9" s="246"/>
+      <c r="R9" s="246"/>
+      <c r="S9" s="246"/>
+      <c r="T9" s="241" t="s">
         <v>8</v>
       </c>
-      <c r="U9" s="173"/>
-      <c r="V9" s="173"/>
-      <c r="W9" s="173"/>
-      <c r="X9" s="174"/>
-      <c r="Y9" s="174"/>
-      <c r="Z9" s="174"/>
-      <c r="AA9" s="174"/>
-      <c r="AB9" s="174"/>
-      <c r="AC9" s="174"/>
-      <c r="AD9" s="174"/>
-      <c r="AE9" s="174"/>
-      <c r="AF9" s="174"/>
+      <c r="U9" s="241"/>
+      <c r="V9" s="241"/>
+      <c r="W9" s="241"/>
+      <c r="X9" s="242"/>
+      <c r="Y9" s="242"/>
+      <c r="Z9" s="242"/>
+      <c r="AA9" s="242"/>
+      <c r="AB9" s="242"/>
+      <c r="AC9" s="242"/>
+      <c r="AD9" s="242"/>
+      <c r="AE9" s="242"/>
+      <c r="AF9" s="242"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="22"/>
       <c r="AK9" s="22"/>
     </row>
     <row r="10" spans="1:37" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="187"/>
-      <c r="B10" s="188"/>
-      <c r="C10" s="189"/>
-      <c r="D10" s="179" t="s">
+      <c r="A10" s="206"/>
+      <c r="B10" s="207"/>
+      <c r="C10" s="208"/>
+      <c r="D10" s="199" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="180"/>
-      <c r="F10" s="181"/>
-      <c r="G10" s="178"/>
-      <c r="H10" s="178"/>
-      <c r="I10" s="178"/>
-      <c r="J10" s="178"/>
-      <c r="K10" s="178"/>
-      <c r="L10" s="178"/>
-      <c r="M10" s="178"/>
-      <c r="N10" s="178"/>
-      <c r="O10" s="178"/>
-      <c r="P10" s="178"/>
-      <c r="Q10" s="178"/>
-      <c r="R10" s="178"/>
-      <c r="S10" s="178"/>
-      <c r="T10" s="173"/>
-      <c r="U10" s="173"/>
-      <c r="V10" s="173"/>
-      <c r="W10" s="173"/>
-      <c r="X10" s="174"/>
-      <c r="Y10" s="174"/>
-      <c r="Z10" s="174"/>
-      <c r="AA10" s="174"/>
-      <c r="AB10" s="174"/>
-      <c r="AC10" s="174"/>
-      <c r="AD10" s="174"/>
-      <c r="AE10" s="174"/>
-      <c r="AF10" s="174"/>
+      <c r="E10" s="200"/>
+      <c r="F10" s="201"/>
+      <c r="G10" s="246"/>
+      <c r="H10" s="246"/>
+      <c r="I10" s="246"/>
+      <c r="J10" s="246"/>
+      <c r="K10" s="246"/>
+      <c r="L10" s="246"/>
+      <c r="M10" s="246"/>
+      <c r="N10" s="246"/>
+      <c r="O10" s="246"/>
+      <c r="P10" s="246"/>
+      <c r="Q10" s="246"/>
+      <c r="R10" s="246"/>
+      <c r="S10" s="246"/>
+      <c r="T10" s="241"/>
+      <c r="U10" s="241"/>
+      <c r="V10" s="241"/>
+      <c r="W10" s="241"/>
+      <c r="X10" s="242"/>
+      <c r="Y10" s="242"/>
+      <c r="Z10" s="242"/>
+      <c r="AA10" s="242"/>
+      <c r="AB10" s="242"/>
+      <c r="AC10" s="242"/>
+      <c r="AD10" s="242"/>
+      <c r="AE10" s="242"/>
+      <c r="AF10" s="242"/>
       <c r="AI10" s="3"/>
       <c r="AJ10" s="22"/>
       <c r="AK10" s="22"/>
     </row>
     <row r="11" spans="1:37" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="187"/>
-      <c r="B11" s="188"/>
-      <c r="C11" s="189"/>
-      <c r="D11" s="204" t="s">
+      <c r="A11" s="206"/>
+      <c r="B11" s="207"/>
+      <c r="C11" s="208"/>
+      <c r="D11" s="226" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="209"/>
-      <c r="F11" s="210"/>
-      <c r="G11" s="97" t="s">
+      <c r="E11" s="229"/>
+      <c r="F11" s="230"/>
+      <c r="G11" s="231" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98"/>
-      <c r="K11" s="98"/>
-      <c r="L11" s="98"/>
-      <c r="M11" s="98"/>
+      <c r="H11" s="232"/>
+      <c r="I11" s="232"/>
+      <c r="J11" s="232"/>
+      <c r="K11" s="232"/>
+      <c r="L11" s="232"/>
+      <c r="M11" s="232"/>
       <c r="N11" s="36" t="s">
         <v>62</v>
       </c>
@@ -3886,26 +3886,26 @@
       <c r="AK11" s="22"/>
     </row>
     <row r="12" spans="1:37" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="190"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="179" t="s">
+      <c r="A12" s="209"/>
+      <c r="B12" s="179"/>
+      <c r="C12" s="180"/>
+      <c r="D12" s="199" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="211"/>
-      <c r="F12" s="212"/>
-      <c r="G12" s="100"/>
-      <c r="H12" s="101"/>
-      <c r="I12" s="101"/>
-      <c r="J12" s="101"/>
-      <c r="K12" s="101"/>
-      <c r="L12" s="101"/>
-      <c r="M12" s="101"/>
-      <c r="N12" s="101"/>
-      <c r="O12" s="101"/>
-      <c r="P12" s="101"/>
-      <c r="Q12" s="101"/>
-      <c r="R12" s="101"/>
+      <c r="E12" s="233"/>
+      <c r="F12" s="234"/>
+      <c r="G12" s="235"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="131"/>
+      <c r="J12" s="131"/>
+      <c r="K12" s="131"/>
+      <c r="L12" s="131"/>
+      <c r="M12" s="131"/>
+      <c r="N12" s="131"/>
+      <c r="O12" s="131"/>
+      <c r="P12" s="131"/>
+      <c r="Q12" s="131"/>
+      <c r="R12" s="131"/>
       <c r="S12" s="74"/>
       <c r="T12" s="74"/>
       <c r="U12" s="74" t="s">
@@ -3913,92 +3913,92 @@
       </c>
       <c r="V12" s="74"/>
       <c r="W12" s="74"/>
-      <c r="X12" s="101"/>
-      <c r="Y12" s="101"/>
-      <c r="Z12" s="101"/>
-      <c r="AA12" s="101"/>
-      <c r="AB12" s="101"/>
-      <c r="AC12" s="101"/>
-      <c r="AD12" s="101"/>
-      <c r="AE12" s="101"/>
-      <c r="AF12" s="169"/>
+      <c r="X12" s="131"/>
+      <c r="Y12" s="131"/>
+      <c r="Z12" s="131"/>
+      <c r="AA12" s="131"/>
+      <c r="AB12" s="131"/>
+      <c r="AC12" s="131"/>
+      <c r="AD12" s="131"/>
+      <c r="AE12" s="131"/>
+      <c r="AF12" s="228"/>
       <c r="AK12" s="22"/>
     </row>
     <row r="13" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="215" t="s">
+      <c r="A13" s="152" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="216"/>
-      <c r="C13" s="216"/>
-      <c r="D13" s="216"/>
-      <c r="E13" s="216"/>
-      <c r="F13" s="217"/>
-      <c r="G13" s="206" t="s">
+      <c r="B13" s="153"/>
+      <c r="C13" s="153"/>
+      <c r="D13" s="153"/>
+      <c r="E13" s="153"/>
+      <c r="F13" s="154"/>
+      <c r="G13" s="316" t="s">
         <v>49</v>
       </c>
-      <c r="H13" s="207"/>
-      <c r="I13" s="207"/>
-      <c r="J13" s="207"/>
-      <c r="K13" s="207"/>
-      <c r="L13" s="207"/>
-      <c r="M13" s="207"/>
-      <c r="N13" s="207"/>
-      <c r="O13" s="207"/>
-      <c r="P13" s="207"/>
-      <c r="Q13" s="207"/>
-      <c r="R13" s="207"/>
-      <c r="S13" s="207"/>
-      <c r="T13" s="207"/>
-      <c r="U13" s="207"/>
-      <c r="V13" s="207"/>
-      <c r="W13" s="207"/>
-      <c r="X13" s="207"/>
-      <c r="Y13" s="207"/>
-      <c r="Z13" s="207"/>
-      <c r="AA13" s="207"/>
-      <c r="AB13" s="207"/>
-      <c r="AC13" s="207"/>
-      <c r="AD13" s="207"/>
-      <c r="AE13" s="207"/>
-      <c r="AF13" s="208"/>
+      <c r="H13" s="317"/>
+      <c r="I13" s="317"/>
+      <c r="J13" s="317"/>
+      <c r="K13" s="317"/>
+      <c r="L13" s="317"/>
+      <c r="M13" s="317"/>
+      <c r="N13" s="317"/>
+      <c r="O13" s="317"/>
+      <c r="P13" s="317"/>
+      <c r="Q13" s="317"/>
+      <c r="R13" s="317"/>
+      <c r="S13" s="317"/>
+      <c r="T13" s="317"/>
+      <c r="U13" s="317"/>
+      <c r="V13" s="317"/>
+      <c r="W13" s="317"/>
+      <c r="X13" s="317"/>
+      <c r="Y13" s="317"/>
+      <c r="Z13" s="317"/>
+      <c r="AA13" s="317"/>
+      <c r="AB13" s="317"/>
+      <c r="AC13" s="317"/>
+      <c r="AD13" s="317"/>
+      <c r="AE13" s="317"/>
+      <c r="AF13" s="318"/>
     </row>
     <row r="14" spans="1:37" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="197" t="s">
+      <c r="A14" s="219" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="198"/>
-      <c r="C14" s="198"/>
-      <c r="D14" s="198"/>
-      <c r="E14" s="198"/>
-      <c r="F14" s="199"/>
-      <c r="G14" s="200"/>
-      <c r="H14" s="198"/>
-      <c r="I14" s="198"/>
-      <c r="J14" s="198"/>
-      <c r="K14" s="198"/>
-      <c r="L14" s="198"/>
-      <c r="M14" s="198"/>
-      <c r="N14" s="198"/>
-      <c r="O14" s="198"/>
-      <c r="P14" s="199"/>
-      <c r="Q14" s="200" t="s">
+      <c r="B14" s="220"/>
+      <c r="C14" s="220"/>
+      <c r="D14" s="220"/>
+      <c r="E14" s="220"/>
+      <c r="F14" s="221"/>
+      <c r="G14" s="222"/>
+      <c r="H14" s="220"/>
+      <c r="I14" s="220"/>
+      <c r="J14" s="220"/>
+      <c r="K14" s="220"/>
+      <c r="L14" s="220"/>
+      <c r="M14" s="220"/>
+      <c r="N14" s="220"/>
+      <c r="O14" s="220"/>
+      <c r="P14" s="221"/>
+      <c r="Q14" s="222" t="s">
         <v>12</v>
       </c>
-      <c r="R14" s="198"/>
-      <c r="S14" s="198"/>
-      <c r="T14" s="198"/>
-      <c r="U14" s="198"/>
-      <c r="V14" s="199"/>
-      <c r="W14" s="201"/>
-      <c r="X14" s="202"/>
-      <c r="Y14" s="202"/>
-      <c r="Z14" s="202"/>
-      <c r="AA14" s="202"/>
-      <c r="AB14" s="202"/>
-      <c r="AC14" s="202"/>
-      <c r="AD14" s="202"/>
-      <c r="AE14" s="202"/>
-      <c r="AF14" s="203"/>
+      <c r="R14" s="220"/>
+      <c r="S14" s="220"/>
+      <c r="T14" s="220"/>
+      <c r="U14" s="220"/>
+      <c r="V14" s="221"/>
+      <c r="W14" s="223"/>
+      <c r="X14" s="224"/>
+      <c r="Y14" s="224"/>
+      <c r="Z14" s="224"/>
+      <c r="AA14" s="224"/>
+      <c r="AB14" s="224"/>
+      <c r="AC14" s="224"/>
+      <c r="AD14" s="224"/>
+      <c r="AE14" s="224"/>
+      <c r="AF14" s="225"/>
     </row>
     <row r="15" spans="1:37" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="19"/>
@@ -4037,32 +4037,32 @@
       <c r="AK15" s="26"/>
     </row>
     <row r="16" spans="1:37" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="221" t="s">
+      <c r="A16" s="157" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="224" t="s">
+      <c r="B16" s="160" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="225"/>
-      <c r="D16" s="225"/>
-      <c r="E16" s="225"/>
-      <c r="F16" s="226"/>
-      <c r="G16" s="170"/>
-      <c r="H16" s="171"/>
-      <c r="I16" s="171"/>
-      <c r="J16" s="171"/>
-      <c r="K16" s="171"/>
-      <c r="L16" s="171"/>
-      <c r="M16" s="171"/>
-      <c r="N16" s="171"/>
-      <c r="O16" s="171"/>
-      <c r="P16" s="172"/>
-      <c r="Q16" s="227" t="s">
+      <c r="C16" s="161"/>
+      <c r="D16" s="161"/>
+      <c r="E16" s="161"/>
+      <c r="F16" s="162"/>
+      <c r="G16" s="193"/>
+      <c r="H16" s="194"/>
+      <c r="I16" s="194"/>
+      <c r="J16" s="194"/>
+      <c r="K16" s="194"/>
+      <c r="L16" s="194"/>
+      <c r="M16" s="194"/>
+      <c r="N16" s="194"/>
+      <c r="O16" s="194"/>
+      <c r="P16" s="195"/>
+      <c r="Q16" s="163" t="s">
         <v>15</v>
       </c>
-      <c r="R16" s="228"/>
-      <c r="S16" s="228"/>
-      <c r="T16" s="229"/>
+      <c r="R16" s="164"/>
+      <c r="S16" s="164"/>
+      <c r="T16" s="165"/>
       <c r="U16" s="89"/>
       <c r="V16" s="89"/>
       <c r="W16" s="89"/>
@@ -4079,144 +4079,144 @@
       <c r="AK16" s="26"/>
     </row>
     <row r="17" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="222"/>
-      <c r="B17" s="230" t="s">
+      <c r="A17" s="158"/>
+      <c r="B17" s="166" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="231"/>
-      <c r="D17" s="231"/>
-      <c r="E17" s="231"/>
-      <c r="F17" s="232"/>
-      <c r="G17" s="155"/>
-      <c r="H17" s="156"/>
-      <c r="I17" s="156"/>
-      <c r="J17" s="156"/>
-      <c r="K17" s="156"/>
-      <c r="L17" s="156"/>
-      <c r="M17" s="156"/>
-      <c r="N17" s="156"/>
-      <c r="O17" s="156"/>
-      <c r="P17" s="251"/>
-      <c r="Q17" s="224" t="s">
+      <c r="C17" s="167"/>
+      <c r="D17" s="167"/>
+      <c r="E17" s="167"/>
+      <c r="F17" s="168"/>
+      <c r="G17" s="196"/>
+      <c r="H17" s="197"/>
+      <c r="I17" s="197"/>
+      <c r="J17" s="197"/>
+      <c r="K17" s="197"/>
+      <c r="L17" s="197"/>
+      <c r="M17" s="197"/>
+      <c r="N17" s="197"/>
+      <c r="O17" s="197"/>
+      <c r="P17" s="198"/>
+      <c r="Q17" s="160" t="s">
         <v>16</v>
       </c>
-      <c r="R17" s="225"/>
-      <c r="S17" s="225"/>
-      <c r="T17" s="226"/>
-      <c r="U17" s="170"/>
-      <c r="V17" s="171"/>
-      <c r="W17" s="171"/>
-      <c r="X17" s="171"/>
-      <c r="Y17" s="171"/>
-      <c r="Z17" s="171"/>
-      <c r="AA17" s="171"/>
-      <c r="AB17" s="171"/>
-      <c r="AC17" s="171"/>
-      <c r="AD17" s="171"/>
-      <c r="AE17" s="171"/>
-      <c r="AF17" s="172"/>
+      <c r="R17" s="161"/>
+      <c r="S17" s="161"/>
+      <c r="T17" s="162"/>
+      <c r="U17" s="193"/>
+      <c r="V17" s="194"/>
+      <c r="W17" s="194"/>
+      <c r="X17" s="194"/>
+      <c r="Y17" s="194"/>
+      <c r="Z17" s="194"/>
+      <c r="AA17" s="194"/>
+      <c r="AB17" s="194"/>
+      <c r="AC17" s="194"/>
+      <c r="AD17" s="194"/>
+      <c r="AE17" s="194"/>
+      <c r="AF17" s="195"/>
     </row>
     <row r="18" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="222"/>
-      <c r="B18" s="219" t="s">
+      <c r="A18" s="158"/>
+      <c r="B18" s="155" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="248"/>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
-      <c r="F18" s="218"/>
-      <c r="G18" s="155"/>
-      <c r="H18" s="156"/>
-      <c r="I18" s="156"/>
-      <c r="J18" s="156"/>
-      <c r="K18" s="156"/>
-      <c r="L18" s="156"/>
-      <c r="M18" s="156"/>
-      <c r="N18" s="156"/>
-      <c r="O18" s="156"/>
-      <c r="P18" s="251"/>
-      <c r="Q18" s="219" t="s">
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="143"/>
+      <c r="G18" s="196"/>
+      <c r="H18" s="197"/>
+      <c r="I18" s="197"/>
+      <c r="J18" s="197"/>
+      <c r="K18" s="197"/>
+      <c r="L18" s="197"/>
+      <c r="M18" s="197"/>
+      <c r="N18" s="197"/>
+      <c r="O18" s="197"/>
+      <c r="P18" s="198"/>
+      <c r="Q18" s="155" t="s">
         <v>17</v>
       </c>
-      <c r="R18" s="248"/>
-      <c r="S18" s="248"/>
-      <c r="T18" s="218"/>
-      <c r="U18" s="249"/>
-      <c r="V18" s="250"/>
-      <c r="W18" s="250"/>
-      <c r="X18" s="250"/>
-      <c r="Y18" s="250"/>
-      <c r="Z18" s="250"/>
-      <c r="AA18" s="250"/>
-      <c r="AB18" s="250"/>
-      <c r="AC18" s="250"/>
-      <c r="AD18" s="250"/>
-      <c r="AE18" s="250"/>
-      <c r="AF18" s="312"/>
+      <c r="R18" s="142"/>
+      <c r="S18" s="142"/>
+      <c r="T18" s="143"/>
+      <c r="U18" s="247"/>
+      <c r="V18" s="248"/>
+      <c r="W18" s="248"/>
+      <c r="X18" s="248"/>
+      <c r="Y18" s="248"/>
+      <c r="Z18" s="248"/>
+      <c r="AA18" s="248"/>
+      <c r="AB18" s="248"/>
+      <c r="AC18" s="248"/>
+      <c r="AD18" s="248"/>
+      <c r="AE18" s="248"/>
+      <c r="AF18" s="249"/>
     </row>
     <row r="19" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="222"/>
-      <c r="B19" s="218" t="s">
+      <c r="A19" s="158"/>
+      <c r="B19" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="219"/>
-      <c r="D19" s="219"/>
-      <c r="E19" s="219"/>
-      <c r="F19" s="220"/>
+      <c r="C19" s="155"/>
+      <c r="D19" s="155"/>
+      <c r="E19" s="155"/>
+      <c r="F19" s="156"/>
       <c r="G19" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="H19" s="164"/>
-      <c r="I19" s="164"/>
-      <c r="J19" s="164"/>
-      <c r="K19" s="164"/>
-      <c r="L19" s="164"/>
+      <c r="H19" s="236"/>
+      <c r="I19" s="236"/>
+      <c r="J19" s="236"/>
+      <c r="K19" s="236"/>
+      <c r="L19" s="236"/>
       <c r="M19" s="33" t="s">
         <v>65</v>
       </c>
       <c r="N19" s="24"/>
-      <c r="O19" s="165" t="s">
+      <c r="O19" s="237" t="s">
         <v>66</v>
       </c>
-      <c r="P19" s="165"/>
-      <c r="Q19" s="165"/>
-      <c r="R19" s="165"/>
-      <c r="S19" s="165"/>
-      <c r="T19" s="165"/>
-      <c r="U19" s="165"/>
-      <c r="V19" s="165"/>
-      <c r="W19" s="165"/>
-      <c r="X19" s="165"/>
-      <c r="Y19" s="165"/>
-      <c r="Z19" s="165"/>
-      <c r="AA19" s="165"/>
-      <c r="AB19" s="165"/>
-      <c r="AC19" s="165"/>
-      <c r="AD19" s="165"/>
-      <c r="AE19" s="165"/>
-      <c r="AF19" s="166"/>
+      <c r="P19" s="237"/>
+      <c r="Q19" s="237"/>
+      <c r="R19" s="237"/>
+      <c r="S19" s="237"/>
+      <c r="T19" s="237"/>
+      <c r="U19" s="237"/>
+      <c r="V19" s="237"/>
+      <c r="W19" s="237"/>
+      <c r="X19" s="237"/>
+      <c r="Y19" s="237"/>
+      <c r="Z19" s="237"/>
+      <c r="AA19" s="237"/>
+      <c r="AB19" s="237"/>
+      <c r="AC19" s="237"/>
+      <c r="AD19" s="237"/>
+      <c r="AE19" s="237"/>
+      <c r="AF19" s="238"/>
     </row>
     <row r="20" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="222"/>
-      <c r="B20" s="218"/>
-      <c r="C20" s="219"/>
-      <c r="D20" s="219"/>
-      <c r="E20" s="219"/>
-      <c r="F20" s="220"/>
-      <c r="G20" s="167"/>
-      <c r="H20" s="168"/>
-      <c r="I20" s="168"/>
-      <c r="J20" s="168"/>
-      <c r="K20" s="168"/>
-      <c r="L20" s="168"/>
-      <c r="M20" s="168"/>
-      <c r="N20" s="168"/>
-      <c r="O20" s="168"/>
-      <c r="P20" s="168"/>
-      <c r="Q20" s="168"/>
-      <c r="R20" s="168"/>
-      <c r="S20" s="168"/>
-      <c r="T20" s="168"/>
+      <c r="A20" s="158"/>
+      <c r="B20" s="143"/>
+      <c r="C20" s="155"/>
+      <c r="D20" s="155"/>
+      <c r="E20" s="155"/>
+      <c r="F20" s="156"/>
+      <c r="G20" s="239"/>
+      <c r="H20" s="240"/>
+      <c r="I20" s="240"/>
+      <c r="J20" s="240"/>
+      <c r="K20" s="240"/>
+      <c r="L20" s="240"/>
+      <c r="M20" s="240"/>
+      <c r="N20" s="240"/>
+      <c r="O20" s="240"/>
+      <c r="P20" s="240"/>
+      <c r="Q20" s="240"/>
+      <c r="R20" s="240"/>
+      <c r="S20" s="240"/>
+      <c r="T20" s="240"/>
       <c r="U20" s="34"/>
       <c r="V20" s="34"/>
       <c r="W20" s="34"/>
@@ -4230,346 +4230,346 @@
       <c r="AF20" s="27"/>
     </row>
     <row r="21" spans="1:37" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="222"/>
-      <c r="B21" s="218"/>
-      <c r="C21" s="219"/>
-      <c r="D21" s="219"/>
-      <c r="E21" s="219"/>
-      <c r="F21" s="220"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="101"/>
-      <c r="I21" s="101"/>
-      <c r="J21" s="101"/>
-      <c r="K21" s="101"/>
-      <c r="L21" s="101"/>
-      <c r="M21" s="101"/>
-      <c r="N21" s="101"/>
-      <c r="O21" s="101"/>
-      <c r="P21" s="101"/>
-      <c r="Q21" s="101"/>
-      <c r="R21" s="101"/>
-      <c r="S21" s="101"/>
-      <c r="T21" s="101"/>
-      <c r="U21" s="101" t="s">
+      <c r="A21" s="158"/>
+      <c r="B21" s="143"/>
+      <c r="C21" s="155"/>
+      <c r="D21" s="155"/>
+      <c r="E21" s="155"/>
+      <c r="F21" s="156"/>
+      <c r="G21" s="235"/>
+      <c r="H21" s="131"/>
+      <c r="I21" s="131"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="131"/>
+      <c r="L21" s="131"/>
+      <c r="M21" s="131"/>
+      <c r="N21" s="131"/>
+      <c r="O21" s="131"/>
+      <c r="P21" s="131"/>
+      <c r="Q21" s="131"/>
+      <c r="R21" s="131"/>
+      <c r="S21" s="131"/>
+      <c r="T21" s="131"/>
+      <c r="U21" s="131" t="s">
         <v>10</v>
       </c>
-      <c r="V21" s="101"/>
-      <c r="W21" s="101"/>
-      <c r="X21" s="101"/>
-      <c r="Y21" s="101"/>
-      <c r="Z21" s="101"/>
-      <c r="AA21" s="101"/>
-      <c r="AB21" s="101"/>
-      <c r="AC21" s="101"/>
-      <c r="AD21" s="101"/>
-      <c r="AE21" s="101"/>
-      <c r="AF21" s="169"/>
+      <c r="V21" s="131"/>
+      <c r="W21" s="131"/>
+      <c r="X21" s="131"/>
+      <c r="Y21" s="131"/>
+      <c r="Z21" s="131"/>
+      <c r="AA21" s="131"/>
+      <c r="AB21" s="131"/>
+      <c r="AC21" s="131"/>
+      <c r="AD21" s="131"/>
+      <c r="AE21" s="131"/>
+      <c r="AF21" s="228"/>
     </row>
     <row r="22" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="222"/>
-      <c r="B22" s="108" t="s">
+      <c r="A22" s="158"/>
+      <c r="B22" s="266" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="109"/>
-      <c r="D22" s="109"/>
-      <c r="E22" s="109"/>
-      <c r="F22" s="118"/>
-      <c r="G22" s="252" t="s">
+      <c r="C22" s="267"/>
+      <c r="D22" s="267"/>
+      <c r="E22" s="267"/>
+      <c r="F22" s="268"/>
+      <c r="G22" s="272" t="s">
         <v>19</v>
       </c>
-      <c r="H22" s="154"/>
-      <c r="I22" s="253"/>
-      <c r="J22" s="155"/>
-      <c r="K22" s="156"/>
-      <c r="L22" s="156"/>
-      <c r="M22" s="156"/>
-      <c r="N22" s="156"/>
-      <c r="O22" s="156"/>
-      <c r="P22" s="156"/>
-      <c r="Q22" s="156"/>
-      <c r="R22" s="156"/>
-      <c r="S22" s="156"/>
-      <c r="T22" s="156"/>
-      <c r="U22" s="156"/>
-      <c r="V22" s="156"/>
-      <c r="W22" s="156"/>
-      <c r="X22" s="156"/>
-      <c r="Y22" s="156"/>
-      <c r="Z22" s="156"/>
-      <c r="AA22" s="156"/>
-      <c r="AB22" s="156"/>
-      <c r="AC22" s="156"/>
-      <c r="AD22" s="156"/>
-      <c r="AE22" s="156"/>
-      <c r="AF22" s="157"/>
+      <c r="H22" s="255"/>
+      <c r="I22" s="273"/>
+      <c r="J22" s="196"/>
+      <c r="K22" s="197"/>
+      <c r="L22" s="197"/>
+      <c r="M22" s="197"/>
+      <c r="N22" s="197"/>
+      <c r="O22" s="197"/>
+      <c r="P22" s="197"/>
+      <c r="Q22" s="197"/>
+      <c r="R22" s="197"/>
+      <c r="S22" s="197"/>
+      <c r="T22" s="197"/>
+      <c r="U22" s="197"/>
+      <c r="V22" s="197"/>
+      <c r="W22" s="197"/>
+      <c r="X22" s="197"/>
+      <c r="Y22" s="197"/>
+      <c r="Z22" s="197"/>
+      <c r="AA22" s="197"/>
+      <c r="AB22" s="197"/>
+      <c r="AC22" s="197"/>
+      <c r="AD22" s="197"/>
+      <c r="AE22" s="197"/>
+      <c r="AF22" s="256"/>
     </row>
     <row r="23" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="222"/>
-      <c r="B23" s="134"/>
-      <c r="C23" s="135"/>
-      <c r="D23" s="135"/>
-      <c r="E23" s="135"/>
-      <c r="F23" s="136"/>
-      <c r="G23" s="252" t="s">
+      <c r="A23" s="158"/>
+      <c r="B23" s="269"/>
+      <c r="C23" s="270"/>
+      <c r="D23" s="270"/>
+      <c r="E23" s="270"/>
+      <c r="F23" s="271"/>
+      <c r="G23" s="272" t="s">
         <v>20</v>
       </c>
-      <c r="H23" s="154"/>
-      <c r="I23" s="253"/>
-      <c r="J23" s="155"/>
-      <c r="K23" s="156"/>
-      <c r="L23" s="156"/>
-      <c r="M23" s="156"/>
-      <c r="N23" s="156"/>
-      <c r="O23" s="156"/>
-      <c r="P23" s="156"/>
-      <c r="Q23" s="156"/>
-      <c r="R23" s="154" t="s">
+      <c r="H23" s="255"/>
+      <c r="I23" s="273"/>
+      <c r="J23" s="196"/>
+      <c r="K23" s="197"/>
+      <c r="L23" s="197"/>
+      <c r="M23" s="197"/>
+      <c r="N23" s="197"/>
+      <c r="O23" s="197"/>
+      <c r="P23" s="197"/>
+      <c r="Q23" s="197"/>
+      <c r="R23" s="255" t="s">
         <v>68</v>
       </c>
-      <c r="S23" s="154"/>
-      <c r="T23" s="156"/>
-      <c r="U23" s="156"/>
-      <c r="V23" s="156"/>
-      <c r="W23" s="156"/>
-      <c r="X23" s="156"/>
-      <c r="Y23" s="156"/>
-      <c r="Z23" s="156"/>
-      <c r="AA23" s="156"/>
-      <c r="AB23" s="156"/>
-      <c r="AC23" s="156"/>
-      <c r="AD23" s="156"/>
-      <c r="AE23" s="156"/>
-      <c r="AF23" s="157"/>
+      <c r="S23" s="255"/>
+      <c r="T23" s="197"/>
+      <c r="U23" s="197"/>
+      <c r="V23" s="197"/>
+      <c r="W23" s="197"/>
+      <c r="X23" s="197"/>
+      <c r="Y23" s="197"/>
+      <c r="Z23" s="197"/>
+      <c r="AA23" s="197"/>
+      <c r="AB23" s="197"/>
+      <c r="AC23" s="197"/>
+      <c r="AD23" s="197"/>
+      <c r="AE23" s="197"/>
+      <c r="AF23" s="256"/>
     </row>
     <row r="24" spans="1:37" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="222"/>
-      <c r="B24" s="233" t="s">
+      <c r="A24" s="158"/>
+      <c r="B24" s="169" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="234"/>
-      <c r="D24" s="234"/>
-      <c r="E24" s="234"/>
-      <c r="F24" s="235"/>
-      <c r="G24" s="313"/>
-      <c r="H24" s="314"/>
-      <c r="I24" s="314"/>
-      <c r="J24" s="314"/>
-      <c r="K24" s="314"/>
-      <c r="L24" s="314"/>
-      <c r="M24" s="314"/>
-      <c r="N24" s="314"/>
-      <c r="O24" s="314"/>
-      <c r="P24" s="314"/>
-      <c r="Q24" s="314"/>
-      <c r="R24" s="314"/>
-      <c r="S24" s="314"/>
-      <c r="T24" s="314"/>
-      <c r="U24" s="314"/>
-      <c r="V24" s="314"/>
-      <c r="W24" s="314"/>
-      <c r="X24" s="314"/>
-      <c r="Y24" s="314"/>
-      <c r="Z24" s="314"/>
-      <c r="AA24" s="314"/>
-      <c r="AB24" s="314"/>
-      <c r="AC24" s="314"/>
-      <c r="AD24" s="314"/>
-      <c r="AE24" s="314"/>
-      <c r="AF24" s="315"/>
+      <c r="C24" s="170"/>
+      <c r="D24" s="170"/>
+      <c r="E24" s="170"/>
+      <c r="F24" s="171"/>
+      <c r="G24" s="257"/>
+      <c r="H24" s="258"/>
+      <c r="I24" s="258"/>
+      <c r="J24" s="258"/>
+      <c r="K24" s="258"/>
+      <c r="L24" s="258"/>
+      <c r="M24" s="258"/>
+      <c r="N24" s="258"/>
+      <c r="O24" s="258"/>
+      <c r="P24" s="258"/>
+      <c r="Q24" s="258"/>
+      <c r="R24" s="258"/>
+      <c r="S24" s="258"/>
+      <c r="T24" s="258"/>
+      <c r="U24" s="258"/>
+      <c r="V24" s="258"/>
+      <c r="W24" s="258"/>
+      <c r="X24" s="258"/>
+      <c r="Y24" s="258"/>
+      <c r="Z24" s="258"/>
+      <c r="AA24" s="258"/>
+      <c r="AB24" s="258"/>
+      <c r="AC24" s="258"/>
+      <c r="AD24" s="258"/>
+      <c r="AE24" s="258"/>
+      <c r="AF24" s="259"/>
       <c r="AJ24" s="33"/>
     </row>
     <row r="25" spans="1:37" s="18" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="222"/>
-      <c r="B25" s="236"/>
-      <c r="C25" s="237"/>
-      <c r="D25" s="237"/>
-      <c r="E25" s="237"/>
-      <c r="F25" s="238"/>
-      <c r="G25" s="316"/>
-      <c r="H25" s="317"/>
-      <c r="I25" s="317"/>
-      <c r="J25" s="317"/>
-      <c r="K25" s="317"/>
-      <c r="L25" s="317"/>
-      <c r="M25" s="317"/>
-      <c r="N25" s="317"/>
-      <c r="O25" s="317"/>
-      <c r="P25" s="317"/>
-      <c r="Q25" s="317"/>
-      <c r="R25" s="317"/>
-      <c r="S25" s="317"/>
-      <c r="T25" s="317"/>
-      <c r="U25" s="317"/>
-      <c r="V25" s="317"/>
-      <c r="W25" s="317"/>
-      <c r="X25" s="317"/>
-      <c r="Y25" s="317"/>
-      <c r="Z25" s="317"/>
-      <c r="AA25" s="317"/>
-      <c r="AB25" s="317"/>
-      <c r="AC25" s="317"/>
-      <c r="AD25" s="317"/>
-      <c r="AE25" s="317"/>
-      <c r="AF25" s="318"/>
+      <c r="A25" s="158"/>
+      <c r="B25" s="172"/>
+      <c r="C25" s="173"/>
+      <c r="D25" s="173"/>
+      <c r="E25" s="173"/>
+      <c r="F25" s="174"/>
+      <c r="G25" s="260"/>
+      <c r="H25" s="261"/>
+      <c r="I25" s="261"/>
+      <c r="J25" s="261"/>
+      <c r="K25" s="261"/>
+      <c r="L25" s="261"/>
+      <c r="M25" s="261"/>
+      <c r="N25" s="261"/>
+      <c r="O25" s="261"/>
+      <c r="P25" s="261"/>
+      <c r="Q25" s="261"/>
+      <c r="R25" s="261"/>
+      <c r="S25" s="261"/>
+      <c r="T25" s="261"/>
+      <c r="U25" s="261"/>
+      <c r="V25" s="261"/>
+      <c r="W25" s="261"/>
+      <c r="X25" s="261"/>
+      <c r="Y25" s="261"/>
+      <c r="Z25" s="261"/>
+      <c r="AA25" s="261"/>
+      <c r="AB25" s="261"/>
+      <c r="AC25" s="261"/>
+      <c r="AD25" s="261"/>
+      <c r="AE25" s="261"/>
+      <c r="AF25" s="262"/>
       <c r="AJ25" s="33"/>
     </row>
     <row r="26" spans="1:37" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="222"/>
-      <c r="B26" s="91" t="s">
+      <c r="A26" s="158"/>
+      <c r="B26" s="175" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="92"/>
-      <c r="D26" s="92"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="93"/>
-      <c r="G26" s="239" t="s">
+      <c r="C26" s="176"/>
+      <c r="D26" s="176"/>
+      <c r="E26" s="176"/>
+      <c r="F26" s="177"/>
+      <c r="G26" s="181" t="s">
         <v>51</v>
       </c>
-      <c r="H26" s="240"/>
-      <c r="I26" s="240"/>
-      <c r="J26" s="240"/>
-      <c r="K26" s="240"/>
-      <c r="L26" s="241"/>
-      <c r="M26" s="158"/>
-      <c r="N26" s="159"/>
-      <c r="O26" s="159"/>
-      <c r="P26" s="159"/>
-      <c r="Q26" s="159"/>
-      <c r="R26" s="159"/>
-      <c r="S26" s="159"/>
-      <c r="T26" s="159"/>
-      <c r="U26" s="160"/>
-      <c r="V26" s="242" t="s">
+      <c r="H26" s="182"/>
+      <c r="I26" s="182"/>
+      <c r="J26" s="182"/>
+      <c r="K26" s="182"/>
+      <c r="L26" s="183"/>
+      <c r="M26" s="187"/>
+      <c r="N26" s="189"/>
+      <c r="O26" s="189"/>
+      <c r="P26" s="189"/>
+      <c r="Q26" s="189"/>
+      <c r="R26" s="189"/>
+      <c r="S26" s="189"/>
+      <c r="T26" s="189"/>
+      <c r="U26" s="188"/>
+      <c r="V26" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="W26" s="243"/>
-      <c r="X26" s="243"/>
-      <c r="Y26" s="243"/>
-      <c r="Z26" s="244"/>
-      <c r="AA26" s="161"/>
-      <c r="AB26" s="162"/>
-      <c r="AC26" s="162"/>
-      <c r="AD26" s="162"/>
-      <c r="AE26" s="162"/>
-      <c r="AF26" s="163"/>
+      <c r="W26" s="185"/>
+      <c r="X26" s="185"/>
+      <c r="Y26" s="185"/>
+      <c r="Z26" s="186"/>
+      <c r="AA26" s="263"/>
+      <c r="AB26" s="264"/>
+      <c r="AC26" s="264"/>
+      <c r="AD26" s="264"/>
+      <c r="AE26" s="264"/>
+      <c r="AF26" s="265"/>
       <c r="AJ26" s="33"/>
       <c r="AK26" s="18"/>
     </row>
     <row r="27" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="222"/>
-      <c r="B27" s="94"/>
-      <c r="C27" s="95"/>
-      <c r="D27" s="95"/>
-      <c r="E27" s="95"/>
-      <c r="F27" s="96"/>
-      <c r="G27" s="239" t="s">
+      <c r="A27" s="158"/>
+      <c r="B27" s="178"/>
+      <c r="C27" s="179"/>
+      <c r="D27" s="179"/>
+      <c r="E27" s="179"/>
+      <c r="F27" s="180"/>
+      <c r="G27" s="181" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="240"/>
-      <c r="I27" s="240"/>
-      <c r="J27" s="240"/>
-      <c r="K27" s="240"/>
-      <c r="L27" s="241"/>
-      <c r="M27" s="158" t="s">
+      <c r="H27" s="182"/>
+      <c r="I27" s="182"/>
+      <c r="J27" s="182"/>
+      <c r="K27" s="182"/>
+      <c r="L27" s="183"/>
+      <c r="M27" s="187" t="s">
         <v>54</v>
       </c>
-      <c r="N27" s="160"/>
-      <c r="O27" s="158"/>
-      <c r="P27" s="159"/>
-      <c r="Q27" s="159"/>
-      <c r="R27" s="159"/>
-      <c r="S27" s="159"/>
-      <c r="T27" s="159"/>
-      <c r="U27" s="160"/>
-      <c r="V27" s="158" t="s">
+      <c r="N27" s="188"/>
+      <c r="O27" s="187"/>
+      <c r="P27" s="189"/>
+      <c r="Q27" s="189"/>
+      <c r="R27" s="189"/>
+      <c r="S27" s="189"/>
+      <c r="T27" s="189"/>
+      <c r="U27" s="188"/>
+      <c r="V27" s="187" t="s">
         <v>55</v>
       </c>
-      <c r="W27" s="159"/>
-      <c r="X27" s="160"/>
-      <c r="Y27" s="161"/>
-      <c r="Z27" s="162"/>
-      <c r="AA27" s="162"/>
-      <c r="AB27" s="162"/>
-      <c r="AC27" s="162"/>
-      <c r="AD27" s="162"/>
-      <c r="AE27" s="162"/>
-      <c r="AF27" s="163"/>
+      <c r="W27" s="189"/>
+      <c r="X27" s="188"/>
+      <c r="Y27" s="263"/>
+      <c r="Z27" s="264"/>
+      <c r="AA27" s="264"/>
+      <c r="AB27" s="264"/>
+      <c r="AC27" s="264"/>
+      <c r="AD27" s="264"/>
+      <c r="AE27" s="264"/>
+      <c r="AF27" s="265"/>
       <c r="AJ27" s="33"/>
       <c r="AK27" s="18"/>
     </row>
     <row r="28" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="222"/>
-      <c r="B28" s="92" t="s">
+      <c r="A28" s="158"/>
+      <c r="B28" s="176" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="92"/>
-      <c r="D28" s="92"/>
-      <c r="E28" s="92"/>
-      <c r="F28" s="93"/>
-      <c r="G28" s="151"/>
-      <c r="H28" s="152"/>
-      <c r="I28" s="152"/>
-      <c r="J28" s="152"/>
-      <c r="K28" s="152"/>
-      <c r="L28" s="152"/>
-      <c r="M28" s="152"/>
-      <c r="N28" s="152"/>
-      <c r="O28" s="152"/>
-      <c r="P28" s="152"/>
-      <c r="Q28" s="152"/>
-      <c r="R28" s="152"/>
-      <c r="S28" s="152"/>
-      <c r="T28" s="152"/>
-      <c r="U28" s="152"/>
-      <c r="V28" s="152"/>
-      <c r="W28" s="152"/>
-      <c r="X28" s="152"/>
-      <c r="Y28" s="152"/>
-      <c r="Z28" s="152"/>
-      <c r="AA28" s="152"/>
-      <c r="AB28" s="152"/>
-      <c r="AC28" s="152"/>
-      <c r="AD28" s="152"/>
-      <c r="AE28" s="152"/>
-      <c r="AF28" s="153"/>
+      <c r="C28" s="176"/>
+      <c r="D28" s="176"/>
+      <c r="E28" s="176"/>
+      <c r="F28" s="177"/>
+      <c r="G28" s="252"/>
+      <c r="H28" s="253"/>
+      <c r="I28" s="253"/>
+      <c r="J28" s="253"/>
+      <c r="K28" s="253"/>
+      <c r="L28" s="253"/>
+      <c r="M28" s="253"/>
+      <c r="N28" s="253"/>
+      <c r="O28" s="253"/>
+      <c r="P28" s="253"/>
+      <c r="Q28" s="253"/>
+      <c r="R28" s="253"/>
+      <c r="S28" s="253"/>
+      <c r="T28" s="253"/>
+      <c r="U28" s="253"/>
+      <c r="V28" s="253"/>
+      <c r="W28" s="253"/>
+      <c r="X28" s="253"/>
+      <c r="Y28" s="253"/>
+      <c r="Z28" s="253"/>
+      <c r="AA28" s="253"/>
+      <c r="AB28" s="253"/>
+      <c r="AC28" s="253"/>
+      <c r="AD28" s="253"/>
+      <c r="AE28" s="253"/>
+      <c r="AF28" s="254"/>
       <c r="AJ28" s="33"/>
       <c r="AK28" s="18"/>
     </row>
     <row r="29" spans="1:37" s="3" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="223"/>
-      <c r="B29" s="149"/>
-      <c r="C29" s="149"/>
-      <c r="D29" s="149"/>
-      <c r="E29" s="149"/>
-      <c r="F29" s="150"/>
-      <c r="G29" s="245" t="s">
+      <c r="A29" s="159"/>
+      <c r="B29" s="250"/>
+      <c r="C29" s="250"/>
+      <c r="D29" s="250"/>
+      <c r="E29" s="250"/>
+      <c r="F29" s="251"/>
+      <c r="G29" s="190" t="s">
         <v>67</v>
       </c>
-      <c r="H29" s="246"/>
-      <c r="I29" s="246"/>
-      <c r="J29" s="246"/>
-      <c r="K29" s="246"/>
-      <c r="L29" s="246"/>
-      <c r="M29" s="246"/>
-      <c r="N29" s="246"/>
-      <c r="O29" s="246"/>
-      <c r="P29" s="246"/>
-      <c r="Q29" s="246"/>
-      <c r="R29" s="246"/>
-      <c r="S29" s="246"/>
-      <c r="T29" s="246"/>
-      <c r="U29" s="246"/>
-      <c r="V29" s="246"/>
-      <c r="W29" s="246"/>
-      <c r="X29" s="246"/>
-      <c r="Y29" s="246"/>
-      <c r="Z29" s="246"/>
-      <c r="AA29" s="246"/>
-      <c r="AB29" s="246"/>
-      <c r="AC29" s="246"/>
-      <c r="AD29" s="246"/>
-      <c r="AE29" s="246"/>
-      <c r="AF29" s="247"/>
+      <c r="H29" s="191"/>
+      <c r="I29" s="191"/>
+      <c r="J29" s="191"/>
+      <c r="K29" s="191"/>
+      <c r="L29" s="191"/>
+      <c r="M29" s="191"/>
+      <c r="N29" s="191"/>
+      <c r="O29" s="191"/>
+      <c r="P29" s="191"/>
+      <c r="Q29" s="191"/>
+      <c r="R29" s="191"/>
+      <c r="S29" s="191"/>
+      <c r="T29" s="191"/>
+      <c r="U29" s="191"/>
+      <c r="V29" s="191"/>
+      <c r="W29" s="191"/>
+      <c r="X29" s="191"/>
+      <c r="Y29" s="191"/>
+      <c r="Z29" s="191"/>
+      <c r="AA29" s="191"/>
+      <c r="AB29" s="191"/>
+      <c r="AC29" s="191"/>
+      <c r="AD29" s="191"/>
+      <c r="AE29" s="191"/>
+      <c r="AF29" s="192"/>
       <c r="AG29" s="1"/>
       <c r="AH29" s="1"/>
       <c r="AI29" s="1"/>
@@ -4613,16 +4613,16 @@
       <c r="AK30" s="26"/>
     </row>
     <row r="31" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="264" t="s">
+      <c r="A31" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="274" t="s">
+      <c r="B31" s="147" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="275"/>
-      <c r="D31" s="275"/>
-      <c r="E31" s="275"/>
-      <c r="F31" s="276"/>
+      <c r="C31" s="148"/>
+      <c r="D31" s="148"/>
+      <c r="E31" s="148"/>
+      <c r="F31" s="149"/>
       <c r="G31" s="42" t="s">
         <v>22</v>
       </c>
@@ -4633,21 +4633,21 @@
       <c r="L31" s="32"/>
       <c r="M31" s="26"/>
       <c r="N31" s="43"/>
-      <c r="O31" s="123" t="s">
+      <c r="O31" s="282" t="s">
         <v>23</v>
       </c>
-      <c r="P31" s="124"/>
-      <c r="Q31" s="137" t="s">
+      <c r="P31" s="216"/>
+      <c r="Q31" s="283" t="s">
         <v>61</v>
       </c>
-      <c r="R31" s="137"/>
-      <c r="S31" s="124"/>
-      <c r="T31" s="124"/>
-      <c r="U31" s="124"/>
-      <c r="V31" s="124"/>
-      <c r="W31" s="124"/>
-      <c r="X31" s="124"/>
-      <c r="Y31" s="124"/>
+      <c r="R31" s="283"/>
+      <c r="S31" s="216"/>
+      <c r="T31" s="216"/>
+      <c r="U31" s="216"/>
+      <c r="V31" s="216"/>
+      <c r="W31" s="216"/>
+      <c r="X31" s="216"/>
+      <c r="Y31" s="216"/>
       <c r="Z31" s="87" t="s">
         <v>65</v>
       </c>
@@ -4661,100 +4661,100 @@
       <c r="AK31" s="26"/>
     </row>
     <row r="32" spans="1:37" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="265"/>
-      <c r="B32" s="138" t="s">
+      <c r="A32" s="136"/>
+      <c r="B32" s="284" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="139"/>
-      <c r="D32" s="139"/>
-      <c r="E32" s="139"/>
-      <c r="F32" s="140"/>
-      <c r="G32" s="103"/>
-      <c r="H32" s="104"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="104"/>
-      <c r="M32" s="104"/>
-      <c r="N32" s="144"/>
-      <c r="O32" s="103"/>
-      <c r="P32" s="104"/>
-      <c r="Q32" s="104"/>
-      <c r="R32" s="104"/>
-      <c r="S32" s="104"/>
-      <c r="T32" s="104"/>
-      <c r="U32" s="104"/>
-      <c r="V32" s="104"/>
-      <c r="W32" s="104"/>
-      <c r="X32" s="104"/>
-      <c r="Y32" s="104"/>
-      <c r="Z32" s="104"/>
-      <c r="AA32" s="104"/>
-      <c r="AB32" s="104"/>
-      <c r="AC32" s="104"/>
-      <c r="AD32" s="104"/>
-      <c r="AE32" s="104"/>
-      <c r="AF32" s="105"/>
+      <c r="C32" s="285"/>
+      <c r="D32" s="285"/>
+      <c r="E32" s="285"/>
+      <c r="F32" s="286"/>
+      <c r="G32" s="290"/>
+      <c r="H32" s="291"/>
+      <c r="I32" s="291"/>
+      <c r="J32" s="291"/>
+      <c r="K32" s="291"/>
+      <c r="L32" s="291"/>
+      <c r="M32" s="291"/>
+      <c r="N32" s="292"/>
+      <c r="O32" s="290"/>
+      <c r="P32" s="291"/>
+      <c r="Q32" s="291"/>
+      <c r="R32" s="291"/>
+      <c r="S32" s="291"/>
+      <c r="T32" s="291"/>
+      <c r="U32" s="291"/>
+      <c r="V32" s="291"/>
+      <c r="W32" s="291"/>
+      <c r="X32" s="291"/>
+      <c r="Y32" s="291"/>
+      <c r="Z32" s="291"/>
+      <c r="AA32" s="291"/>
+      <c r="AB32" s="291"/>
+      <c r="AC32" s="291"/>
+      <c r="AD32" s="291"/>
+      <c r="AE32" s="291"/>
+      <c r="AF32" s="296"/>
       <c r="AJ32" s="32"/>
       <c r="AK32" s="26"/>
     </row>
     <row r="33" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="265"/>
-      <c r="B33" s="141"/>
-      <c r="C33" s="142"/>
-      <c r="D33" s="142"/>
-      <c r="E33" s="142"/>
-      <c r="F33" s="143"/>
-      <c r="G33" s="145"/>
-      <c r="H33" s="146"/>
-      <c r="I33" s="146"/>
-      <c r="J33" s="146"/>
-      <c r="K33" s="146"/>
-      <c r="L33" s="146"/>
-      <c r="M33" s="146"/>
-      <c r="N33" s="147"/>
+      <c r="A33" s="136"/>
+      <c r="B33" s="287"/>
+      <c r="C33" s="288"/>
+      <c r="D33" s="288"/>
+      <c r="E33" s="288"/>
+      <c r="F33" s="289"/>
+      <c r="G33" s="293"/>
+      <c r="H33" s="294"/>
+      <c r="I33" s="294"/>
+      <c r="J33" s="294"/>
+      <c r="K33" s="294"/>
+      <c r="L33" s="294"/>
+      <c r="M33" s="294"/>
+      <c r="N33" s="295"/>
       <c r="O33" s="47"/>
       <c r="P33" s="48"/>
       <c r="Q33" s="35"/>
       <c r="R33" s="5"/>
       <c r="S33" s="5"/>
-      <c r="T33" s="148" t="s">
+      <c r="T33" s="297" t="s">
         <v>10</v>
       </c>
-      <c r="U33" s="148"/>
-      <c r="V33" s="148"/>
-      <c r="W33" s="106"/>
-      <c r="X33" s="106"/>
-      <c r="Y33" s="106"/>
-      <c r="Z33" s="106"/>
-      <c r="AA33" s="106"/>
-      <c r="AB33" s="106"/>
-      <c r="AC33" s="106"/>
-      <c r="AD33" s="106"/>
-      <c r="AE33" s="106"/>
-      <c r="AF33" s="107"/>
+      <c r="U33" s="297"/>
+      <c r="V33" s="297"/>
+      <c r="W33" s="298"/>
+      <c r="X33" s="298"/>
+      <c r="Y33" s="298"/>
+      <c r="Z33" s="298"/>
+      <c r="AA33" s="298"/>
+      <c r="AB33" s="298"/>
+      <c r="AC33" s="298"/>
+      <c r="AD33" s="298"/>
+      <c r="AE33" s="298"/>
+      <c r="AF33" s="299"/>
       <c r="AJ33" s="32"/>
       <c r="AK33" s="26"/>
     </row>
     <row r="34" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="265"/>
-      <c r="B34" s="267" t="s">
+      <c r="A34" s="136"/>
+      <c r="B34" s="138" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="267"/>
-      <c r="D34" s="267"/>
-      <c r="E34" s="267"/>
-      <c r="F34" s="268"/>
-      <c r="G34" s="126" t="s">
+      <c r="C34" s="138"/>
+      <c r="D34" s="138"/>
+      <c r="E34" s="138"/>
+      <c r="F34" s="139"/>
+      <c r="G34" s="274" t="s">
         <v>6</v>
       </c>
-      <c r="H34" s="127"/>
-      <c r="I34" s="128"/>
-      <c r="J34" s="128"/>
-      <c r="K34" s="128"/>
-      <c r="L34" s="128"/>
-      <c r="M34" s="128"/>
-      <c r="N34" s="129"/>
+      <c r="H34" s="275"/>
+      <c r="I34" s="276"/>
+      <c r="J34" s="276"/>
+      <c r="K34" s="276"/>
+      <c r="L34" s="276"/>
+      <c r="M34" s="276"/>
+      <c r="N34" s="277"/>
       <c r="O34" s="50" t="s">
         <v>8</v>
       </c>
@@ -4776,82 +4776,82 @@
       <c r="AK34" s="26"/>
     </row>
     <row r="35" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="265"/>
-      <c r="B35" s="269" t="s">
+      <c r="A35" s="136"/>
+      <c r="B35" s="140" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="269"/>
-      <c r="D35" s="269"/>
-      <c r="E35" s="269"/>
-      <c r="F35" s="270"/>
-      <c r="G35" s="130" t="s">
+      <c r="C35" s="140"/>
+      <c r="D35" s="140"/>
+      <c r="E35" s="140"/>
+      <c r="F35" s="141"/>
+      <c r="G35" s="278" t="s">
         <v>71</v>
       </c>
-      <c r="H35" s="131"/>
-      <c r="I35" s="132"/>
-      <c r="J35" s="132"/>
-      <c r="K35" s="132"/>
-      <c r="L35" s="132"/>
-      <c r="M35" s="132"/>
-      <c r="N35" s="133"/>
-      <c r="O35" s="134"/>
-      <c r="P35" s="135"/>
-      <c r="Q35" s="135"/>
-      <c r="R35" s="135"/>
-      <c r="S35" s="136"/>
-      <c r="T35" s="115"/>
-      <c r="U35" s="116"/>
-      <c r="V35" s="116"/>
-      <c r="W35" s="116"/>
-      <c r="X35" s="116"/>
-      <c r="Y35" s="116"/>
-      <c r="Z35" s="116"/>
-      <c r="AA35" s="116"/>
-      <c r="AB35" s="116"/>
-      <c r="AC35" s="116"/>
-      <c r="AD35" s="116"/>
-      <c r="AE35" s="116"/>
-      <c r="AF35" s="117"/>
+      <c r="H35" s="279"/>
+      <c r="I35" s="280"/>
+      <c r="J35" s="280"/>
+      <c r="K35" s="280"/>
+      <c r="L35" s="280"/>
+      <c r="M35" s="280"/>
+      <c r="N35" s="281"/>
+      <c r="O35" s="269"/>
+      <c r="P35" s="270"/>
+      <c r="Q35" s="270"/>
+      <c r="R35" s="270"/>
+      <c r="S35" s="271"/>
+      <c r="T35" s="306"/>
+      <c r="U35" s="307"/>
+      <c r="V35" s="307"/>
+      <c r="W35" s="307"/>
+      <c r="X35" s="307"/>
+      <c r="Y35" s="307"/>
+      <c r="Z35" s="307"/>
+      <c r="AA35" s="307"/>
+      <c r="AB35" s="307"/>
+      <c r="AC35" s="307"/>
+      <c r="AD35" s="307"/>
+      <c r="AE35" s="307"/>
+      <c r="AF35" s="308"/>
       <c r="AJ35" s="32"/>
       <c r="AK35" s="26"/>
     </row>
     <row r="36" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="265"/>
-      <c r="B36" s="248" t="s">
+      <c r="A36" s="136"/>
+      <c r="B36" s="142" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="248"/>
-      <c r="D36" s="248"/>
-      <c r="E36" s="248"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="271" t="s">
+      <c r="C36" s="142"/>
+      <c r="D36" s="142"/>
+      <c r="E36" s="142"/>
+      <c r="F36" s="143"/>
+      <c r="G36" s="144" t="s">
         <v>72</v>
       </c>
-      <c r="H36" s="272"/>
-      <c r="I36" s="272"/>
-      <c r="J36" s="272"/>
-      <c r="K36" s="272"/>
-      <c r="L36" s="272"/>
-      <c r="M36" s="272"/>
-      <c r="N36" s="272"/>
-      <c r="O36" s="272"/>
-      <c r="P36" s="272"/>
-      <c r="Q36" s="272"/>
-      <c r="R36" s="272"/>
-      <c r="S36" s="272"/>
-      <c r="T36" s="272"/>
-      <c r="U36" s="272"/>
-      <c r="V36" s="272"/>
-      <c r="W36" s="272"/>
-      <c r="X36" s="272"/>
-      <c r="Y36" s="272"/>
-      <c r="Z36" s="272"/>
-      <c r="AA36" s="272"/>
-      <c r="AB36" s="272"/>
-      <c r="AC36" s="272"/>
-      <c r="AD36" s="272"/>
-      <c r="AE36" s="272"/>
-      <c r="AF36" s="273"/>
+      <c r="H36" s="145"/>
+      <c r="I36" s="145"/>
+      <c r="J36" s="145"/>
+      <c r="K36" s="145"/>
+      <c r="L36" s="145"/>
+      <c r="M36" s="145"/>
+      <c r="N36" s="145"/>
+      <c r="O36" s="145"/>
+      <c r="P36" s="145"/>
+      <c r="Q36" s="145"/>
+      <c r="R36" s="145"/>
+      <c r="S36" s="145"/>
+      <c r="T36" s="145"/>
+      <c r="U36" s="145"/>
+      <c r="V36" s="145"/>
+      <c r="W36" s="145"/>
+      <c r="X36" s="145"/>
+      <c r="Y36" s="145"/>
+      <c r="Z36" s="145"/>
+      <c r="AA36" s="145"/>
+      <c r="AB36" s="145"/>
+      <c r="AC36" s="145"/>
+      <c r="AD36" s="145"/>
+      <c r="AE36" s="145"/>
+      <c r="AF36" s="146"/>
       <c r="AG36" s="18"/>
       <c r="AH36" s="18"/>
       <c r="AI36" s="18"/>
@@ -4859,40 +4859,40 @@
       <c r="AK36" s="18"/>
     </row>
     <row r="37" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="265"/>
-      <c r="B37" s="108" t="s">
+      <c r="A37" s="136"/>
+      <c r="B37" s="266" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="109"/>
-      <c r="D37" s="109"/>
-      <c r="E37" s="109"/>
-      <c r="F37" s="118"/>
-      <c r="G37" s="120"/>
-      <c r="H37" s="121"/>
-      <c r="I37" s="121"/>
-      <c r="J37" s="121"/>
-      <c r="K37" s="121"/>
-      <c r="L37" s="121"/>
-      <c r="M37" s="121"/>
-      <c r="N37" s="121"/>
-      <c r="O37" s="121"/>
-      <c r="P37" s="121"/>
-      <c r="Q37" s="121"/>
-      <c r="R37" s="121"/>
-      <c r="S37" s="121"/>
-      <c r="T37" s="121"/>
-      <c r="U37" s="121"/>
-      <c r="V37" s="121"/>
-      <c r="W37" s="121"/>
-      <c r="X37" s="121"/>
-      <c r="Y37" s="121"/>
-      <c r="Z37" s="121"/>
-      <c r="AA37" s="121"/>
-      <c r="AB37" s="121"/>
-      <c r="AC37" s="121"/>
-      <c r="AD37" s="121"/>
-      <c r="AE37" s="121"/>
-      <c r="AF37" s="122"/>
+      <c r="C37" s="267"/>
+      <c r="D37" s="267"/>
+      <c r="E37" s="267"/>
+      <c r="F37" s="268"/>
+      <c r="G37" s="310"/>
+      <c r="H37" s="311"/>
+      <c r="I37" s="311"/>
+      <c r="J37" s="311"/>
+      <c r="K37" s="311"/>
+      <c r="L37" s="311"/>
+      <c r="M37" s="311"/>
+      <c r="N37" s="311"/>
+      <c r="O37" s="311"/>
+      <c r="P37" s="311"/>
+      <c r="Q37" s="311"/>
+      <c r="R37" s="311"/>
+      <c r="S37" s="311"/>
+      <c r="T37" s="311"/>
+      <c r="U37" s="311"/>
+      <c r="V37" s="311"/>
+      <c r="W37" s="311"/>
+      <c r="X37" s="311"/>
+      <c r="Y37" s="311"/>
+      <c r="Z37" s="311"/>
+      <c r="AA37" s="311"/>
+      <c r="AB37" s="311"/>
+      <c r="AC37" s="311"/>
+      <c r="AD37" s="311"/>
+      <c r="AE37" s="311"/>
+      <c r="AF37" s="312"/>
       <c r="AG37" s="18"/>
       <c r="AH37" s="18"/>
       <c r="AI37" s="18"/>
@@ -4900,40 +4900,40 @@
       <c r="AK37" s="18"/>
     </row>
     <row r="38" spans="1:37" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="266"/>
-      <c r="B38" s="110"/>
-      <c r="C38" s="111"/>
-      <c r="D38" s="111"/>
-      <c r="E38" s="111"/>
-      <c r="F38" s="119"/>
-      <c r="G38" s="254" t="s">
+      <c r="A38" s="137"/>
+      <c r="B38" s="301"/>
+      <c r="C38" s="302"/>
+      <c r="D38" s="302"/>
+      <c r="E38" s="302"/>
+      <c r="F38" s="309"/>
+      <c r="G38" s="313" t="s">
         <v>29</v>
       </c>
-      <c r="H38" s="255"/>
-      <c r="I38" s="255"/>
-      <c r="J38" s="255"/>
-      <c r="K38" s="255"/>
-      <c r="L38" s="255"/>
-      <c r="M38" s="255"/>
-      <c r="N38" s="255"/>
-      <c r="O38" s="255"/>
-      <c r="P38" s="255"/>
-      <c r="Q38" s="255"/>
-      <c r="R38" s="255"/>
-      <c r="S38" s="255"/>
-      <c r="T38" s="255"/>
-      <c r="U38" s="255"/>
-      <c r="V38" s="255"/>
-      <c r="W38" s="255"/>
-      <c r="X38" s="255"/>
-      <c r="Y38" s="255"/>
-      <c r="Z38" s="255"/>
-      <c r="AA38" s="255"/>
-      <c r="AB38" s="255"/>
-      <c r="AC38" s="255"/>
-      <c r="AD38" s="255"/>
-      <c r="AE38" s="255"/>
-      <c r="AF38" s="256"/>
+      <c r="H38" s="314"/>
+      <c r="I38" s="314"/>
+      <c r="J38" s="314"/>
+      <c r="K38" s="314"/>
+      <c r="L38" s="314"/>
+      <c r="M38" s="314"/>
+      <c r="N38" s="314"/>
+      <c r="O38" s="314"/>
+      <c r="P38" s="314"/>
+      <c r="Q38" s="314"/>
+      <c r="R38" s="314"/>
+      <c r="S38" s="314"/>
+      <c r="T38" s="314"/>
+      <c r="U38" s="314"/>
+      <c r="V38" s="314"/>
+      <c r="W38" s="314"/>
+      <c r="X38" s="314"/>
+      <c r="Y38" s="314"/>
+      <c r="Z38" s="314"/>
+      <c r="AA38" s="314"/>
+      <c r="AB38" s="314"/>
+      <c r="AC38" s="314"/>
+      <c r="AD38" s="314"/>
+      <c r="AE38" s="314"/>
+      <c r="AF38" s="315"/>
       <c r="AG38" s="18"/>
       <c r="AH38" s="18"/>
       <c r="AI38" s="18"/>
@@ -4975,26 +4975,26 @@
       <c r="AF39" s="28"/>
     </row>
     <row r="40" spans="1:37" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="257" t="s">
+      <c r="A40" s="126" t="s">
         <v>30</v>
       </c>
-      <c r="B40" s="185" t="s">
+      <c r="B40" s="130" t="s">
         <v>31</v>
       </c>
-      <c r="C40" s="185"/>
-      <c r="D40" s="185"/>
-      <c r="E40" s="185"/>
-      <c r="F40" s="185"/>
-      <c r="G40" s="123"/>
-      <c r="H40" s="124"/>
-      <c r="I40" s="124"/>
-      <c r="J40" s="124"/>
-      <c r="K40" s="124"/>
-      <c r="L40" s="124"/>
-      <c r="M40" s="124"/>
-      <c r="N40" s="124"/>
-      <c r="O40" s="124"/>
-      <c r="P40" s="125"/>
+      <c r="C40" s="130"/>
+      <c r="D40" s="130"/>
+      <c r="E40" s="130"/>
+      <c r="F40" s="130"/>
+      <c r="G40" s="282"/>
+      <c r="H40" s="216"/>
+      <c r="I40" s="216"/>
+      <c r="J40" s="216"/>
+      <c r="K40" s="216"/>
+      <c r="L40" s="216"/>
+      <c r="M40" s="216"/>
+      <c r="N40" s="216"/>
+      <c r="O40" s="216"/>
+      <c r="P40" s="217"/>
       <c r="Q40" s="59" t="s">
         <v>32</v>
       </c>
@@ -5020,31 +5020,31 @@
       <c r="AK40" s="18"/>
     </row>
     <row r="41" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="258"/>
-      <c r="B41" s="101"/>
-      <c r="C41" s="101"/>
-      <c r="D41" s="101"/>
-      <c r="E41" s="101"/>
-      <c r="F41" s="101"/>
-      <c r="G41" s="100"/>
-      <c r="H41" s="101"/>
-      <c r="I41" s="101"/>
-      <c r="J41" s="101"/>
-      <c r="K41" s="101"/>
-      <c r="L41" s="101"/>
-      <c r="M41" s="101"/>
-      <c r="N41" s="101"/>
-      <c r="O41" s="101"/>
-      <c r="P41" s="102"/>
-      <c r="Q41" s="97" t="s">
+      <c r="A41" s="127"/>
+      <c r="B41" s="131"/>
+      <c r="C41" s="131"/>
+      <c r="D41" s="131"/>
+      <c r="E41" s="131"/>
+      <c r="F41" s="131"/>
+      <c r="G41" s="235"/>
+      <c r="H41" s="131"/>
+      <c r="I41" s="131"/>
+      <c r="J41" s="131"/>
+      <c r="K41" s="131"/>
+      <c r="L41" s="131"/>
+      <c r="M41" s="131"/>
+      <c r="N41" s="131"/>
+      <c r="O41" s="131"/>
+      <c r="P41" s="218"/>
+      <c r="Q41" s="231" t="s">
         <v>61</v>
       </c>
-      <c r="R41" s="98"/>
-      <c r="S41" s="98"/>
-      <c r="T41" s="98"/>
-      <c r="U41" s="98"/>
-      <c r="V41" s="98"/>
-      <c r="W41" s="98"/>
+      <c r="R41" s="232"/>
+      <c r="S41" s="232"/>
+      <c r="T41" s="232"/>
+      <c r="U41" s="232"/>
+      <c r="V41" s="232"/>
+      <c r="W41" s="232"/>
       <c r="X41" s="36" t="s">
         <v>65</v>
       </c>
@@ -5059,80 +5059,80 @@
       <c r="AK41" s="23"/>
     </row>
     <row r="42" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="259"/>
-      <c r="B42" s="91" t="s">
+      <c r="A42" s="128"/>
+      <c r="B42" s="175" t="s">
         <v>33</v>
       </c>
-      <c r="C42" s="92"/>
-      <c r="D42" s="92"/>
-      <c r="E42" s="92"/>
-      <c r="F42" s="93"/>
-      <c r="G42" s="97"/>
-      <c r="H42" s="98"/>
-      <c r="I42" s="98"/>
-      <c r="J42" s="98"/>
-      <c r="K42" s="98"/>
-      <c r="L42" s="98"/>
-      <c r="M42" s="98"/>
-      <c r="N42" s="98"/>
-      <c r="O42" s="98"/>
-      <c r="P42" s="99"/>
-      <c r="Q42" s="103"/>
-      <c r="R42" s="104"/>
-      <c r="S42" s="104"/>
-      <c r="T42" s="104"/>
-      <c r="U42" s="104"/>
-      <c r="V42" s="104"/>
-      <c r="W42" s="104"/>
-      <c r="X42" s="104"/>
-      <c r="Y42" s="104"/>
-      <c r="Z42" s="104"/>
-      <c r="AA42" s="104"/>
-      <c r="AB42" s="104"/>
-      <c r="AC42" s="104"/>
-      <c r="AD42" s="104"/>
-      <c r="AE42" s="104"/>
-      <c r="AF42" s="105"/>
+      <c r="C42" s="176"/>
+      <c r="D42" s="176"/>
+      <c r="E42" s="176"/>
+      <c r="F42" s="177"/>
+      <c r="G42" s="231"/>
+      <c r="H42" s="232"/>
+      <c r="I42" s="232"/>
+      <c r="J42" s="232"/>
+      <c r="K42" s="232"/>
+      <c r="L42" s="232"/>
+      <c r="M42" s="232"/>
+      <c r="N42" s="232"/>
+      <c r="O42" s="232"/>
+      <c r="P42" s="300"/>
+      <c r="Q42" s="290"/>
+      <c r="R42" s="291"/>
+      <c r="S42" s="291"/>
+      <c r="T42" s="291"/>
+      <c r="U42" s="291"/>
+      <c r="V42" s="291"/>
+      <c r="W42" s="291"/>
+      <c r="X42" s="291"/>
+      <c r="Y42" s="291"/>
+      <c r="Z42" s="291"/>
+      <c r="AA42" s="291"/>
+      <c r="AB42" s="291"/>
+      <c r="AC42" s="291"/>
+      <c r="AD42" s="291"/>
+      <c r="AE42" s="291"/>
+      <c r="AF42" s="296"/>
       <c r="AK42" s="23"/>
     </row>
     <row r="43" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="259"/>
-      <c r="B43" s="94"/>
-      <c r="C43" s="95"/>
-      <c r="D43" s="95"/>
-      <c r="E43" s="95"/>
-      <c r="F43" s="96"/>
-      <c r="G43" s="100"/>
-      <c r="H43" s="101"/>
-      <c r="I43" s="101"/>
-      <c r="J43" s="101"/>
-      <c r="K43" s="101"/>
-      <c r="L43" s="101"/>
-      <c r="M43" s="101"/>
-      <c r="N43" s="101"/>
-      <c r="O43" s="101"/>
-      <c r="P43" s="102"/>
+      <c r="A43" s="128"/>
+      <c r="B43" s="178"/>
+      <c r="C43" s="179"/>
+      <c r="D43" s="179"/>
+      <c r="E43" s="179"/>
+      <c r="F43" s="180"/>
+      <c r="G43" s="235"/>
+      <c r="H43" s="131"/>
+      <c r="I43" s="131"/>
+      <c r="J43" s="131"/>
+      <c r="K43" s="131"/>
+      <c r="L43" s="131"/>
+      <c r="M43" s="131"/>
+      <c r="N43" s="131"/>
+      <c r="O43" s="131"/>
+      <c r="P43" s="218"/>
       <c r="Q43" s="64" t="s">
         <v>10</v>
       </c>
       <c r="R43" s="62"/>
       <c r="S43" s="62"/>
       <c r="T43" s="62"/>
-      <c r="U43" s="106"/>
-      <c r="V43" s="106"/>
-      <c r="W43" s="106"/>
-      <c r="X43" s="106"/>
-      <c r="Y43" s="106"/>
-      <c r="Z43" s="106"/>
-      <c r="AA43" s="106"/>
-      <c r="AB43" s="106"/>
-      <c r="AC43" s="106"/>
-      <c r="AD43" s="106"/>
-      <c r="AE43" s="106"/>
-      <c r="AF43" s="107"/>
+      <c r="U43" s="298"/>
+      <c r="V43" s="298"/>
+      <c r="W43" s="298"/>
+      <c r="X43" s="298"/>
+      <c r="Y43" s="298"/>
+      <c r="Z43" s="298"/>
+      <c r="AA43" s="298"/>
+      <c r="AB43" s="298"/>
+      <c r="AC43" s="298"/>
+      <c r="AD43" s="298"/>
+      <c r="AE43" s="298"/>
+      <c r="AF43" s="299"/>
     </row>
     <row r="44" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="259"/>
+      <c r="A44" s="128"/>
       <c r="B44" s="36" t="s">
         <v>34</v>
       </c>
@@ -5167,7 +5167,7 @@
       <c r="AJ44" s="33"/>
     </row>
     <row r="45" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="259"/>
+      <c r="A45" s="128"/>
       <c r="B45" s="69" t="s">
         <v>35</v>
       </c>
@@ -5203,76 +5203,76 @@
       <c r="AF45" s="49"/>
     </row>
     <row r="46" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="259"/>
-      <c r="B46" s="108" t="s">
+      <c r="A46" s="128"/>
+      <c r="B46" s="266" t="s">
         <v>28</v>
       </c>
-      <c r="C46" s="109"/>
-      <c r="D46" s="109"/>
-      <c r="E46" s="109"/>
-      <c r="F46" s="109"/>
-      <c r="G46" s="112"/>
-      <c r="H46" s="113"/>
-      <c r="I46" s="113"/>
-      <c r="J46" s="113"/>
-      <c r="K46" s="113"/>
-      <c r="L46" s="113"/>
-      <c r="M46" s="113"/>
-      <c r="N46" s="113"/>
-      <c r="O46" s="113"/>
-      <c r="P46" s="113"/>
-      <c r="Q46" s="113"/>
-      <c r="R46" s="113"/>
-      <c r="S46" s="113"/>
-      <c r="T46" s="113"/>
-      <c r="U46" s="113"/>
-      <c r="V46" s="113"/>
-      <c r="W46" s="113"/>
-      <c r="X46" s="113"/>
-      <c r="Y46" s="113"/>
-      <c r="Z46" s="113"/>
-      <c r="AA46" s="113"/>
-      <c r="AB46" s="113"/>
-      <c r="AC46" s="113"/>
-      <c r="AD46" s="113"/>
-      <c r="AE46" s="113"/>
-      <c r="AF46" s="114"/>
+      <c r="C46" s="267"/>
+      <c r="D46" s="267"/>
+      <c r="E46" s="267"/>
+      <c r="F46" s="267"/>
+      <c r="G46" s="303"/>
+      <c r="H46" s="304"/>
+      <c r="I46" s="304"/>
+      <c r="J46" s="304"/>
+      <c r="K46" s="304"/>
+      <c r="L46" s="304"/>
+      <c r="M46" s="304"/>
+      <c r="N46" s="304"/>
+      <c r="O46" s="304"/>
+      <c r="P46" s="304"/>
+      <c r="Q46" s="304"/>
+      <c r="R46" s="304"/>
+      <c r="S46" s="304"/>
+      <c r="T46" s="304"/>
+      <c r="U46" s="304"/>
+      <c r="V46" s="304"/>
+      <c r="W46" s="304"/>
+      <c r="X46" s="304"/>
+      <c r="Y46" s="304"/>
+      <c r="Z46" s="304"/>
+      <c r="AA46" s="304"/>
+      <c r="AB46" s="304"/>
+      <c r="AC46" s="304"/>
+      <c r="AD46" s="304"/>
+      <c r="AE46" s="304"/>
+      <c r="AF46" s="305"/>
     </row>
     <row r="47" spans="1:37" s="72" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="260"/>
-      <c r="B47" s="110"/>
-      <c r="C47" s="111"/>
-      <c r="D47" s="111"/>
-      <c r="E47" s="111"/>
-      <c r="F47" s="111"/>
-      <c r="G47" s="261" t="s">
+      <c r="A47" s="129"/>
+      <c r="B47" s="301"/>
+      <c r="C47" s="302"/>
+      <c r="D47" s="302"/>
+      <c r="E47" s="302"/>
+      <c r="F47" s="302"/>
+      <c r="G47" s="132" t="s">
         <v>36</v>
       </c>
-      <c r="H47" s="262"/>
-      <c r="I47" s="262"/>
-      <c r="J47" s="262"/>
-      <c r="K47" s="262"/>
-      <c r="L47" s="262"/>
-      <c r="M47" s="262"/>
-      <c r="N47" s="262"/>
-      <c r="O47" s="262"/>
-      <c r="P47" s="262"/>
-      <c r="Q47" s="262"/>
-      <c r="R47" s="262"/>
-      <c r="S47" s="262"/>
-      <c r="T47" s="262"/>
-      <c r="U47" s="262"/>
-      <c r="V47" s="262"/>
-      <c r="W47" s="262"/>
-      <c r="X47" s="262"/>
-      <c r="Y47" s="262"/>
-      <c r="Z47" s="262"/>
-      <c r="AA47" s="262"/>
-      <c r="AB47" s="262"/>
-      <c r="AC47" s="262"/>
-      <c r="AD47" s="262"/>
-      <c r="AE47" s="262"/>
-      <c r="AF47" s="263"/>
+      <c r="H47" s="133"/>
+      <c r="I47" s="133"/>
+      <c r="J47" s="133"/>
+      <c r="K47" s="133"/>
+      <c r="L47" s="133"/>
+      <c r="M47" s="133"/>
+      <c r="N47" s="133"/>
+      <c r="O47" s="133"/>
+      <c r="P47" s="133"/>
+      <c r="Q47" s="133"/>
+      <c r="R47" s="133"/>
+      <c r="S47" s="133"/>
+      <c r="T47" s="133"/>
+      <c r="U47" s="133"/>
+      <c r="V47" s="133"/>
+      <c r="W47" s="133"/>
+      <c r="X47" s="133"/>
+      <c r="Y47" s="133"/>
+      <c r="Z47" s="133"/>
+      <c r="AA47" s="133"/>
+      <c r="AB47" s="133"/>
+      <c r="AC47" s="133"/>
+      <c r="AD47" s="133"/>
+      <c r="AE47" s="133"/>
+      <c r="AF47" s="134"/>
       <c r="AJ47" s="73"/>
     </row>
     <row r="48" spans="1:37" s="3" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -5313,301 +5313,301 @@
       <c r="D49" s="77"/>
       <c r="E49" s="77"/>
       <c r="F49" s="78"/>
-      <c r="G49" s="277" t="s">
+      <c r="G49" s="91" t="s">
         <v>57</v>
       </c>
-      <c r="H49" s="278"/>
-      <c r="I49" s="278"/>
-      <c r="J49" s="278"/>
-      <c r="K49" s="278"/>
-      <c r="L49" s="278"/>
-      <c r="M49" s="278"/>
-      <c r="N49" s="278"/>
-      <c r="O49" s="278"/>
-      <c r="P49" s="278"/>
-      <c r="Q49" s="278"/>
-      <c r="R49" s="278"/>
-      <c r="S49" s="278"/>
-      <c r="T49" s="278"/>
-      <c r="U49" s="278"/>
-      <c r="V49" s="278"/>
-      <c r="W49" s="278"/>
-      <c r="X49" s="278"/>
-      <c r="Y49" s="278"/>
-      <c r="Z49" s="278"/>
-      <c r="AA49" s="278"/>
-      <c r="AB49" s="278"/>
-      <c r="AC49" s="278"/>
-      <c r="AD49" s="278"/>
-      <c r="AE49" s="278"/>
-      <c r="AF49" s="279"/>
+      <c r="H49" s="92"/>
+      <c r="I49" s="92"/>
+      <c r="J49" s="92"/>
+      <c r="K49" s="92"/>
+      <c r="L49" s="92"/>
+      <c r="M49" s="92"/>
+      <c r="N49" s="92"/>
+      <c r="O49" s="92"/>
+      <c r="P49" s="92"/>
+      <c r="Q49" s="92"/>
+      <c r="R49" s="92"/>
+      <c r="S49" s="92"/>
+      <c r="T49" s="92"/>
+      <c r="U49" s="92"/>
+      <c r="V49" s="92"/>
+      <c r="W49" s="92"/>
+      <c r="X49" s="92"/>
+      <c r="Y49" s="92"/>
+      <c r="Z49" s="92"/>
+      <c r="AA49" s="92"/>
+      <c r="AB49" s="92"/>
+      <c r="AC49" s="92"/>
+      <c r="AD49" s="92"/>
+      <c r="AE49" s="92"/>
+      <c r="AF49" s="93"/>
       <c r="AG49" s="76"/>
     </row>
     <row r="50" spans="1:33" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="B50" s="292" t="s">
+      <c r="B50" s="106" t="s">
         <v>38</v>
       </c>
-      <c r="C50" s="293"/>
-      <c r="D50" s="293"/>
-      <c r="E50" s="294"/>
+      <c r="C50" s="107"/>
+      <c r="D50" s="107"/>
+      <c r="E50" s="108"/>
       <c r="F50" s="78"/>
-      <c r="G50" s="280"/>
-      <c r="H50" s="281"/>
-      <c r="I50" s="281"/>
-      <c r="J50" s="281"/>
-      <c r="K50" s="281"/>
-      <c r="L50" s="281"/>
-      <c r="M50" s="281"/>
-      <c r="N50" s="281"/>
-      <c r="O50" s="281"/>
-      <c r="P50" s="281"/>
-      <c r="Q50" s="281"/>
-      <c r="R50" s="281"/>
-      <c r="S50" s="281"/>
-      <c r="T50" s="281"/>
-      <c r="U50" s="281"/>
-      <c r="V50" s="281"/>
-      <c r="W50" s="281"/>
-      <c r="X50" s="281"/>
-      <c r="Y50" s="281"/>
-      <c r="Z50" s="281"/>
-      <c r="AA50" s="281"/>
-      <c r="AB50" s="281"/>
-      <c r="AC50" s="281"/>
-      <c r="AD50" s="281"/>
-      <c r="AE50" s="281"/>
-      <c r="AF50" s="282"/>
+      <c r="G50" s="94"/>
+      <c r="H50" s="95"/>
+      <c r="I50" s="95"/>
+      <c r="J50" s="95"/>
+      <c r="K50" s="95"/>
+      <c r="L50" s="95"/>
+      <c r="M50" s="95"/>
+      <c r="N50" s="95"/>
+      <c r="O50" s="95"/>
+      <c r="P50" s="95"/>
+      <c r="Q50" s="95"/>
+      <c r="R50" s="95"/>
+      <c r="S50" s="95"/>
+      <c r="T50" s="95"/>
+      <c r="U50" s="95"/>
+      <c r="V50" s="95"/>
+      <c r="W50" s="95"/>
+      <c r="X50" s="95"/>
+      <c r="Y50" s="95"/>
+      <c r="Z50" s="95"/>
+      <c r="AA50" s="95"/>
+      <c r="AB50" s="95"/>
+      <c r="AC50" s="95"/>
+      <c r="AD50" s="95"/>
+      <c r="AE50" s="95"/>
+      <c r="AF50" s="96"/>
       <c r="AG50" s="76"/>
     </row>
     <row r="51" spans="1:33" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="295" t="s">
+      <c r="A51" s="109" t="s">
         <v>39</v>
       </c>
-      <c r="B51" s="298" t="s">
+      <c r="B51" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="300" t="s">
+      <c r="C51" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D51" s="301"/>
-      <c r="E51" s="302"/>
+      <c r="D51" s="115"/>
+      <c r="E51" s="116"/>
       <c r="F51" s="78"/>
-      <c r="G51" s="280"/>
-      <c r="H51" s="281"/>
-      <c r="I51" s="281"/>
-      <c r="J51" s="281"/>
-      <c r="K51" s="281"/>
-      <c r="L51" s="281"/>
-      <c r="M51" s="281"/>
-      <c r="N51" s="281"/>
-      <c r="O51" s="281"/>
-      <c r="P51" s="281"/>
-      <c r="Q51" s="281"/>
-      <c r="R51" s="281"/>
-      <c r="S51" s="281"/>
-      <c r="T51" s="281"/>
-      <c r="U51" s="281"/>
-      <c r="V51" s="281"/>
-      <c r="W51" s="281"/>
-      <c r="X51" s="281"/>
-      <c r="Y51" s="281"/>
-      <c r="Z51" s="281"/>
-      <c r="AA51" s="281"/>
-      <c r="AB51" s="281"/>
-      <c r="AC51" s="281"/>
-      <c r="AD51" s="281"/>
-      <c r="AE51" s="281"/>
-      <c r="AF51" s="282"/>
+      <c r="G51" s="94"/>
+      <c r="H51" s="95"/>
+      <c r="I51" s="95"/>
+      <c r="J51" s="95"/>
+      <c r="K51" s="95"/>
+      <c r="L51" s="95"/>
+      <c r="M51" s="95"/>
+      <c r="N51" s="95"/>
+      <c r="O51" s="95"/>
+      <c r="P51" s="95"/>
+      <c r="Q51" s="95"/>
+      <c r="R51" s="95"/>
+      <c r="S51" s="95"/>
+      <c r="T51" s="95"/>
+      <c r="U51" s="95"/>
+      <c r="V51" s="95"/>
+      <c r="W51" s="95"/>
+      <c r="X51" s="95"/>
+      <c r="Y51" s="95"/>
+      <c r="Z51" s="95"/>
+      <c r="AA51" s="95"/>
+      <c r="AB51" s="95"/>
+      <c r="AC51" s="95"/>
+      <c r="AD51" s="95"/>
+      <c r="AE51" s="95"/>
+      <c r="AF51" s="96"/>
       <c r="AG51" s="76"/>
     </row>
     <row r="52" spans="1:33" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="296"/>
-      <c r="B52" s="299"/>
-      <c r="C52" s="303"/>
-      <c r="D52" s="304"/>
-      <c r="E52" s="305"/>
+      <c r="A52" s="110"/>
+      <c r="B52" s="113"/>
+      <c r="C52" s="117"/>
+      <c r="D52" s="118"/>
+      <c r="E52" s="119"/>
       <c r="F52" s="78"/>
-      <c r="G52" s="280"/>
-      <c r="H52" s="281"/>
-      <c r="I52" s="281"/>
-      <c r="J52" s="281"/>
-      <c r="K52" s="281"/>
-      <c r="L52" s="281"/>
-      <c r="M52" s="281"/>
-      <c r="N52" s="281"/>
-      <c r="O52" s="281"/>
-      <c r="P52" s="281"/>
-      <c r="Q52" s="281"/>
-      <c r="R52" s="281"/>
-      <c r="S52" s="281"/>
-      <c r="T52" s="281"/>
-      <c r="U52" s="281"/>
-      <c r="V52" s="281"/>
-      <c r="W52" s="281"/>
-      <c r="X52" s="281"/>
-      <c r="Y52" s="281"/>
-      <c r="Z52" s="281"/>
-      <c r="AA52" s="281"/>
-      <c r="AB52" s="281"/>
-      <c r="AC52" s="281"/>
-      <c r="AD52" s="281"/>
-      <c r="AE52" s="281"/>
-      <c r="AF52" s="282"/>
+      <c r="G52" s="94"/>
+      <c r="H52" s="95"/>
+      <c r="I52" s="95"/>
+      <c r="J52" s="95"/>
+      <c r="K52" s="95"/>
+      <c r="L52" s="95"/>
+      <c r="M52" s="95"/>
+      <c r="N52" s="95"/>
+      <c r="O52" s="95"/>
+      <c r="P52" s="95"/>
+      <c r="Q52" s="95"/>
+      <c r="R52" s="95"/>
+      <c r="S52" s="95"/>
+      <c r="T52" s="95"/>
+      <c r="U52" s="95"/>
+      <c r="V52" s="95"/>
+      <c r="W52" s="95"/>
+      <c r="X52" s="95"/>
+      <c r="Y52" s="95"/>
+      <c r="Z52" s="95"/>
+      <c r="AA52" s="95"/>
+      <c r="AB52" s="95"/>
+      <c r="AC52" s="95"/>
+      <c r="AD52" s="95"/>
+      <c r="AE52" s="95"/>
+      <c r="AF52" s="96"/>
       <c r="AG52" s="76"/>
     </row>
     <row r="53" spans="1:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="296"/>
-      <c r="B53" s="298" t="s">
+      <c r="A53" s="110"/>
+      <c r="B53" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="300" t="s">
+      <c r="C53" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="D53" s="301"/>
-      <c r="E53" s="302"/>
+      <c r="D53" s="115"/>
+      <c r="E53" s="116"/>
       <c r="F53" s="78"/>
-      <c r="G53" s="280"/>
-      <c r="H53" s="281"/>
-      <c r="I53" s="281"/>
-      <c r="J53" s="281"/>
-      <c r="K53" s="281"/>
-      <c r="L53" s="281"/>
-      <c r="M53" s="281"/>
-      <c r="N53" s="281"/>
-      <c r="O53" s="281"/>
-      <c r="P53" s="281"/>
-      <c r="Q53" s="281"/>
-      <c r="R53" s="281"/>
-      <c r="S53" s="281"/>
-      <c r="T53" s="281"/>
-      <c r="U53" s="281"/>
-      <c r="V53" s="281"/>
-      <c r="W53" s="281"/>
-      <c r="X53" s="281"/>
-      <c r="Y53" s="281"/>
-      <c r="Z53" s="281"/>
-      <c r="AA53" s="281"/>
-      <c r="AB53" s="281"/>
-      <c r="AC53" s="281"/>
-      <c r="AD53" s="281"/>
-      <c r="AE53" s="281"/>
-      <c r="AF53" s="282"/>
+      <c r="G53" s="94"/>
+      <c r="H53" s="95"/>
+      <c r="I53" s="95"/>
+      <c r="J53" s="95"/>
+      <c r="K53" s="95"/>
+      <c r="L53" s="95"/>
+      <c r="M53" s="95"/>
+      <c r="N53" s="95"/>
+      <c r="O53" s="95"/>
+      <c r="P53" s="95"/>
+      <c r="Q53" s="95"/>
+      <c r="R53" s="95"/>
+      <c r="S53" s="95"/>
+      <c r="T53" s="95"/>
+      <c r="U53" s="95"/>
+      <c r="V53" s="95"/>
+      <c r="W53" s="95"/>
+      <c r="X53" s="95"/>
+      <c r="Y53" s="95"/>
+      <c r="Z53" s="95"/>
+      <c r="AA53" s="95"/>
+      <c r="AB53" s="95"/>
+      <c r="AC53" s="95"/>
+      <c r="AD53" s="95"/>
+      <c r="AE53" s="95"/>
+      <c r="AF53" s="96"/>
       <c r="AG53" s="76"/>
     </row>
     <row r="54" spans="1:33" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="296"/>
-      <c r="B54" s="306"/>
-      <c r="C54" s="303"/>
-      <c r="D54" s="304"/>
-      <c r="E54" s="305"/>
+      <c r="A54" s="110"/>
+      <c r="B54" s="120"/>
+      <c r="C54" s="117"/>
+      <c r="D54" s="118"/>
+      <c r="E54" s="119"/>
       <c r="F54" s="78"/>
-      <c r="G54" s="283" t="s">
+      <c r="G54" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="H54" s="284"/>
-      <c r="I54" s="284"/>
-      <c r="J54" s="284"/>
-      <c r="K54" s="284"/>
-      <c r="L54" s="284"/>
-      <c r="M54" s="284"/>
-      <c r="N54" s="284"/>
-      <c r="O54" s="284"/>
-      <c r="P54" s="284"/>
-      <c r="Q54" s="284"/>
-      <c r="R54" s="284"/>
-      <c r="S54" s="284"/>
-      <c r="T54" s="284"/>
-      <c r="U54" s="284"/>
-      <c r="V54" s="284"/>
-      <c r="W54" s="284"/>
-      <c r="X54" s="284"/>
-      <c r="Y54" s="284"/>
-      <c r="Z54" s="284"/>
-      <c r="AA54" s="284"/>
-      <c r="AB54" s="284"/>
-      <c r="AC54" s="284"/>
-      <c r="AD54" s="284"/>
-      <c r="AE54" s="284"/>
-      <c r="AF54" s="285"/>
+      <c r="H54" s="98"/>
+      <c r="I54" s="98"/>
+      <c r="J54" s="98"/>
+      <c r="K54" s="98"/>
+      <c r="L54" s="98"/>
+      <c r="M54" s="98"/>
+      <c r="N54" s="98"/>
+      <c r="O54" s="98"/>
+      <c r="P54" s="98"/>
+      <c r="Q54" s="98"/>
+      <c r="R54" s="98"/>
+      <c r="S54" s="98"/>
+      <c r="T54" s="98"/>
+      <c r="U54" s="98"/>
+      <c r="V54" s="98"/>
+      <c r="W54" s="98"/>
+      <c r="X54" s="98"/>
+      <c r="Y54" s="98"/>
+      <c r="Z54" s="98"/>
+      <c r="AA54" s="98"/>
+      <c r="AB54" s="98"/>
+      <c r="AC54" s="98"/>
+      <c r="AD54" s="98"/>
+      <c r="AE54" s="98"/>
+      <c r="AF54" s="99"/>
       <c r="AG54" s="76"/>
     </row>
     <row r="55" spans="1:33" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="296"/>
-      <c r="B55" s="307" t="s">
+      <c r="A55" s="110"/>
+      <c r="B55" s="121" t="s">
         <v>44</v>
       </c>
-      <c r="C55" s="309" t="s">
+      <c r="C55" s="123" t="s">
         <v>45</v>
       </c>
-      <c r="D55" s="310"/>
-      <c r="E55" s="311"/>
+      <c r="D55" s="124"/>
+      <c r="E55" s="125"/>
       <c r="F55" s="78"/>
-      <c r="G55" s="286"/>
-      <c r="H55" s="287"/>
-      <c r="I55" s="287"/>
-      <c r="J55" s="287"/>
-      <c r="K55" s="287"/>
-      <c r="L55" s="287"/>
-      <c r="M55" s="287"/>
-      <c r="N55" s="287"/>
-      <c r="O55" s="287"/>
-      <c r="P55" s="287"/>
-      <c r="Q55" s="287"/>
-      <c r="R55" s="287"/>
-      <c r="S55" s="287"/>
-      <c r="T55" s="287"/>
-      <c r="U55" s="287"/>
-      <c r="V55" s="287"/>
-      <c r="W55" s="287"/>
-      <c r="X55" s="287"/>
-      <c r="Y55" s="287"/>
-      <c r="Z55" s="287"/>
-      <c r="AA55" s="287"/>
-      <c r="AB55" s="287"/>
-      <c r="AC55" s="287"/>
-      <c r="AD55" s="287"/>
-      <c r="AE55" s="287"/>
-      <c r="AF55" s="288"/>
+      <c r="G55" s="100"/>
+      <c r="H55" s="101"/>
+      <c r="I55" s="101"/>
+      <c r="J55" s="101"/>
+      <c r="K55" s="101"/>
+      <c r="L55" s="101"/>
+      <c r="M55" s="101"/>
+      <c r="N55" s="101"/>
+      <c r="O55" s="101"/>
+      <c r="P55" s="101"/>
+      <c r="Q55" s="101"/>
+      <c r="R55" s="101"/>
+      <c r="S55" s="101"/>
+      <c r="T55" s="101"/>
+      <c r="U55" s="101"/>
+      <c r="V55" s="101"/>
+      <c r="W55" s="101"/>
+      <c r="X55" s="101"/>
+      <c r="Y55" s="101"/>
+      <c r="Z55" s="101"/>
+      <c r="AA55" s="101"/>
+      <c r="AB55" s="101"/>
+      <c r="AC55" s="101"/>
+      <c r="AD55" s="101"/>
+      <c r="AE55" s="101"/>
+      <c r="AF55" s="102"/>
       <c r="AG55" s="76"/>
     </row>
     <row r="56" spans="1:33" ht="30.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="297"/>
-      <c r="B56" s="308"/>
-      <c r="C56" s="303"/>
-      <c r="D56" s="304"/>
-      <c r="E56" s="305"/>
+      <c r="A56" s="111"/>
+      <c r="B56" s="122"/>
+      <c r="C56" s="117"/>
+      <c r="D56" s="118"/>
+      <c r="E56" s="119"/>
       <c r="F56" s="80"/>
-      <c r="G56" s="289" t="s">
+      <c r="G56" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="H56" s="290"/>
-      <c r="I56" s="290"/>
-      <c r="J56" s="290"/>
-      <c r="K56" s="290"/>
-      <c r="L56" s="290"/>
-      <c r="M56" s="290"/>
-      <c r="N56" s="290"/>
-      <c r="O56" s="290"/>
-      <c r="P56" s="290"/>
-      <c r="Q56" s="290"/>
-      <c r="R56" s="290"/>
-      <c r="S56" s="290"/>
-      <c r="T56" s="290"/>
-      <c r="U56" s="290"/>
-      <c r="V56" s="290"/>
-      <c r="W56" s="290"/>
-      <c r="X56" s="290"/>
-      <c r="Y56" s="290"/>
-      <c r="Z56" s="290"/>
-      <c r="AA56" s="290"/>
-      <c r="AB56" s="290"/>
-      <c r="AC56" s="290"/>
-      <c r="AD56" s="290"/>
-      <c r="AE56" s="290"/>
-      <c r="AF56" s="291"/>
+      <c r="H56" s="104"/>
+      <c r="I56" s="104"/>
+      <c r="J56" s="104"/>
+      <c r="K56" s="104"/>
+      <c r="L56" s="104"/>
+      <c r="M56" s="104"/>
+      <c r="N56" s="104"/>
+      <c r="O56" s="104"/>
+      <c r="P56" s="104"/>
+      <c r="Q56" s="104"/>
+      <c r="R56" s="104"/>
+      <c r="S56" s="104"/>
+      <c r="T56" s="104"/>
+      <c r="U56" s="104"/>
+      <c r="V56" s="104"/>
+      <c r="W56" s="104"/>
+      <c r="X56" s="104"/>
+      <c r="Y56" s="104"/>
+      <c r="Z56" s="104"/>
+      <c r="AA56" s="104"/>
+      <c r="AB56" s="104"/>
+      <c r="AC56" s="104"/>
+      <c r="AD56" s="104"/>
+      <c r="AE56" s="104"/>
+      <c r="AF56" s="105"/>
     </row>
     <row r="57" spans="1:33" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="81" t="s">
@@ -5635,27 +5635,57 @@
       <c r="AF57" s="82"/>
     </row>
   </sheetData>
-  <mergeCells count="110">
-    <mergeCell ref="G49:AF53"/>
-    <mergeCell ref="G54:AF55"/>
-    <mergeCell ref="G56:AF56"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="A51:A56"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:E52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:E54"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:E56"/>
-    <mergeCell ref="A40:A47"/>
-    <mergeCell ref="B40:F41"/>
-    <mergeCell ref="G47:AF47"/>
-    <mergeCell ref="A31:A38"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="G36:AF36"/>
-    <mergeCell ref="B31:F31"/>
+  <mergeCells count="109">
+    <mergeCell ref="Q42:AF42"/>
+    <mergeCell ref="U43:AF43"/>
+    <mergeCell ref="B46:F47"/>
+    <mergeCell ref="G46:AF46"/>
+    <mergeCell ref="T35:AF35"/>
+    <mergeCell ref="B37:F38"/>
+    <mergeCell ref="G37:AF37"/>
+    <mergeCell ref="G40:P41"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="S41:W41"/>
+    <mergeCell ref="G38:AF38"/>
+    <mergeCell ref="B28:F29"/>
+    <mergeCell ref="G28:AF28"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="J23:Q23"/>
+    <mergeCell ref="T23:AF23"/>
+    <mergeCell ref="G24:AF25"/>
+    <mergeCell ref="M26:U26"/>
+    <mergeCell ref="AA26:AF26"/>
+    <mergeCell ref="O27:U27"/>
+    <mergeCell ref="Y27:AF27"/>
+    <mergeCell ref="B22:F23"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:AF22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="H19:L19"/>
+    <mergeCell ref="O19:AF19"/>
+    <mergeCell ref="G20:T21"/>
+    <mergeCell ref="U21:X21"/>
+    <mergeCell ref="Y21:AF21"/>
+    <mergeCell ref="G16:P16"/>
+    <mergeCell ref="T9:W10"/>
+    <mergeCell ref="X9:AF10"/>
+    <mergeCell ref="G8:S8"/>
+    <mergeCell ref="G9:S10"/>
+    <mergeCell ref="U18:AF18"/>
+    <mergeCell ref="A8:C12"/>
+    <mergeCell ref="X7:AF8"/>
+    <mergeCell ref="T7:W8"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="G14:P14"/>
+    <mergeCell ref="Q14:V14"/>
+    <mergeCell ref="W14:AF14"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="X12:AF12"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:M11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:R12"/>
     <mergeCell ref="AD1:AF2"/>
     <mergeCell ref="C3:X4"/>
     <mergeCell ref="A13:F13"/>
@@ -5680,46 +5710,15 @@
     <mergeCell ref="G18:P18"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D8:F8"/>
-    <mergeCell ref="A8:C12"/>
-    <mergeCell ref="X7:AF8"/>
-    <mergeCell ref="T7:W8"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="G14:P14"/>
-    <mergeCell ref="Q14:V14"/>
-    <mergeCell ref="W14:AF14"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="X12:AF12"/>
-    <mergeCell ref="G13:AF13"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:M11"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:R12"/>
-    <mergeCell ref="H19:L19"/>
-    <mergeCell ref="O19:AF19"/>
-    <mergeCell ref="G20:T21"/>
-    <mergeCell ref="U21:X21"/>
-    <mergeCell ref="Y21:AF21"/>
-    <mergeCell ref="G16:P16"/>
-    <mergeCell ref="T9:W10"/>
-    <mergeCell ref="X9:AF10"/>
-    <mergeCell ref="G8:S8"/>
-    <mergeCell ref="G9:S10"/>
-    <mergeCell ref="U18:AF18"/>
-    <mergeCell ref="B28:F29"/>
-    <mergeCell ref="G28:AF28"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="J23:Q23"/>
-    <mergeCell ref="T23:AF23"/>
-    <mergeCell ref="G24:AF25"/>
-    <mergeCell ref="M26:U26"/>
-    <mergeCell ref="AA26:AF26"/>
-    <mergeCell ref="O27:U27"/>
-    <mergeCell ref="Y27:AF27"/>
-    <mergeCell ref="B22:F23"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:AF22"/>
-    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="A40:A47"/>
+    <mergeCell ref="B40:F41"/>
+    <mergeCell ref="G47:AF47"/>
+    <mergeCell ref="A31:A38"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="G36:AF36"/>
+    <mergeCell ref="B31:F31"/>
     <mergeCell ref="G34:H34"/>
     <mergeCell ref="I34:N34"/>
     <mergeCell ref="G35:H35"/>
@@ -5735,17 +5734,17 @@
     <mergeCell ref="W33:AF33"/>
     <mergeCell ref="B42:F43"/>
     <mergeCell ref="G42:P43"/>
-    <mergeCell ref="Q42:AF42"/>
-    <mergeCell ref="U43:AF43"/>
-    <mergeCell ref="B46:F47"/>
-    <mergeCell ref="G46:AF46"/>
-    <mergeCell ref="T35:AF35"/>
-    <mergeCell ref="B37:F38"/>
-    <mergeCell ref="G37:AF37"/>
-    <mergeCell ref="G40:P41"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="S41:W41"/>
-    <mergeCell ref="G38:AF38"/>
+    <mergeCell ref="G49:AF53"/>
+    <mergeCell ref="G54:AF55"/>
+    <mergeCell ref="G56:AF56"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="A51:A56"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:E52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:E54"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:E56"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/templates/forms/LTC_Certification_Change_R8.4-.xlsx
+++ b/templates/forms/LTC_Certification_Change_R8.4-.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CareManagementTool\templates\forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8D6C8A-A091-4453-96DE-FDDC9866047F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A10F265-5AEF-4A9B-8FB5-C87C9EC35D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2158,7 +2158,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="319">
+  <cellXfs count="316">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2380,6 +2380,567 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -2485,584 +3046,14 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -3519,9 +3510,9 @@
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
-      <c r="AD1" s="150"/>
-      <c r="AE1" s="150"/>
-      <c r="AF1" s="150"/>
+      <c r="AD1" s="194"/>
+      <c r="AE1" s="194"/>
+      <c r="AF1" s="194"/>
     </row>
     <row r="2" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
@@ -3548,62 +3539,62 @@
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
-      <c r="AD2" s="150"/>
-      <c r="AE2" s="150"/>
-      <c r="AF2" s="150"/>
+      <c r="AD2" s="194"/>
+      <c r="AE2" s="194"/>
+      <c r="AF2" s="194"/>
     </row>
     <row r="3" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C3" s="151" t="s">
+      <c r="C3" s="195" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="151"/>
-      <c r="E3" s="151"/>
-      <c r="F3" s="151"/>
-      <c r="G3" s="151"/>
-      <c r="H3" s="151"/>
-      <c r="I3" s="151"/>
-      <c r="J3" s="151"/>
-      <c r="K3" s="151"/>
-      <c r="L3" s="151"/>
-      <c r="M3" s="151"/>
-      <c r="N3" s="151"/>
-      <c r="O3" s="151"/>
-      <c r="P3" s="151"/>
-      <c r="Q3" s="151"/>
-      <c r="R3" s="151"/>
-      <c r="S3" s="151"/>
-      <c r="T3" s="151"/>
-      <c r="U3" s="151"/>
-      <c r="V3" s="151"/>
-      <c r="W3" s="151"/>
-      <c r="X3" s="151"/>
+      <c r="D3" s="195"/>
+      <c r="E3" s="195"/>
+      <c r="F3" s="195"/>
+      <c r="G3" s="195"/>
+      <c r="H3" s="195"/>
+      <c r="I3" s="195"/>
+      <c r="J3" s="195"/>
+      <c r="K3" s="195"/>
+      <c r="L3" s="195"/>
+      <c r="M3" s="195"/>
+      <c r="N3" s="195"/>
+      <c r="O3" s="195"/>
+      <c r="P3" s="195"/>
+      <c r="Q3" s="195"/>
+      <c r="R3" s="195"/>
+      <c r="S3" s="195"/>
+      <c r="T3" s="195"/>
+      <c r="U3" s="195"/>
+      <c r="V3" s="195"/>
+      <c r="W3" s="195"/>
+      <c r="X3" s="195"/>
       <c r="AD3" s="5"/>
       <c r="AE3" s="5"/>
       <c r="AF3" s="5"/>
     </row>
     <row r="4" spans="1:37" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C4" s="151"/>
-      <c r="D4" s="151"/>
-      <c r="E4" s="151"/>
-      <c r="F4" s="151"/>
-      <c r="G4" s="151"/>
-      <c r="H4" s="151"/>
-      <c r="I4" s="151"/>
-      <c r="J4" s="151"/>
-      <c r="K4" s="151"/>
-      <c r="L4" s="151"/>
-      <c r="M4" s="151"/>
-      <c r="N4" s="151"/>
-      <c r="O4" s="151"/>
-      <c r="P4" s="151"/>
-      <c r="Q4" s="151"/>
-      <c r="R4" s="151"/>
-      <c r="S4" s="151"/>
-      <c r="T4" s="151"/>
-      <c r="U4" s="151"/>
-      <c r="V4" s="151"/>
-      <c r="W4" s="151"/>
-      <c r="X4" s="151"/>
+      <c r="C4" s="195"/>
+      <c r="D4" s="195"/>
+      <c r="E4" s="195"/>
+      <c r="F4" s="195"/>
+      <c r="G4" s="195"/>
+      <c r="H4" s="195"/>
+      <c r="I4" s="195"/>
+      <c r="J4" s="195"/>
+      <c r="K4" s="195"/>
+      <c r="L4" s="195"/>
+      <c r="M4" s="195"/>
+      <c r="N4" s="195"/>
+      <c r="O4" s="195"/>
+      <c r="P4" s="195"/>
+      <c r="Q4" s="195"/>
+      <c r="R4" s="195"/>
+      <c r="S4" s="195"/>
+      <c r="T4" s="195"/>
+      <c r="U4" s="195"/>
+      <c r="V4" s="195"/>
+      <c r="W4" s="195"/>
+      <c r="X4" s="195"/>
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
       <c r="AC4" s="7"/>
@@ -3704,164 +3695,164 @@
       <c r="Q7" s="20"/>
       <c r="R7" s="20"/>
       <c r="S7" s="21"/>
-      <c r="T7" s="216" t="s">
+      <c r="T7" s="115" t="s">
         <v>5</v>
       </c>
-      <c r="U7" s="216"/>
-      <c r="V7" s="216"/>
-      <c r="W7" s="217"/>
-      <c r="X7" s="210"/>
-      <c r="Y7" s="211"/>
-      <c r="Z7" s="211"/>
-      <c r="AA7" s="211"/>
-      <c r="AB7" s="211"/>
-      <c r="AC7" s="211"/>
-      <c r="AD7" s="211"/>
-      <c r="AE7" s="211"/>
-      <c r="AF7" s="212"/>
+      <c r="U7" s="115"/>
+      <c r="V7" s="115"/>
+      <c r="W7" s="116"/>
+      <c r="X7" s="174"/>
+      <c r="Y7" s="175"/>
+      <c r="Z7" s="175"/>
+      <c r="AA7" s="175"/>
+      <c r="AB7" s="175"/>
+      <c r="AC7" s="175"/>
+      <c r="AD7" s="175"/>
+      <c r="AE7" s="175"/>
+      <c r="AF7" s="176"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="83"/>
     </row>
     <row r="8" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="204" t="s">
+      <c r="A8" s="165" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="130"/>
-      <c r="C8" s="205"/>
-      <c r="D8" s="202" t="s">
+      <c r="B8" s="166"/>
+      <c r="C8" s="167"/>
+      <c r="D8" s="235" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="203"/>
-      <c r="F8" s="203"/>
-      <c r="G8" s="243"/>
-      <c r="H8" s="244"/>
-      <c r="I8" s="244"/>
-      <c r="J8" s="244"/>
-      <c r="K8" s="244"/>
-      <c r="L8" s="244"/>
-      <c r="M8" s="244"/>
-      <c r="N8" s="244"/>
-      <c r="O8" s="244"/>
-      <c r="P8" s="244"/>
-      <c r="Q8" s="244"/>
-      <c r="R8" s="244"/>
-      <c r="S8" s="245"/>
-      <c r="T8" s="131"/>
-      <c r="U8" s="131"/>
-      <c r="V8" s="131"/>
-      <c r="W8" s="218"/>
-      <c r="X8" s="213"/>
-      <c r="Y8" s="214"/>
-      <c r="Z8" s="214"/>
-      <c r="AA8" s="214"/>
-      <c r="AB8" s="214"/>
-      <c r="AC8" s="214"/>
-      <c r="AD8" s="214"/>
-      <c r="AE8" s="214"/>
-      <c r="AF8" s="215"/>
+      <c r="E8" s="236"/>
+      <c r="F8" s="236"/>
+      <c r="G8" s="158"/>
+      <c r="H8" s="159"/>
+      <c r="I8" s="159"/>
+      <c r="J8" s="159"/>
+      <c r="K8" s="159"/>
+      <c r="L8" s="159"/>
+      <c r="M8" s="159"/>
+      <c r="N8" s="159"/>
+      <c r="O8" s="159"/>
+      <c r="P8" s="159"/>
+      <c r="Q8" s="159"/>
+      <c r="R8" s="159"/>
+      <c r="S8" s="160"/>
+      <c r="T8" s="118"/>
+      <c r="U8" s="118"/>
+      <c r="V8" s="118"/>
+      <c r="W8" s="119"/>
+      <c r="X8" s="177"/>
+      <c r="Y8" s="178"/>
+      <c r="Z8" s="178"/>
+      <c r="AA8" s="178"/>
+      <c r="AB8" s="178"/>
+      <c r="AC8" s="178"/>
+      <c r="AD8" s="178"/>
+      <c r="AE8" s="178"/>
+      <c r="AF8" s="179"/>
       <c r="AI8" s="3"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="83"/>
     </row>
     <row r="9" spans="1:37" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="206"/>
-      <c r="B9" s="207"/>
-      <c r="C9" s="208"/>
-      <c r="D9" s="226" t="s">
+      <c r="A9" s="168"/>
+      <c r="B9" s="169"/>
+      <c r="C9" s="170"/>
+      <c r="D9" s="187" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="227"/>
-      <c r="F9" s="227"/>
-      <c r="G9" s="246"/>
-      <c r="H9" s="246"/>
-      <c r="I9" s="246"/>
-      <c r="J9" s="246"/>
-      <c r="K9" s="246"/>
-      <c r="L9" s="246"/>
-      <c r="M9" s="246"/>
-      <c r="N9" s="246"/>
-      <c r="O9" s="246"/>
-      <c r="P9" s="246"/>
-      <c r="Q9" s="246"/>
-      <c r="R9" s="246"/>
-      <c r="S9" s="246"/>
-      <c r="T9" s="241" t="s">
+      <c r="E9" s="188"/>
+      <c r="F9" s="188"/>
+      <c r="G9" s="161"/>
+      <c r="H9" s="161"/>
+      <c r="I9" s="161"/>
+      <c r="J9" s="161"/>
+      <c r="K9" s="161"/>
+      <c r="L9" s="161"/>
+      <c r="M9" s="161"/>
+      <c r="N9" s="161"/>
+      <c r="O9" s="161"/>
+      <c r="P9" s="161"/>
+      <c r="Q9" s="161"/>
+      <c r="R9" s="161"/>
+      <c r="S9" s="161"/>
+      <c r="T9" s="156" t="s">
         <v>8</v>
       </c>
-      <c r="U9" s="241"/>
-      <c r="V9" s="241"/>
-      <c r="W9" s="241"/>
-      <c r="X9" s="242"/>
-      <c r="Y9" s="242"/>
-      <c r="Z9" s="242"/>
-      <c r="AA9" s="242"/>
-      <c r="AB9" s="242"/>
-      <c r="AC9" s="242"/>
-      <c r="AD9" s="242"/>
-      <c r="AE9" s="242"/>
-      <c r="AF9" s="242"/>
+      <c r="U9" s="156"/>
+      <c r="V9" s="156"/>
+      <c r="W9" s="156"/>
+      <c r="X9" s="157"/>
+      <c r="Y9" s="157"/>
+      <c r="Z9" s="157"/>
+      <c r="AA9" s="157"/>
+      <c r="AB9" s="157"/>
+      <c r="AC9" s="157"/>
+      <c r="AD9" s="157"/>
+      <c r="AE9" s="157"/>
+      <c r="AF9" s="157"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="22"/>
       <c r="AK9" s="22"/>
     </row>
     <row r="10" spans="1:37" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="206"/>
-      <c r="B10" s="207"/>
-      <c r="C10" s="208"/>
-      <c r="D10" s="199" t="s">
+      <c r="A10" s="168"/>
+      <c r="B10" s="169"/>
+      <c r="C10" s="170"/>
+      <c r="D10" s="191" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="200"/>
-      <c r="F10" s="201"/>
-      <c r="G10" s="246"/>
-      <c r="H10" s="246"/>
-      <c r="I10" s="246"/>
-      <c r="J10" s="246"/>
-      <c r="K10" s="246"/>
-      <c r="L10" s="246"/>
-      <c r="M10" s="246"/>
-      <c r="N10" s="246"/>
-      <c r="O10" s="246"/>
-      <c r="P10" s="246"/>
-      <c r="Q10" s="246"/>
-      <c r="R10" s="246"/>
-      <c r="S10" s="246"/>
-      <c r="T10" s="241"/>
-      <c r="U10" s="241"/>
-      <c r="V10" s="241"/>
-      <c r="W10" s="241"/>
-      <c r="X10" s="242"/>
-      <c r="Y10" s="242"/>
-      <c r="Z10" s="242"/>
-      <c r="AA10" s="242"/>
-      <c r="AB10" s="242"/>
-      <c r="AC10" s="242"/>
-      <c r="AD10" s="242"/>
-      <c r="AE10" s="242"/>
-      <c r="AF10" s="242"/>
+      <c r="E10" s="233"/>
+      <c r="F10" s="234"/>
+      <c r="G10" s="161"/>
+      <c r="H10" s="161"/>
+      <c r="I10" s="161"/>
+      <c r="J10" s="161"/>
+      <c r="K10" s="161"/>
+      <c r="L10" s="161"/>
+      <c r="M10" s="161"/>
+      <c r="N10" s="161"/>
+      <c r="O10" s="161"/>
+      <c r="P10" s="161"/>
+      <c r="Q10" s="161"/>
+      <c r="R10" s="161"/>
+      <c r="S10" s="161"/>
+      <c r="T10" s="156"/>
+      <c r="U10" s="156"/>
+      <c r="V10" s="156"/>
+      <c r="W10" s="156"/>
+      <c r="X10" s="157"/>
+      <c r="Y10" s="157"/>
+      <c r="Z10" s="157"/>
+      <c r="AA10" s="157"/>
+      <c r="AB10" s="157"/>
+      <c r="AC10" s="157"/>
+      <c r="AD10" s="157"/>
+      <c r="AE10" s="157"/>
+      <c r="AF10" s="157"/>
       <c r="AI10" s="3"/>
       <c r="AJ10" s="22"/>
       <c r="AK10" s="22"/>
     </row>
     <row r="11" spans="1:37" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="206"/>
-      <c r="B11" s="207"/>
-      <c r="C11" s="208"/>
-      <c r="D11" s="226" t="s">
+      <c r="A11" s="168"/>
+      <c r="B11" s="169"/>
+      <c r="C11" s="170"/>
+      <c r="D11" s="187" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="229"/>
-      <c r="F11" s="230"/>
-      <c r="G11" s="231" t="s">
+      <c r="E11" s="189"/>
+      <c r="F11" s="190"/>
+      <c r="G11" s="120" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="232"/>
-      <c r="I11" s="232"/>
-      <c r="J11" s="232"/>
-      <c r="K11" s="232"/>
-      <c r="L11" s="232"/>
-      <c r="M11" s="232"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="121"/>
+      <c r="K11" s="121"/>
+      <c r="L11" s="121"/>
+      <c r="M11" s="121"/>
       <c r="N11" s="36" t="s">
         <v>62</v>
       </c>
@@ -3886,26 +3877,26 @@
       <c r="AK11" s="22"/>
     </row>
     <row r="12" spans="1:37" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="209"/>
-      <c r="B12" s="179"/>
-      <c r="C12" s="180"/>
-      <c r="D12" s="199" t="s">
+      <c r="A12" s="171"/>
+      <c r="B12" s="172"/>
+      <c r="C12" s="173"/>
+      <c r="D12" s="191" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="233"/>
-      <c r="F12" s="234"/>
-      <c r="G12" s="235"/>
-      <c r="H12" s="131"/>
-      <c r="I12" s="131"/>
-      <c r="J12" s="131"/>
-      <c r="K12" s="131"/>
-      <c r="L12" s="131"/>
-      <c r="M12" s="131"/>
-      <c r="N12" s="131"/>
-      <c r="O12" s="131"/>
-      <c r="P12" s="131"/>
-      <c r="Q12" s="131"/>
-      <c r="R12" s="131"/>
+      <c r="E12" s="192"/>
+      <c r="F12" s="193"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="118"/>
+      <c r="J12" s="118"/>
+      <c r="K12" s="118"/>
+      <c r="L12" s="118"/>
+      <c r="M12" s="118"/>
+      <c r="N12" s="118"/>
+      <c r="O12" s="118"/>
+      <c r="P12" s="118"/>
+      <c r="Q12" s="118"/>
+      <c r="R12" s="118"/>
       <c r="S12" s="74"/>
       <c r="T12" s="74"/>
       <c r="U12" s="74" t="s">
@@ -3913,92 +3904,92 @@
       </c>
       <c r="V12" s="74"/>
       <c r="W12" s="74"/>
-      <c r="X12" s="131"/>
-      <c r="Y12" s="131"/>
-      <c r="Z12" s="131"/>
-      <c r="AA12" s="131"/>
-      <c r="AB12" s="131"/>
-      <c r="AC12" s="131"/>
-      <c r="AD12" s="131"/>
-      <c r="AE12" s="131"/>
-      <c r="AF12" s="228"/>
+      <c r="X12" s="118"/>
+      <c r="Y12" s="118"/>
+      <c r="Z12" s="118"/>
+      <c r="AA12" s="118"/>
+      <c r="AB12" s="118"/>
+      <c r="AC12" s="118"/>
+      <c r="AD12" s="118"/>
+      <c r="AE12" s="118"/>
+      <c r="AF12" s="152"/>
       <c r="AK12" s="22"/>
     </row>
     <row r="13" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="152" t="s">
+      <c r="A13" s="196" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="153"/>
-      <c r="C13" s="153"/>
-      <c r="D13" s="153"/>
-      <c r="E13" s="153"/>
-      <c r="F13" s="154"/>
-      <c r="G13" s="316" t="s">
+      <c r="B13" s="197"/>
+      <c r="C13" s="197"/>
+      <c r="D13" s="197"/>
+      <c r="E13" s="197"/>
+      <c r="F13" s="198"/>
+      <c r="G13" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="H13" s="317"/>
-      <c r="I13" s="317"/>
-      <c r="J13" s="317"/>
-      <c r="K13" s="317"/>
-      <c r="L13" s="317"/>
-      <c r="M13" s="317"/>
-      <c r="N13" s="317"/>
-      <c r="O13" s="317"/>
-      <c r="P13" s="317"/>
-      <c r="Q13" s="317"/>
-      <c r="R13" s="317"/>
-      <c r="S13" s="317"/>
-      <c r="T13" s="317"/>
-      <c r="U13" s="317"/>
-      <c r="V13" s="317"/>
-      <c r="W13" s="317"/>
-      <c r="X13" s="317"/>
-      <c r="Y13" s="317"/>
-      <c r="Z13" s="317"/>
-      <c r="AA13" s="317"/>
-      <c r="AB13" s="317"/>
-      <c r="AC13" s="317"/>
-      <c r="AD13" s="317"/>
-      <c r="AE13" s="317"/>
-      <c r="AF13" s="318"/>
+      <c r="H13" s="92"/>
+      <c r="I13" s="92"/>
+      <c r="J13" s="92"/>
+      <c r="K13" s="92"/>
+      <c r="L13" s="92"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="92"/>
+      <c r="O13" s="92"/>
+      <c r="P13" s="92"/>
+      <c r="Q13" s="92"/>
+      <c r="R13" s="92"/>
+      <c r="S13" s="92"/>
+      <c r="T13" s="92"/>
+      <c r="U13" s="92"/>
+      <c r="V13" s="92"/>
+      <c r="W13" s="92"/>
+      <c r="X13" s="92"/>
+      <c r="Y13" s="92"/>
+      <c r="Z13" s="92"/>
+      <c r="AA13" s="92"/>
+      <c r="AB13" s="92"/>
+      <c r="AC13" s="92"/>
+      <c r="AD13" s="92"/>
+      <c r="AE13" s="92"/>
+      <c r="AF13" s="93"/>
     </row>
     <row r="14" spans="1:37" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="219" t="s">
+      <c r="A14" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="220"/>
-      <c r="C14" s="220"/>
-      <c r="D14" s="220"/>
-      <c r="E14" s="220"/>
-      <c r="F14" s="221"/>
-      <c r="G14" s="222"/>
-      <c r="H14" s="220"/>
-      <c r="I14" s="220"/>
-      <c r="J14" s="220"/>
-      <c r="K14" s="220"/>
-      <c r="L14" s="220"/>
-      <c r="M14" s="220"/>
-      <c r="N14" s="220"/>
-      <c r="O14" s="220"/>
-      <c r="P14" s="221"/>
-      <c r="Q14" s="222" t="s">
+      <c r="B14" s="181"/>
+      <c r="C14" s="181"/>
+      <c r="D14" s="181"/>
+      <c r="E14" s="181"/>
+      <c r="F14" s="182"/>
+      <c r="G14" s="183"/>
+      <c r="H14" s="181"/>
+      <c r="I14" s="181"/>
+      <c r="J14" s="181"/>
+      <c r="K14" s="181"/>
+      <c r="L14" s="181"/>
+      <c r="M14" s="181"/>
+      <c r="N14" s="181"/>
+      <c r="O14" s="181"/>
+      <c r="P14" s="182"/>
+      <c r="Q14" s="183" t="s">
         <v>12</v>
       </c>
-      <c r="R14" s="220"/>
-      <c r="S14" s="220"/>
-      <c r="T14" s="220"/>
-      <c r="U14" s="220"/>
-      <c r="V14" s="221"/>
-      <c r="W14" s="223"/>
-      <c r="X14" s="224"/>
-      <c r="Y14" s="224"/>
-      <c r="Z14" s="224"/>
-      <c r="AA14" s="224"/>
-      <c r="AB14" s="224"/>
-      <c r="AC14" s="224"/>
-      <c r="AD14" s="224"/>
-      <c r="AE14" s="224"/>
-      <c r="AF14" s="225"/>
+      <c r="R14" s="181"/>
+      <c r="S14" s="181"/>
+      <c r="T14" s="181"/>
+      <c r="U14" s="181"/>
+      <c r="V14" s="182"/>
+      <c r="W14" s="184"/>
+      <c r="X14" s="185"/>
+      <c r="Y14" s="185"/>
+      <c r="Z14" s="185"/>
+      <c r="AA14" s="185"/>
+      <c r="AB14" s="185"/>
+      <c r="AC14" s="185"/>
+      <c r="AD14" s="185"/>
+      <c r="AE14" s="185"/>
+      <c r="AF14" s="186"/>
     </row>
     <row r="15" spans="1:37" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="19"/>
@@ -4037,32 +4028,32 @@
       <c r="AK15" s="26"/>
     </row>
     <row r="16" spans="1:37" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="157" t="s">
+      <c r="A16" s="202" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="160" t="s">
+      <c r="B16" s="205" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="161"/>
-      <c r="D16" s="161"/>
-      <c r="E16" s="161"/>
-      <c r="F16" s="162"/>
-      <c r="G16" s="193"/>
-      <c r="H16" s="194"/>
-      <c r="I16" s="194"/>
-      <c r="J16" s="194"/>
-      <c r="K16" s="194"/>
-      <c r="L16" s="194"/>
-      <c r="M16" s="194"/>
-      <c r="N16" s="194"/>
-      <c r="O16" s="194"/>
-      <c r="P16" s="195"/>
-      <c r="Q16" s="163" t="s">
+      <c r="C16" s="206"/>
+      <c r="D16" s="206"/>
+      <c r="E16" s="206"/>
+      <c r="F16" s="207"/>
+      <c r="G16" s="153"/>
+      <c r="H16" s="154"/>
+      <c r="I16" s="154"/>
+      <c r="J16" s="154"/>
+      <c r="K16" s="154"/>
+      <c r="L16" s="154"/>
+      <c r="M16" s="154"/>
+      <c r="N16" s="154"/>
+      <c r="O16" s="154"/>
+      <c r="P16" s="155"/>
+      <c r="Q16" s="208" t="s">
         <v>15</v>
       </c>
-      <c r="R16" s="164"/>
-      <c r="S16" s="164"/>
-      <c r="T16" s="165"/>
+      <c r="R16" s="209"/>
+      <c r="S16" s="209"/>
+      <c r="T16" s="210"/>
       <c r="U16" s="89"/>
       <c r="V16" s="89"/>
       <c r="W16" s="89"/>
@@ -4079,144 +4070,144 @@
       <c r="AK16" s="26"/>
     </row>
     <row r="17" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="158"/>
-      <c r="B17" s="166" t="s">
+      <c r="A17" s="203"/>
+      <c r="B17" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="167"/>
-      <c r="D17" s="167"/>
-      <c r="E17" s="167"/>
-      <c r="F17" s="168"/>
-      <c r="G17" s="196"/>
-      <c r="H17" s="197"/>
-      <c r="I17" s="197"/>
-      <c r="J17" s="197"/>
-      <c r="K17" s="197"/>
-      <c r="L17" s="197"/>
-      <c r="M17" s="197"/>
-      <c r="N17" s="197"/>
-      <c r="O17" s="197"/>
-      <c r="P17" s="198"/>
-      <c r="Q17" s="160" t="s">
+      <c r="C17" s="212"/>
+      <c r="D17" s="212"/>
+      <c r="E17" s="212"/>
+      <c r="F17" s="213"/>
+      <c r="G17" s="133"/>
+      <c r="H17" s="134"/>
+      <c r="I17" s="134"/>
+      <c r="J17" s="134"/>
+      <c r="K17" s="134"/>
+      <c r="L17" s="134"/>
+      <c r="M17" s="134"/>
+      <c r="N17" s="134"/>
+      <c r="O17" s="134"/>
+      <c r="P17" s="232"/>
+      <c r="Q17" s="205" t="s">
         <v>16</v>
       </c>
-      <c r="R17" s="161"/>
-      <c r="S17" s="161"/>
-      <c r="T17" s="162"/>
-      <c r="U17" s="193"/>
-      <c r="V17" s="194"/>
-      <c r="W17" s="194"/>
-      <c r="X17" s="194"/>
-      <c r="Y17" s="194"/>
-      <c r="Z17" s="194"/>
-      <c r="AA17" s="194"/>
-      <c r="AB17" s="194"/>
-      <c r="AC17" s="194"/>
-      <c r="AD17" s="194"/>
-      <c r="AE17" s="194"/>
-      <c r="AF17" s="195"/>
+      <c r="R17" s="206"/>
+      <c r="S17" s="206"/>
+      <c r="T17" s="207"/>
+      <c r="U17" s="153"/>
+      <c r="V17" s="154"/>
+      <c r="W17" s="154"/>
+      <c r="X17" s="154"/>
+      <c r="Y17" s="154"/>
+      <c r="Z17" s="154"/>
+      <c r="AA17" s="154"/>
+      <c r="AB17" s="154"/>
+      <c r="AC17" s="154"/>
+      <c r="AD17" s="154"/>
+      <c r="AE17" s="154"/>
+      <c r="AF17" s="155"/>
     </row>
     <row r="18" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="158"/>
-      <c r="B18" s="155" t="s">
+      <c r="A18" s="203"/>
+      <c r="B18" s="200" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="143"/>
-      <c r="G18" s="196"/>
-      <c r="H18" s="197"/>
-      <c r="I18" s="197"/>
-      <c r="J18" s="197"/>
-      <c r="K18" s="197"/>
-      <c r="L18" s="197"/>
-      <c r="M18" s="197"/>
-      <c r="N18" s="197"/>
-      <c r="O18" s="197"/>
-      <c r="P18" s="198"/>
-      <c r="Q18" s="155" t="s">
+      <c r="C18" s="231"/>
+      <c r="D18" s="231"/>
+      <c r="E18" s="231"/>
+      <c r="F18" s="199"/>
+      <c r="G18" s="133"/>
+      <c r="H18" s="134"/>
+      <c r="I18" s="134"/>
+      <c r="J18" s="134"/>
+      <c r="K18" s="134"/>
+      <c r="L18" s="134"/>
+      <c r="M18" s="134"/>
+      <c r="N18" s="134"/>
+      <c r="O18" s="134"/>
+      <c r="P18" s="232"/>
+      <c r="Q18" s="200" t="s">
         <v>17</v>
       </c>
-      <c r="R18" s="142"/>
-      <c r="S18" s="142"/>
-      <c r="T18" s="143"/>
-      <c r="U18" s="247"/>
-      <c r="V18" s="248"/>
-      <c r="W18" s="248"/>
-      <c r="X18" s="248"/>
-      <c r="Y18" s="248"/>
-      <c r="Z18" s="248"/>
-      <c r="AA18" s="248"/>
-      <c r="AB18" s="248"/>
-      <c r="AC18" s="248"/>
-      <c r="AD18" s="248"/>
-      <c r="AE18" s="248"/>
-      <c r="AF18" s="249"/>
+      <c r="R18" s="231"/>
+      <c r="S18" s="231"/>
+      <c r="T18" s="199"/>
+      <c r="U18" s="162"/>
+      <c r="V18" s="163"/>
+      <c r="W18" s="163"/>
+      <c r="X18" s="163"/>
+      <c r="Y18" s="163"/>
+      <c r="Z18" s="163"/>
+      <c r="AA18" s="163"/>
+      <c r="AB18" s="163"/>
+      <c r="AC18" s="163"/>
+      <c r="AD18" s="163"/>
+      <c r="AE18" s="163"/>
+      <c r="AF18" s="164"/>
     </row>
     <row r="19" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="158"/>
-      <c r="B19" s="143" t="s">
+      <c r="A19" s="203"/>
+      <c r="B19" s="199" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="155"/>
-      <c r="D19" s="155"/>
-      <c r="E19" s="155"/>
-      <c r="F19" s="156"/>
+      <c r="C19" s="200"/>
+      <c r="D19" s="200"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="201"/>
       <c r="G19" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="H19" s="236"/>
-      <c r="I19" s="236"/>
-      <c r="J19" s="236"/>
-      <c r="K19" s="236"/>
-      <c r="L19" s="236"/>
+      <c r="H19" s="147"/>
+      <c r="I19" s="147"/>
+      <c r="J19" s="147"/>
+      <c r="K19" s="147"/>
+      <c r="L19" s="147"/>
       <c r="M19" s="33" t="s">
         <v>65</v>
       </c>
       <c r="N19" s="24"/>
-      <c r="O19" s="237" t="s">
+      <c r="O19" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="P19" s="237"/>
-      <c r="Q19" s="237"/>
-      <c r="R19" s="237"/>
-      <c r="S19" s="237"/>
-      <c r="T19" s="237"/>
-      <c r="U19" s="237"/>
-      <c r="V19" s="237"/>
-      <c r="W19" s="237"/>
-      <c r="X19" s="237"/>
-      <c r="Y19" s="237"/>
-      <c r="Z19" s="237"/>
-      <c r="AA19" s="237"/>
-      <c r="AB19" s="237"/>
-      <c r="AC19" s="237"/>
-      <c r="AD19" s="237"/>
-      <c r="AE19" s="237"/>
-      <c r="AF19" s="238"/>
+      <c r="P19" s="148"/>
+      <c r="Q19" s="148"/>
+      <c r="R19" s="148"/>
+      <c r="S19" s="148"/>
+      <c r="T19" s="148"/>
+      <c r="U19" s="148"/>
+      <c r="V19" s="148"/>
+      <c r="W19" s="148"/>
+      <c r="X19" s="148"/>
+      <c r="Y19" s="148"/>
+      <c r="Z19" s="148"/>
+      <c r="AA19" s="148"/>
+      <c r="AB19" s="148"/>
+      <c r="AC19" s="148"/>
+      <c r="AD19" s="148"/>
+      <c r="AE19" s="148"/>
+      <c r="AF19" s="149"/>
     </row>
     <row r="20" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="158"/>
-      <c r="B20" s="143"/>
-      <c r="C20" s="155"/>
-      <c r="D20" s="155"/>
-      <c r="E20" s="155"/>
-      <c r="F20" s="156"/>
-      <c r="G20" s="239"/>
-      <c r="H20" s="240"/>
-      <c r="I20" s="240"/>
-      <c r="J20" s="240"/>
-      <c r="K20" s="240"/>
-      <c r="L20" s="240"/>
-      <c r="M20" s="240"/>
-      <c r="N20" s="240"/>
-      <c r="O20" s="240"/>
-      <c r="P20" s="240"/>
-      <c r="Q20" s="240"/>
-      <c r="R20" s="240"/>
-      <c r="S20" s="240"/>
-      <c r="T20" s="240"/>
+      <c r="A20" s="203"/>
+      <c r="B20" s="199"/>
+      <c r="C20" s="200"/>
+      <c r="D20" s="200"/>
+      <c r="E20" s="200"/>
+      <c r="F20" s="201"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="151"/>
+      <c r="I20" s="151"/>
+      <c r="J20" s="151"/>
+      <c r="K20" s="151"/>
+      <c r="L20" s="151"/>
+      <c r="M20" s="151"/>
+      <c r="N20" s="151"/>
+      <c r="O20" s="151"/>
+      <c r="P20" s="151"/>
+      <c r="Q20" s="151"/>
+      <c r="R20" s="151"/>
+      <c r="S20" s="151"/>
+      <c r="T20" s="151"/>
       <c r="U20" s="34"/>
       <c r="V20" s="34"/>
       <c r="W20" s="34"/>
@@ -4230,346 +4221,346 @@
       <c r="AF20" s="27"/>
     </row>
     <row r="21" spans="1:37" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="158"/>
-      <c r="B21" s="143"/>
-      <c r="C21" s="155"/>
-      <c r="D21" s="155"/>
-      <c r="E21" s="155"/>
-      <c r="F21" s="156"/>
-      <c r="G21" s="235"/>
-      <c r="H21" s="131"/>
-      <c r="I21" s="131"/>
-      <c r="J21" s="131"/>
-      <c r="K21" s="131"/>
-      <c r="L21" s="131"/>
-      <c r="M21" s="131"/>
-      <c r="N21" s="131"/>
-      <c r="O21" s="131"/>
-      <c r="P21" s="131"/>
-      <c r="Q21" s="131"/>
-      <c r="R21" s="131"/>
-      <c r="S21" s="131"/>
-      <c r="T21" s="131"/>
-      <c r="U21" s="131" t="s">
+      <c r="A21" s="203"/>
+      <c r="B21" s="199"/>
+      <c r="C21" s="200"/>
+      <c r="D21" s="200"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="201"/>
+      <c r="G21" s="117"/>
+      <c r="H21" s="118"/>
+      <c r="I21" s="118"/>
+      <c r="J21" s="118"/>
+      <c r="K21" s="118"/>
+      <c r="L21" s="118"/>
+      <c r="M21" s="118"/>
+      <c r="N21" s="118"/>
+      <c r="O21" s="118"/>
+      <c r="P21" s="118"/>
+      <c r="Q21" s="118"/>
+      <c r="R21" s="118"/>
+      <c r="S21" s="118"/>
+      <c r="T21" s="118"/>
+      <c r="U21" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="V21" s="131"/>
-      <c r="W21" s="131"/>
-      <c r="X21" s="131"/>
-      <c r="Y21" s="131"/>
-      <c r="Z21" s="131"/>
-      <c r="AA21" s="131"/>
-      <c r="AB21" s="131"/>
-      <c r="AC21" s="131"/>
-      <c r="AD21" s="131"/>
-      <c r="AE21" s="131"/>
-      <c r="AF21" s="228"/>
+      <c r="V21" s="118"/>
+      <c r="W21" s="118"/>
+      <c r="X21" s="118"/>
+      <c r="Y21" s="118"/>
+      <c r="Z21" s="118"/>
+      <c r="AA21" s="118"/>
+      <c r="AB21" s="118"/>
+      <c r="AC21" s="118"/>
+      <c r="AD21" s="118"/>
+      <c r="AE21" s="118"/>
+      <c r="AF21" s="152"/>
     </row>
     <row r="22" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="158"/>
-      <c r="B22" s="266" t="s">
+      <c r="A22" s="203"/>
+      <c r="B22" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="267"/>
-      <c r="D22" s="267"/>
-      <c r="E22" s="267"/>
-      <c r="F22" s="268"/>
-      <c r="G22" s="272" t="s">
+      <c r="C22" s="100"/>
+      <c r="D22" s="100"/>
+      <c r="E22" s="100"/>
+      <c r="F22" s="109"/>
+      <c r="G22" s="145" t="s">
         <v>19</v>
       </c>
-      <c r="H22" s="255"/>
-      <c r="I22" s="273"/>
-      <c r="J22" s="196"/>
-      <c r="K22" s="197"/>
-      <c r="L22" s="197"/>
-      <c r="M22" s="197"/>
-      <c r="N22" s="197"/>
-      <c r="O22" s="197"/>
-      <c r="P22" s="197"/>
-      <c r="Q22" s="197"/>
-      <c r="R22" s="197"/>
-      <c r="S22" s="197"/>
-      <c r="T22" s="197"/>
-      <c r="U22" s="197"/>
-      <c r="V22" s="197"/>
-      <c r="W22" s="197"/>
-      <c r="X22" s="197"/>
-      <c r="Y22" s="197"/>
-      <c r="Z22" s="197"/>
-      <c r="AA22" s="197"/>
-      <c r="AB22" s="197"/>
-      <c r="AC22" s="197"/>
-      <c r="AD22" s="197"/>
-      <c r="AE22" s="197"/>
-      <c r="AF22" s="256"/>
+      <c r="H22" s="132"/>
+      <c r="I22" s="146"/>
+      <c r="J22" s="133"/>
+      <c r="K22" s="134"/>
+      <c r="L22" s="134"/>
+      <c r="M22" s="134"/>
+      <c r="N22" s="134"/>
+      <c r="O22" s="134"/>
+      <c r="P22" s="134"/>
+      <c r="Q22" s="134"/>
+      <c r="R22" s="134"/>
+      <c r="S22" s="134"/>
+      <c r="T22" s="134"/>
+      <c r="U22" s="134"/>
+      <c r="V22" s="134"/>
+      <c r="W22" s="134"/>
+      <c r="X22" s="134"/>
+      <c r="Y22" s="134"/>
+      <c r="Z22" s="134"/>
+      <c r="AA22" s="134"/>
+      <c r="AB22" s="134"/>
+      <c r="AC22" s="134"/>
+      <c r="AD22" s="134"/>
+      <c r="AE22" s="134"/>
+      <c r="AF22" s="135"/>
     </row>
     <row r="23" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="158"/>
-      <c r="B23" s="269"/>
-      <c r="C23" s="270"/>
-      <c r="D23" s="270"/>
-      <c r="E23" s="270"/>
-      <c r="F23" s="271"/>
-      <c r="G23" s="272" t="s">
+      <c r="A23" s="203"/>
+      <c r="B23" s="142"/>
+      <c r="C23" s="143"/>
+      <c r="D23" s="143"/>
+      <c r="E23" s="143"/>
+      <c r="F23" s="144"/>
+      <c r="G23" s="145" t="s">
         <v>20</v>
       </c>
-      <c r="H23" s="255"/>
-      <c r="I23" s="273"/>
-      <c r="J23" s="196"/>
-      <c r="K23" s="197"/>
-      <c r="L23" s="197"/>
-      <c r="M23" s="197"/>
-      <c r="N23" s="197"/>
-      <c r="O23" s="197"/>
-      <c r="P23" s="197"/>
-      <c r="Q23" s="197"/>
-      <c r="R23" s="255" t="s">
+      <c r="H23" s="132"/>
+      <c r="I23" s="146"/>
+      <c r="J23" s="133"/>
+      <c r="K23" s="134"/>
+      <c r="L23" s="134"/>
+      <c r="M23" s="134"/>
+      <c r="N23" s="134"/>
+      <c r="O23" s="134"/>
+      <c r="P23" s="134"/>
+      <c r="Q23" s="134"/>
+      <c r="R23" s="132" t="s">
         <v>68</v>
       </c>
-      <c r="S23" s="255"/>
-      <c r="T23" s="197"/>
-      <c r="U23" s="197"/>
-      <c r="V23" s="197"/>
-      <c r="W23" s="197"/>
-      <c r="X23" s="197"/>
-      <c r="Y23" s="197"/>
-      <c r="Z23" s="197"/>
-      <c r="AA23" s="197"/>
-      <c r="AB23" s="197"/>
-      <c r="AC23" s="197"/>
-      <c r="AD23" s="197"/>
-      <c r="AE23" s="197"/>
-      <c r="AF23" s="256"/>
+      <c r="S23" s="132"/>
+      <c r="T23" s="134"/>
+      <c r="U23" s="134"/>
+      <c r="V23" s="134"/>
+      <c r="W23" s="134"/>
+      <c r="X23" s="134"/>
+      <c r="Y23" s="134"/>
+      <c r="Z23" s="134"/>
+      <c r="AA23" s="134"/>
+      <c r="AB23" s="134"/>
+      <c r="AC23" s="134"/>
+      <c r="AD23" s="134"/>
+      <c r="AE23" s="134"/>
+      <c r="AF23" s="135"/>
     </row>
     <row r="24" spans="1:37" s="18" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="158"/>
-      <c r="B24" s="169" t="s">
+      <c r="A24" s="203"/>
+      <c r="B24" s="214" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="170"/>
-      <c r="D24" s="170"/>
-      <c r="E24" s="170"/>
-      <c r="F24" s="171"/>
-      <c r="G24" s="257"/>
-      <c r="H24" s="258"/>
-      <c r="I24" s="258"/>
-      <c r="J24" s="258"/>
-      <c r="K24" s="258"/>
-      <c r="L24" s="258"/>
-      <c r="M24" s="258"/>
-      <c r="N24" s="258"/>
-      <c r="O24" s="258"/>
-      <c r="P24" s="258"/>
-      <c r="Q24" s="258"/>
-      <c r="R24" s="258"/>
-      <c r="S24" s="258"/>
-      <c r="T24" s="258"/>
-      <c r="U24" s="258"/>
-      <c r="V24" s="258"/>
-      <c r="W24" s="258"/>
-      <c r="X24" s="258"/>
-      <c r="Y24" s="258"/>
-      <c r="Z24" s="258"/>
-      <c r="AA24" s="258"/>
-      <c r="AB24" s="258"/>
-      <c r="AC24" s="258"/>
-      <c r="AD24" s="258"/>
-      <c r="AE24" s="258"/>
-      <c r="AF24" s="259"/>
+      <c r="C24" s="215"/>
+      <c r="D24" s="215"/>
+      <c r="E24" s="215"/>
+      <c r="F24" s="216"/>
+      <c r="G24" s="111"/>
+      <c r="H24" s="112"/>
+      <c r="I24" s="112"/>
+      <c r="J24" s="112"/>
+      <c r="K24" s="112"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="112"/>
+      <c r="R24" s="112"/>
+      <c r="S24" s="112"/>
+      <c r="T24" s="112"/>
+      <c r="U24" s="112"/>
+      <c r="V24" s="112"/>
+      <c r="W24" s="112"/>
+      <c r="X24" s="112"/>
+      <c r="Y24" s="112"/>
+      <c r="Z24" s="112"/>
+      <c r="AA24" s="112"/>
+      <c r="AB24" s="112"/>
+      <c r="AC24" s="112"/>
+      <c r="AD24" s="112"/>
+      <c r="AE24" s="112"/>
+      <c r="AF24" s="113"/>
       <c r="AJ24" s="33"/>
     </row>
     <row r="25" spans="1:37" s="18" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="158"/>
-      <c r="B25" s="172"/>
-      <c r="C25" s="173"/>
-      <c r="D25" s="173"/>
-      <c r="E25" s="173"/>
-      <c r="F25" s="174"/>
-      <c r="G25" s="260"/>
-      <c r="H25" s="261"/>
-      <c r="I25" s="261"/>
-      <c r="J25" s="261"/>
-      <c r="K25" s="261"/>
-      <c r="L25" s="261"/>
-      <c r="M25" s="261"/>
-      <c r="N25" s="261"/>
-      <c r="O25" s="261"/>
-      <c r="P25" s="261"/>
-      <c r="Q25" s="261"/>
-      <c r="R25" s="261"/>
-      <c r="S25" s="261"/>
-      <c r="T25" s="261"/>
-      <c r="U25" s="261"/>
-      <c r="V25" s="261"/>
-      <c r="W25" s="261"/>
-      <c r="X25" s="261"/>
-      <c r="Y25" s="261"/>
-      <c r="Z25" s="261"/>
-      <c r="AA25" s="261"/>
-      <c r="AB25" s="261"/>
-      <c r="AC25" s="261"/>
-      <c r="AD25" s="261"/>
-      <c r="AE25" s="261"/>
-      <c r="AF25" s="262"/>
+      <c r="A25" s="203"/>
+      <c r="B25" s="217"/>
+      <c r="C25" s="218"/>
+      <c r="D25" s="218"/>
+      <c r="E25" s="218"/>
+      <c r="F25" s="219"/>
+      <c r="G25" s="313"/>
+      <c r="H25" s="314"/>
+      <c r="I25" s="314"/>
+      <c r="J25" s="314"/>
+      <c r="K25" s="314"/>
+      <c r="L25" s="314"/>
+      <c r="M25" s="314"/>
+      <c r="N25" s="314"/>
+      <c r="O25" s="314"/>
+      <c r="P25" s="314"/>
+      <c r="Q25" s="314"/>
+      <c r="R25" s="314"/>
+      <c r="S25" s="314"/>
+      <c r="T25" s="314"/>
+      <c r="U25" s="314"/>
+      <c r="V25" s="314"/>
+      <c r="W25" s="314"/>
+      <c r="X25" s="314"/>
+      <c r="Y25" s="314"/>
+      <c r="Z25" s="314"/>
+      <c r="AA25" s="314"/>
+      <c r="AB25" s="314"/>
+      <c r="AC25" s="314"/>
+      <c r="AD25" s="314"/>
+      <c r="AE25" s="314"/>
+      <c r="AF25" s="315"/>
       <c r="AJ25" s="33"/>
     </row>
     <row r="26" spans="1:37" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="158"/>
-      <c r="B26" s="175" t="s">
+      <c r="A26" s="203"/>
+      <c r="B26" s="220" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="176"/>
-      <c r="D26" s="176"/>
-      <c r="E26" s="176"/>
-      <c r="F26" s="177"/>
-      <c r="G26" s="181" t="s">
+      <c r="C26" s="125"/>
+      <c r="D26" s="125"/>
+      <c r="E26" s="125"/>
+      <c r="F26" s="126"/>
+      <c r="G26" s="222" t="s">
         <v>51</v>
       </c>
-      <c r="H26" s="182"/>
-      <c r="I26" s="182"/>
-      <c r="J26" s="182"/>
-      <c r="K26" s="182"/>
-      <c r="L26" s="183"/>
-      <c r="M26" s="187"/>
-      <c r="N26" s="189"/>
-      <c r="O26" s="189"/>
-      <c r="P26" s="189"/>
-      <c r="Q26" s="189"/>
-      <c r="R26" s="189"/>
-      <c r="S26" s="189"/>
-      <c r="T26" s="189"/>
-      <c r="U26" s="188"/>
-      <c r="V26" s="184" t="s">
+      <c r="H26" s="223"/>
+      <c r="I26" s="223"/>
+      <c r="J26" s="223"/>
+      <c r="K26" s="223"/>
+      <c r="L26" s="224"/>
+      <c r="M26" s="136"/>
+      <c r="N26" s="137"/>
+      <c r="O26" s="137"/>
+      <c r="P26" s="137"/>
+      <c r="Q26" s="137"/>
+      <c r="R26" s="137"/>
+      <c r="S26" s="137"/>
+      <c r="T26" s="137"/>
+      <c r="U26" s="138"/>
+      <c r="V26" s="225" t="s">
         <v>52</v>
       </c>
-      <c r="W26" s="185"/>
-      <c r="X26" s="185"/>
-      <c r="Y26" s="185"/>
-      <c r="Z26" s="186"/>
-      <c r="AA26" s="263"/>
-      <c r="AB26" s="264"/>
-      <c r="AC26" s="264"/>
-      <c r="AD26" s="264"/>
-      <c r="AE26" s="264"/>
-      <c r="AF26" s="265"/>
+      <c r="W26" s="226"/>
+      <c r="X26" s="226"/>
+      <c r="Y26" s="226"/>
+      <c r="Z26" s="227"/>
+      <c r="AA26" s="139"/>
+      <c r="AB26" s="140"/>
+      <c r="AC26" s="140"/>
+      <c r="AD26" s="140"/>
+      <c r="AE26" s="140"/>
+      <c r="AF26" s="141"/>
       <c r="AJ26" s="33"/>
       <c r="AK26" s="18"/>
     </row>
     <row r="27" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="158"/>
-      <c r="B27" s="178"/>
-      <c r="C27" s="179"/>
-      <c r="D27" s="179"/>
-      <c r="E27" s="179"/>
-      <c r="F27" s="180"/>
-      <c r="G27" s="181" t="s">
+      <c r="A27" s="203"/>
+      <c r="B27" s="221"/>
+      <c r="C27" s="172"/>
+      <c r="D27" s="172"/>
+      <c r="E27" s="172"/>
+      <c r="F27" s="173"/>
+      <c r="G27" s="222" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="182"/>
-      <c r="I27" s="182"/>
-      <c r="J27" s="182"/>
-      <c r="K27" s="182"/>
-      <c r="L27" s="183"/>
-      <c r="M27" s="187" t="s">
+      <c r="H27" s="223"/>
+      <c r="I27" s="223"/>
+      <c r="J27" s="223"/>
+      <c r="K27" s="223"/>
+      <c r="L27" s="224"/>
+      <c r="M27" s="136" t="s">
         <v>54</v>
       </c>
-      <c r="N27" s="188"/>
-      <c r="O27" s="187"/>
-      <c r="P27" s="189"/>
-      <c r="Q27" s="189"/>
-      <c r="R27" s="189"/>
-      <c r="S27" s="189"/>
-      <c r="T27" s="189"/>
-      <c r="U27" s="188"/>
-      <c r="V27" s="187" t="s">
+      <c r="N27" s="138"/>
+      <c r="O27" s="136"/>
+      <c r="P27" s="137"/>
+      <c r="Q27" s="137"/>
+      <c r="R27" s="137"/>
+      <c r="S27" s="137"/>
+      <c r="T27" s="137"/>
+      <c r="U27" s="138"/>
+      <c r="V27" s="136" t="s">
         <v>55</v>
       </c>
-      <c r="W27" s="189"/>
-      <c r="X27" s="188"/>
-      <c r="Y27" s="263"/>
-      <c r="Z27" s="264"/>
-      <c r="AA27" s="264"/>
-      <c r="AB27" s="264"/>
-      <c r="AC27" s="264"/>
-      <c r="AD27" s="264"/>
-      <c r="AE27" s="264"/>
-      <c r="AF27" s="265"/>
+      <c r="W27" s="137"/>
+      <c r="X27" s="138"/>
+      <c r="Y27" s="139"/>
+      <c r="Z27" s="140"/>
+      <c r="AA27" s="140"/>
+      <c r="AB27" s="140"/>
+      <c r="AC27" s="140"/>
+      <c r="AD27" s="140"/>
+      <c r="AE27" s="140"/>
+      <c r="AF27" s="141"/>
       <c r="AJ27" s="33"/>
       <c r="AK27" s="18"/>
     </row>
     <row r="28" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="158"/>
-      <c r="B28" s="176" t="s">
+      <c r="A28" s="203"/>
+      <c r="B28" s="125" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="176"/>
-      <c r="D28" s="176"/>
-      <c r="E28" s="176"/>
-      <c r="F28" s="177"/>
-      <c r="G28" s="252"/>
-      <c r="H28" s="253"/>
-      <c r="I28" s="253"/>
-      <c r="J28" s="253"/>
-      <c r="K28" s="253"/>
-      <c r="L28" s="253"/>
-      <c r="M28" s="253"/>
-      <c r="N28" s="253"/>
-      <c r="O28" s="253"/>
-      <c r="P28" s="253"/>
-      <c r="Q28" s="253"/>
-      <c r="R28" s="253"/>
-      <c r="S28" s="253"/>
-      <c r="T28" s="253"/>
-      <c r="U28" s="253"/>
-      <c r="V28" s="253"/>
-      <c r="W28" s="253"/>
-      <c r="X28" s="253"/>
-      <c r="Y28" s="253"/>
-      <c r="Z28" s="253"/>
-      <c r="AA28" s="253"/>
-      <c r="AB28" s="253"/>
-      <c r="AC28" s="253"/>
-      <c r="AD28" s="253"/>
-      <c r="AE28" s="253"/>
-      <c r="AF28" s="254"/>
+      <c r="C28" s="125"/>
+      <c r="D28" s="125"/>
+      <c r="E28" s="125"/>
+      <c r="F28" s="126"/>
+      <c r="G28" s="129"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="130"/>
+      <c r="J28" s="130"/>
+      <c r="K28" s="130"/>
+      <c r="L28" s="130"/>
+      <c r="M28" s="130"/>
+      <c r="N28" s="130"/>
+      <c r="O28" s="130"/>
+      <c r="P28" s="130"/>
+      <c r="Q28" s="130"/>
+      <c r="R28" s="130"/>
+      <c r="S28" s="130"/>
+      <c r="T28" s="130"/>
+      <c r="U28" s="130"/>
+      <c r="V28" s="130"/>
+      <c r="W28" s="130"/>
+      <c r="X28" s="130"/>
+      <c r="Y28" s="130"/>
+      <c r="Z28" s="130"/>
+      <c r="AA28" s="130"/>
+      <c r="AB28" s="130"/>
+      <c r="AC28" s="130"/>
+      <c r="AD28" s="130"/>
+      <c r="AE28" s="130"/>
+      <c r="AF28" s="131"/>
       <c r="AJ28" s="33"/>
       <c r="AK28" s="18"/>
     </row>
     <row r="29" spans="1:37" s="3" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="159"/>
-      <c r="B29" s="250"/>
-      <c r="C29" s="250"/>
-      <c r="D29" s="250"/>
-      <c r="E29" s="250"/>
-      <c r="F29" s="251"/>
-      <c r="G29" s="190" t="s">
+      <c r="A29" s="204"/>
+      <c r="B29" s="127"/>
+      <c r="C29" s="127"/>
+      <c r="D29" s="127"/>
+      <c r="E29" s="127"/>
+      <c r="F29" s="128"/>
+      <c r="G29" s="228" t="s">
         <v>67</v>
       </c>
-      <c r="H29" s="191"/>
-      <c r="I29" s="191"/>
-      <c r="J29" s="191"/>
-      <c r="K29" s="191"/>
-      <c r="L29" s="191"/>
-      <c r="M29" s="191"/>
-      <c r="N29" s="191"/>
-      <c r="O29" s="191"/>
-      <c r="P29" s="191"/>
-      <c r="Q29" s="191"/>
-      <c r="R29" s="191"/>
-      <c r="S29" s="191"/>
-      <c r="T29" s="191"/>
-      <c r="U29" s="191"/>
-      <c r="V29" s="191"/>
-      <c r="W29" s="191"/>
-      <c r="X29" s="191"/>
-      <c r="Y29" s="191"/>
-      <c r="Z29" s="191"/>
-      <c r="AA29" s="191"/>
-      <c r="AB29" s="191"/>
-      <c r="AC29" s="191"/>
-      <c r="AD29" s="191"/>
-      <c r="AE29" s="191"/>
-      <c r="AF29" s="192"/>
+      <c r="H29" s="229"/>
+      <c r="I29" s="229"/>
+      <c r="J29" s="229"/>
+      <c r="K29" s="229"/>
+      <c r="L29" s="229"/>
+      <c r="M29" s="229"/>
+      <c r="N29" s="229"/>
+      <c r="O29" s="229"/>
+      <c r="P29" s="229"/>
+      <c r="Q29" s="229"/>
+      <c r="R29" s="229"/>
+      <c r="S29" s="229"/>
+      <c r="T29" s="229"/>
+      <c r="U29" s="229"/>
+      <c r="V29" s="229"/>
+      <c r="W29" s="229"/>
+      <c r="X29" s="229"/>
+      <c r="Y29" s="229"/>
+      <c r="Z29" s="229"/>
+      <c r="AA29" s="229"/>
+      <c r="AB29" s="229"/>
+      <c r="AC29" s="229"/>
+      <c r="AD29" s="229"/>
+      <c r="AE29" s="229"/>
+      <c r="AF29" s="230"/>
       <c r="AG29" s="1"/>
       <c r="AH29" s="1"/>
       <c r="AI29" s="1"/>
@@ -4613,16 +4604,16 @@
       <c r="AK30" s="26"/>
     </row>
     <row r="31" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="135" t="s">
+      <c r="A31" s="244" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="147" t="s">
+      <c r="B31" s="254" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="148"/>
-      <c r="D31" s="148"/>
-      <c r="E31" s="148"/>
-      <c r="F31" s="149"/>
+      <c r="C31" s="255"/>
+      <c r="D31" s="255"/>
+      <c r="E31" s="255"/>
+      <c r="F31" s="256"/>
       <c r="G31" s="42" t="s">
         <v>22</v>
       </c>
@@ -4633,21 +4624,21 @@
       <c r="L31" s="32"/>
       <c r="M31" s="26"/>
       <c r="N31" s="43"/>
-      <c r="O31" s="282" t="s">
+      <c r="O31" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="P31" s="216"/>
-      <c r="Q31" s="283" t="s">
+      <c r="P31" s="115"/>
+      <c r="Q31" s="265" t="s">
         <v>61</v>
       </c>
-      <c r="R31" s="283"/>
-      <c r="S31" s="216"/>
-      <c r="T31" s="216"/>
-      <c r="U31" s="216"/>
-      <c r="V31" s="216"/>
-      <c r="W31" s="216"/>
-      <c r="X31" s="216"/>
-      <c r="Y31" s="216"/>
+      <c r="R31" s="265"/>
+      <c r="S31" s="115"/>
+      <c r="T31" s="115"/>
+      <c r="U31" s="115"/>
+      <c r="V31" s="115"/>
+      <c r="W31" s="115"/>
+      <c r="X31" s="115"/>
+      <c r="Y31" s="115"/>
       <c r="Z31" s="87" t="s">
         <v>65</v>
       </c>
@@ -4661,100 +4652,100 @@
       <c r="AK31" s="26"/>
     </row>
     <row r="32" spans="1:37" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="136"/>
-      <c r="B32" s="284" t="s">
+      <c r="A32" s="245"/>
+      <c r="B32" s="266" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="285"/>
-      <c r="D32" s="285"/>
-      <c r="E32" s="285"/>
-      <c r="F32" s="286"/>
-      <c r="G32" s="290"/>
-      <c r="H32" s="291"/>
-      <c r="I32" s="291"/>
-      <c r="J32" s="291"/>
-      <c r="K32" s="291"/>
-      <c r="L32" s="291"/>
-      <c r="M32" s="291"/>
-      <c r="N32" s="292"/>
-      <c r="O32" s="290"/>
-      <c r="P32" s="291"/>
-      <c r="Q32" s="291"/>
-      <c r="R32" s="291"/>
-      <c r="S32" s="291"/>
-      <c r="T32" s="291"/>
-      <c r="U32" s="291"/>
-      <c r="V32" s="291"/>
-      <c r="W32" s="291"/>
-      <c r="X32" s="291"/>
-      <c r="Y32" s="291"/>
-      <c r="Z32" s="291"/>
-      <c r="AA32" s="291"/>
-      <c r="AB32" s="291"/>
-      <c r="AC32" s="291"/>
-      <c r="AD32" s="291"/>
-      <c r="AE32" s="291"/>
-      <c r="AF32" s="296"/>
+      <c r="C32" s="267"/>
+      <c r="D32" s="267"/>
+      <c r="E32" s="267"/>
+      <c r="F32" s="268"/>
+      <c r="G32" s="94"/>
+      <c r="H32" s="95"/>
+      <c r="I32" s="95"/>
+      <c r="J32" s="95"/>
+      <c r="K32" s="95"/>
+      <c r="L32" s="95"/>
+      <c r="M32" s="95"/>
+      <c r="N32" s="272"/>
+      <c r="O32" s="94"/>
+      <c r="P32" s="95"/>
+      <c r="Q32" s="95"/>
+      <c r="R32" s="95"/>
+      <c r="S32" s="95"/>
+      <c r="T32" s="95"/>
+      <c r="U32" s="95"/>
+      <c r="V32" s="95"/>
+      <c r="W32" s="95"/>
+      <c r="X32" s="95"/>
+      <c r="Y32" s="95"/>
+      <c r="Z32" s="95"/>
+      <c r="AA32" s="95"/>
+      <c r="AB32" s="95"/>
+      <c r="AC32" s="95"/>
+      <c r="AD32" s="95"/>
+      <c r="AE32" s="95"/>
+      <c r="AF32" s="96"/>
       <c r="AJ32" s="32"/>
       <c r="AK32" s="26"/>
     </row>
     <row r="33" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="136"/>
-      <c r="B33" s="287"/>
-      <c r="C33" s="288"/>
-      <c r="D33" s="288"/>
-      <c r="E33" s="288"/>
-      <c r="F33" s="289"/>
-      <c r="G33" s="293"/>
-      <c r="H33" s="294"/>
-      <c r="I33" s="294"/>
-      <c r="J33" s="294"/>
-      <c r="K33" s="294"/>
-      <c r="L33" s="294"/>
-      <c r="M33" s="294"/>
-      <c r="N33" s="295"/>
+      <c r="A33" s="245"/>
+      <c r="B33" s="269"/>
+      <c r="C33" s="270"/>
+      <c r="D33" s="270"/>
+      <c r="E33" s="270"/>
+      <c r="F33" s="271"/>
+      <c r="G33" s="273"/>
+      <c r="H33" s="274"/>
+      <c r="I33" s="274"/>
+      <c r="J33" s="274"/>
+      <c r="K33" s="274"/>
+      <c r="L33" s="274"/>
+      <c r="M33" s="274"/>
+      <c r="N33" s="275"/>
       <c r="O33" s="47"/>
       <c r="P33" s="48"/>
       <c r="Q33" s="35"/>
       <c r="R33" s="5"/>
       <c r="S33" s="5"/>
-      <c r="T33" s="297" t="s">
+      <c r="T33" s="276" t="s">
         <v>10</v>
       </c>
-      <c r="U33" s="297"/>
-      <c r="V33" s="297"/>
-      <c r="W33" s="298"/>
-      <c r="X33" s="298"/>
-      <c r="Y33" s="298"/>
-      <c r="Z33" s="298"/>
-      <c r="AA33" s="298"/>
-      <c r="AB33" s="298"/>
-      <c r="AC33" s="298"/>
-      <c r="AD33" s="298"/>
-      <c r="AE33" s="298"/>
-      <c r="AF33" s="299"/>
+      <c r="U33" s="276"/>
+      <c r="V33" s="276"/>
+      <c r="W33" s="97"/>
+      <c r="X33" s="97"/>
+      <c r="Y33" s="97"/>
+      <c r="Z33" s="97"/>
+      <c r="AA33" s="97"/>
+      <c r="AB33" s="97"/>
+      <c r="AC33" s="97"/>
+      <c r="AD33" s="97"/>
+      <c r="AE33" s="97"/>
+      <c r="AF33" s="98"/>
       <c r="AJ33" s="32"/>
       <c r="AK33" s="26"/>
     </row>
     <row r="34" spans="1:37" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="136"/>
-      <c r="B34" s="138" t="s">
+      <c r="A34" s="245"/>
+      <c r="B34" s="247" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="138"/>
-      <c r="D34" s="138"/>
-      <c r="E34" s="138"/>
-      <c r="F34" s="139"/>
-      <c r="G34" s="274" t="s">
+      <c r="C34" s="247"/>
+      <c r="D34" s="247"/>
+      <c r="E34" s="247"/>
+      <c r="F34" s="248"/>
+      <c r="G34" s="257" t="s">
         <v>6</v>
       </c>
-      <c r="H34" s="275"/>
-      <c r="I34" s="276"/>
-      <c r="J34" s="276"/>
-      <c r="K34" s="276"/>
-      <c r="L34" s="276"/>
-      <c r="M34" s="276"/>
-      <c r="N34" s="277"/>
+      <c r="H34" s="258"/>
+      <c r="I34" s="259"/>
+      <c r="J34" s="259"/>
+      <c r="K34" s="259"/>
+      <c r="L34" s="259"/>
+      <c r="M34" s="259"/>
+      <c r="N34" s="260"/>
       <c r="O34" s="50" t="s">
         <v>8</v>
       </c>
@@ -4776,82 +4767,82 @@
       <c r="AK34" s="26"/>
     </row>
     <row r="35" spans="1:37" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="136"/>
-      <c r="B35" s="140" t="s">
+      <c r="A35" s="245"/>
+      <c r="B35" s="249" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="140"/>
-      <c r="D35" s="140"/>
-      <c r="E35" s="140"/>
-      <c r="F35" s="141"/>
-      <c r="G35" s="278" t="s">
+      <c r="C35" s="249"/>
+      <c r="D35" s="249"/>
+      <c r="E35" s="249"/>
+      <c r="F35" s="250"/>
+      <c r="G35" s="261" t="s">
         <v>71</v>
       </c>
-      <c r="H35" s="279"/>
-      <c r="I35" s="280"/>
-      <c r="J35" s="280"/>
-      <c r="K35" s="280"/>
-      <c r="L35" s="280"/>
-      <c r="M35" s="280"/>
-      <c r="N35" s="281"/>
-      <c r="O35" s="269"/>
-      <c r="P35" s="270"/>
-      <c r="Q35" s="270"/>
-      <c r="R35" s="270"/>
-      <c r="S35" s="271"/>
-      <c r="T35" s="306"/>
-      <c r="U35" s="307"/>
-      <c r="V35" s="307"/>
-      <c r="W35" s="307"/>
-      <c r="X35" s="307"/>
-      <c r="Y35" s="307"/>
-      <c r="Z35" s="307"/>
-      <c r="AA35" s="307"/>
-      <c r="AB35" s="307"/>
-      <c r="AC35" s="307"/>
-      <c r="AD35" s="307"/>
-      <c r="AE35" s="307"/>
-      <c r="AF35" s="308"/>
+      <c r="H35" s="262"/>
+      <c r="I35" s="263"/>
+      <c r="J35" s="263"/>
+      <c r="K35" s="263"/>
+      <c r="L35" s="263"/>
+      <c r="M35" s="263"/>
+      <c r="N35" s="264"/>
+      <c r="O35" s="142"/>
+      <c r="P35" s="143"/>
+      <c r="Q35" s="143"/>
+      <c r="R35" s="143"/>
+      <c r="S35" s="144"/>
+      <c r="T35" s="106"/>
+      <c r="U35" s="107"/>
+      <c r="V35" s="107"/>
+      <c r="W35" s="107"/>
+      <c r="X35" s="107"/>
+      <c r="Y35" s="107"/>
+      <c r="Z35" s="107"/>
+      <c r="AA35" s="107"/>
+      <c r="AB35" s="107"/>
+      <c r="AC35" s="107"/>
+      <c r="AD35" s="107"/>
+      <c r="AE35" s="107"/>
+      <c r="AF35" s="108"/>
       <c r="AJ35" s="32"/>
       <c r="AK35" s="26"/>
     </row>
     <row r="36" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="136"/>
-      <c r="B36" s="142" t="s">
+      <c r="A36" s="245"/>
+      <c r="B36" s="231" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="142"/>
-      <c r="D36" s="142"/>
-      <c r="E36" s="142"/>
-      <c r="F36" s="143"/>
-      <c r="G36" s="144" t="s">
+      <c r="C36" s="231"/>
+      <c r="D36" s="231"/>
+      <c r="E36" s="231"/>
+      <c r="F36" s="199"/>
+      <c r="G36" s="251" t="s">
         <v>72</v>
       </c>
-      <c r="H36" s="145"/>
-      <c r="I36" s="145"/>
-      <c r="J36" s="145"/>
-      <c r="K36" s="145"/>
-      <c r="L36" s="145"/>
-      <c r="M36" s="145"/>
-      <c r="N36" s="145"/>
-      <c r="O36" s="145"/>
-      <c r="P36" s="145"/>
-      <c r="Q36" s="145"/>
-      <c r="R36" s="145"/>
-      <c r="S36" s="145"/>
-      <c r="T36" s="145"/>
-      <c r="U36" s="145"/>
-      <c r="V36" s="145"/>
-      <c r="W36" s="145"/>
-      <c r="X36" s="145"/>
-      <c r="Y36" s="145"/>
-      <c r="Z36" s="145"/>
-      <c r="AA36" s="145"/>
-      <c r="AB36" s="145"/>
-      <c r="AC36" s="145"/>
-      <c r="AD36" s="145"/>
-      <c r="AE36" s="145"/>
-      <c r="AF36" s="146"/>
+      <c r="H36" s="252"/>
+      <c r="I36" s="252"/>
+      <c r="J36" s="252"/>
+      <c r="K36" s="252"/>
+      <c r="L36" s="252"/>
+      <c r="M36" s="252"/>
+      <c r="N36" s="252"/>
+      <c r="O36" s="252"/>
+      <c r="P36" s="252"/>
+      <c r="Q36" s="252"/>
+      <c r="R36" s="252"/>
+      <c r="S36" s="252"/>
+      <c r="T36" s="252"/>
+      <c r="U36" s="252"/>
+      <c r="V36" s="252"/>
+      <c r="W36" s="252"/>
+      <c r="X36" s="252"/>
+      <c r="Y36" s="252"/>
+      <c r="Z36" s="252"/>
+      <c r="AA36" s="252"/>
+      <c r="AB36" s="252"/>
+      <c r="AC36" s="252"/>
+      <c r="AD36" s="252"/>
+      <c r="AE36" s="252"/>
+      <c r="AF36" s="253"/>
       <c r="AG36" s="18"/>
       <c r="AH36" s="18"/>
       <c r="AI36" s="18"/>
@@ -4859,40 +4850,40 @@
       <c r="AK36" s="18"/>
     </row>
     <row r="37" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="136"/>
-      <c r="B37" s="266" t="s">
+      <c r="A37" s="245"/>
+      <c r="B37" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="267"/>
-      <c r="D37" s="267"/>
-      <c r="E37" s="267"/>
-      <c r="F37" s="268"/>
-      <c r="G37" s="310"/>
-      <c r="H37" s="311"/>
-      <c r="I37" s="311"/>
-      <c r="J37" s="311"/>
-      <c r="K37" s="311"/>
-      <c r="L37" s="311"/>
-      <c r="M37" s="311"/>
-      <c r="N37" s="311"/>
-      <c r="O37" s="311"/>
-      <c r="P37" s="311"/>
-      <c r="Q37" s="311"/>
-      <c r="R37" s="311"/>
-      <c r="S37" s="311"/>
-      <c r="T37" s="311"/>
-      <c r="U37" s="311"/>
-      <c r="V37" s="311"/>
-      <c r="W37" s="311"/>
-      <c r="X37" s="311"/>
-      <c r="Y37" s="311"/>
-      <c r="Z37" s="311"/>
-      <c r="AA37" s="311"/>
-      <c r="AB37" s="311"/>
-      <c r="AC37" s="311"/>
-      <c r="AD37" s="311"/>
-      <c r="AE37" s="311"/>
-      <c r="AF37" s="312"/>
+      <c r="C37" s="100"/>
+      <c r="D37" s="100"/>
+      <c r="E37" s="100"/>
+      <c r="F37" s="109"/>
+      <c r="G37" s="111"/>
+      <c r="H37" s="112"/>
+      <c r="I37" s="112"/>
+      <c r="J37" s="112"/>
+      <c r="K37" s="112"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="112"/>
+      <c r="R37" s="112"/>
+      <c r="S37" s="112"/>
+      <c r="T37" s="112"/>
+      <c r="U37" s="112"/>
+      <c r="V37" s="112"/>
+      <c r="W37" s="112"/>
+      <c r="X37" s="112"/>
+      <c r="Y37" s="112"/>
+      <c r="Z37" s="112"/>
+      <c r="AA37" s="112"/>
+      <c r="AB37" s="112"/>
+      <c r="AC37" s="112"/>
+      <c r="AD37" s="112"/>
+      <c r="AE37" s="112"/>
+      <c r="AF37" s="113"/>
       <c r="AG37" s="18"/>
       <c r="AH37" s="18"/>
       <c r="AI37" s="18"/>
@@ -4900,40 +4891,40 @@
       <c r="AK37" s="18"/>
     </row>
     <row r="38" spans="1:37" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="137"/>
-      <c r="B38" s="301"/>
-      <c r="C38" s="302"/>
-      <c r="D38" s="302"/>
-      <c r="E38" s="302"/>
-      <c r="F38" s="309"/>
-      <c r="G38" s="313" t="s">
+      <c r="A38" s="246"/>
+      <c r="B38" s="101"/>
+      <c r="C38" s="102"/>
+      <c r="D38" s="102"/>
+      <c r="E38" s="102"/>
+      <c r="F38" s="110"/>
+      <c r="G38" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="H38" s="314"/>
-      <c r="I38" s="314"/>
-      <c r="J38" s="314"/>
-      <c r="K38" s="314"/>
-      <c r="L38" s="314"/>
-      <c r="M38" s="314"/>
-      <c r="N38" s="314"/>
-      <c r="O38" s="314"/>
-      <c r="P38" s="314"/>
-      <c r="Q38" s="314"/>
-      <c r="R38" s="314"/>
-      <c r="S38" s="314"/>
-      <c r="T38" s="314"/>
-      <c r="U38" s="314"/>
-      <c r="V38" s="314"/>
-      <c r="W38" s="314"/>
-      <c r="X38" s="314"/>
-      <c r="Y38" s="314"/>
-      <c r="Z38" s="314"/>
-      <c r="AA38" s="314"/>
-      <c r="AB38" s="314"/>
-      <c r="AC38" s="314"/>
-      <c r="AD38" s="314"/>
-      <c r="AE38" s="314"/>
-      <c r="AF38" s="315"/>
+      <c r="H38" s="123"/>
+      <c r="I38" s="123"/>
+      <c r="J38" s="123"/>
+      <c r="K38" s="123"/>
+      <c r="L38" s="123"/>
+      <c r="M38" s="123"/>
+      <c r="N38" s="123"/>
+      <c r="O38" s="123"/>
+      <c r="P38" s="123"/>
+      <c r="Q38" s="123"/>
+      <c r="R38" s="123"/>
+      <c r="S38" s="123"/>
+      <c r="T38" s="123"/>
+      <c r="U38" s="123"/>
+      <c r="V38" s="123"/>
+      <c r="W38" s="123"/>
+      <c r="X38" s="123"/>
+      <c r="Y38" s="123"/>
+      <c r="Z38" s="123"/>
+      <c r="AA38" s="123"/>
+      <c r="AB38" s="123"/>
+      <c r="AC38" s="123"/>
+      <c r="AD38" s="123"/>
+      <c r="AE38" s="123"/>
+      <c r="AF38" s="124"/>
       <c r="AG38" s="18"/>
       <c r="AH38" s="18"/>
       <c r="AI38" s="18"/>
@@ -4975,26 +4966,26 @@
       <c r="AF39" s="28"/>
     </row>
     <row r="40" spans="1:37" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="126" t="s">
+      <c r="A40" s="237" t="s">
         <v>30</v>
       </c>
-      <c r="B40" s="130" t="s">
+      <c r="B40" s="166" t="s">
         <v>31</v>
       </c>
-      <c r="C40" s="130"/>
-      <c r="D40" s="130"/>
-      <c r="E40" s="130"/>
-      <c r="F40" s="130"/>
-      <c r="G40" s="282"/>
-      <c r="H40" s="216"/>
-      <c r="I40" s="216"/>
-      <c r="J40" s="216"/>
-      <c r="K40" s="216"/>
-      <c r="L40" s="216"/>
-      <c r="M40" s="216"/>
-      <c r="N40" s="216"/>
-      <c r="O40" s="216"/>
-      <c r="P40" s="217"/>
+      <c r="C40" s="166"/>
+      <c r="D40" s="166"/>
+      <c r="E40" s="166"/>
+      <c r="F40" s="166"/>
+      <c r="G40" s="114"/>
+      <c r="H40" s="115"/>
+      <c r="I40" s="115"/>
+      <c r="J40" s="115"/>
+      <c r="K40" s="115"/>
+      <c r="L40" s="115"/>
+      <c r="M40" s="115"/>
+      <c r="N40" s="115"/>
+      <c r="O40" s="115"/>
+      <c r="P40" s="116"/>
       <c r="Q40" s="59" t="s">
         <v>32</v>
       </c>
@@ -5020,31 +5011,31 @@
       <c r="AK40" s="18"/>
     </row>
     <row r="41" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="127"/>
-      <c r="B41" s="131"/>
-      <c r="C41" s="131"/>
-      <c r="D41" s="131"/>
-      <c r="E41" s="131"/>
-      <c r="F41" s="131"/>
-      <c r="G41" s="235"/>
-      <c r="H41" s="131"/>
-      <c r="I41" s="131"/>
-      <c r="J41" s="131"/>
-      <c r="K41" s="131"/>
-      <c r="L41" s="131"/>
-      <c r="M41" s="131"/>
-      <c r="N41" s="131"/>
-      <c r="O41" s="131"/>
-      <c r="P41" s="218"/>
-      <c r="Q41" s="231" t="s">
+      <c r="A41" s="238"/>
+      <c r="B41" s="118"/>
+      <c r="C41" s="118"/>
+      <c r="D41" s="118"/>
+      <c r="E41" s="118"/>
+      <c r="F41" s="118"/>
+      <c r="G41" s="117"/>
+      <c r="H41" s="118"/>
+      <c r="I41" s="118"/>
+      <c r="J41" s="118"/>
+      <c r="K41" s="118"/>
+      <c r="L41" s="118"/>
+      <c r="M41" s="118"/>
+      <c r="N41" s="118"/>
+      <c r="O41" s="118"/>
+      <c r="P41" s="119"/>
+      <c r="Q41" s="120" t="s">
         <v>61</v>
       </c>
-      <c r="R41" s="232"/>
-      <c r="S41" s="232"/>
-      <c r="T41" s="232"/>
-      <c r="U41" s="232"/>
-      <c r="V41" s="232"/>
-      <c r="W41" s="232"/>
+      <c r="R41" s="121"/>
+      <c r="S41" s="121"/>
+      <c r="T41" s="121"/>
+      <c r="U41" s="121"/>
+      <c r="V41" s="121"/>
+      <c r="W41" s="121"/>
       <c r="X41" s="36" t="s">
         <v>65</v>
       </c>
@@ -5059,80 +5050,80 @@
       <c r="AK41" s="23"/>
     </row>
     <row r="42" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="128"/>
-      <c r="B42" s="175" t="s">
+      <c r="A42" s="239"/>
+      <c r="B42" s="220" t="s">
         <v>33</v>
       </c>
-      <c r="C42" s="176"/>
-      <c r="D42" s="176"/>
-      <c r="E42" s="176"/>
-      <c r="F42" s="177"/>
-      <c r="G42" s="231"/>
-      <c r="H42" s="232"/>
-      <c r="I42" s="232"/>
-      <c r="J42" s="232"/>
-      <c r="K42" s="232"/>
-      <c r="L42" s="232"/>
-      <c r="M42" s="232"/>
-      <c r="N42" s="232"/>
-      <c r="O42" s="232"/>
-      <c r="P42" s="300"/>
-      <c r="Q42" s="290"/>
-      <c r="R42" s="291"/>
-      <c r="S42" s="291"/>
-      <c r="T42" s="291"/>
-      <c r="U42" s="291"/>
-      <c r="V42" s="291"/>
-      <c r="W42" s="291"/>
-      <c r="X42" s="291"/>
-      <c r="Y42" s="291"/>
-      <c r="Z42" s="291"/>
-      <c r="AA42" s="291"/>
-      <c r="AB42" s="291"/>
-      <c r="AC42" s="291"/>
-      <c r="AD42" s="291"/>
-      <c r="AE42" s="291"/>
-      <c r="AF42" s="296"/>
+      <c r="C42" s="125"/>
+      <c r="D42" s="125"/>
+      <c r="E42" s="125"/>
+      <c r="F42" s="126"/>
+      <c r="G42" s="120"/>
+      <c r="H42" s="121"/>
+      <c r="I42" s="121"/>
+      <c r="J42" s="121"/>
+      <c r="K42" s="121"/>
+      <c r="L42" s="121"/>
+      <c r="M42" s="121"/>
+      <c r="N42" s="121"/>
+      <c r="O42" s="121"/>
+      <c r="P42" s="277"/>
+      <c r="Q42" s="94"/>
+      <c r="R42" s="95"/>
+      <c r="S42" s="95"/>
+      <c r="T42" s="95"/>
+      <c r="U42" s="95"/>
+      <c r="V42" s="95"/>
+      <c r="W42" s="95"/>
+      <c r="X42" s="95"/>
+      <c r="Y42" s="95"/>
+      <c r="Z42" s="95"/>
+      <c r="AA42" s="95"/>
+      <c r="AB42" s="95"/>
+      <c r="AC42" s="95"/>
+      <c r="AD42" s="95"/>
+      <c r="AE42" s="95"/>
+      <c r="AF42" s="96"/>
       <c r="AK42" s="23"/>
     </row>
     <row r="43" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="128"/>
-      <c r="B43" s="178"/>
-      <c r="C43" s="179"/>
-      <c r="D43" s="179"/>
-      <c r="E43" s="179"/>
-      <c r="F43" s="180"/>
-      <c r="G43" s="235"/>
-      <c r="H43" s="131"/>
-      <c r="I43" s="131"/>
-      <c r="J43" s="131"/>
-      <c r="K43" s="131"/>
-      <c r="L43" s="131"/>
-      <c r="M43" s="131"/>
-      <c r="N43" s="131"/>
-      <c r="O43" s="131"/>
-      <c r="P43" s="218"/>
+      <c r="A43" s="239"/>
+      <c r="B43" s="221"/>
+      <c r="C43" s="172"/>
+      <c r="D43" s="172"/>
+      <c r="E43" s="172"/>
+      <c r="F43" s="173"/>
+      <c r="G43" s="117"/>
+      <c r="H43" s="118"/>
+      <c r="I43" s="118"/>
+      <c r="J43" s="118"/>
+      <c r="K43" s="118"/>
+      <c r="L43" s="118"/>
+      <c r="M43" s="118"/>
+      <c r="N43" s="118"/>
+      <c r="O43" s="118"/>
+      <c r="P43" s="119"/>
       <c r="Q43" s="64" t="s">
         <v>10</v>
       </c>
       <c r="R43" s="62"/>
       <c r="S43" s="62"/>
       <c r="T43" s="62"/>
-      <c r="U43" s="298"/>
-      <c r="V43" s="298"/>
-      <c r="W43" s="298"/>
-      <c r="X43" s="298"/>
-      <c r="Y43" s="298"/>
-      <c r="Z43" s="298"/>
-      <c r="AA43" s="298"/>
-      <c r="AB43" s="298"/>
-      <c r="AC43" s="298"/>
-      <c r="AD43" s="298"/>
-      <c r="AE43" s="298"/>
-      <c r="AF43" s="299"/>
+      <c r="U43" s="97"/>
+      <c r="V43" s="97"/>
+      <c r="W43" s="97"/>
+      <c r="X43" s="97"/>
+      <c r="Y43" s="97"/>
+      <c r="Z43" s="97"/>
+      <c r="AA43" s="97"/>
+      <c r="AB43" s="97"/>
+      <c r="AC43" s="97"/>
+      <c r="AD43" s="97"/>
+      <c r="AE43" s="97"/>
+      <c r="AF43" s="98"/>
     </row>
     <row r="44" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="128"/>
+      <c r="A44" s="239"/>
       <c r="B44" s="36" t="s">
         <v>34</v>
       </c>
@@ -5167,7 +5158,7 @@
       <c r="AJ44" s="33"/>
     </row>
     <row r="45" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="128"/>
+      <c r="A45" s="239"/>
       <c r="B45" s="69" t="s">
         <v>35</v>
       </c>
@@ -5203,76 +5194,76 @@
       <c r="AF45" s="49"/>
     </row>
     <row r="46" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="128"/>
-      <c r="B46" s="266" t="s">
+      <c r="A46" s="239"/>
+      <c r="B46" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="C46" s="267"/>
-      <c r="D46" s="267"/>
-      <c r="E46" s="267"/>
-      <c r="F46" s="267"/>
-      <c r="G46" s="303"/>
-      <c r="H46" s="304"/>
-      <c r="I46" s="304"/>
-      <c r="J46" s="304"/>
-      <c r="K46" s="304"/>
-      <c r="L46" s="304"/>
-      <c r="M46" s="304"/>
-      <c r="N46" s="304"/>
-      <c r="O46" s="304"/>
-      <c r="P46" s="304"/>
-      <c r="Q46" s="304"/>
-      <c r="R46" s="304"/>
-      <c r="S46" s="304"/>
-      <c r="T46" s="304"/>
-      <c r="U46" s="304"/>
-      <c r="V46" s="304"/>
-      <c r="W46" s="304"/>
-      <c r="X46" s="304"/>
-      <c r="Y46" s="304"/>
-      <c r="Z46" s="304"/>
-      <c r="AA46" s="304"/>
-      <c r="AB46" s="304"/>
-      <c r="AC46" s="304"/>
-      <c r="AD46" s="304"/>
-      <c r="AE46" s="304"/>
-      <c r="AF46" s="305"/>
+      <c r="C46" s="100"/>
+      <c r="D46" s="100"/>
+      <c r="E46" s="100"/>
+      <c r="F46" s="100"/>
+      <c r="G46" s="103"/>
+      <c r="H46" s="104"/>
+      <c r="I46" s="104"/>
+      <c r="J46" s="104"/>
+      <c r="K46" s="104"/>
+      <c r="L46" s="104"/>
+      <c r="M46" s="104"/>
+      <c r="N46" s="104"/>
+      <c r="O46" s="104"/>
+      <c r="P46" s="104"/>
+      <c r="Q46" s="104"/>
+      <c r="R46" s="104"/>
+      <c r="S46" s="104"/>
+      <c r="T46" s="104"/>
+      <c r="U46" s="104"/>
+      <c r="V46" s="104"/>
+      <c r="W46" s="104"/>
+      <c r="X46" s="104"/>
+      <c r="Y46" s="104"/>
+      <c r="Z46" s="104"/>
+      <c r="AA46" s="104"/>
+      <c r="AB46" s="104"/>
+      <c r="AC46" s="104"/>
+      <c r="AD46" s="104"/>
+      <c r="AE46" s="104"/>
+      <c r="AF46" s="105"/>
     </row>
     <row r="47" spans="1:37" s="72" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="129"/>
-      <c r="B47" s="301"/>
-      <c r="C47" s="302"/>
-      <c r="D47" s="302"/>
-      <c r="E47" s="302"/>
-      <c r="F47" s="302"/>
-      <c r="G47" s="132" t="s">
+      <c r="A47" s="240"/>
+      <c r="B47" s="101"/>
+      <c r="C47" s="102"/>
+      <c r="D47" s="102"/>
+      <c r="E47" s="102"/>
+      <c r="F47" s="102"/>
+      <c r="G47" s="241" t="s">
         <v>36</v>
       </c>
-      <c r="H47" s="133"/>
-      <c r="I47" s="133"/>
-      <c r="J47" s="133"/>
-      <c r="K47" s="133"/>
-      <c r="L47" s="133"/>
-      <c r="M47" s="133"/>
-      <c r="N47" s="133"/>
-      <c r="O47" s="133"/>
-      <c r="P47" s="133"/>
-      <c r="Q47" s="133"/>
-      <c r="R47" s="133"/>
-      <c r="S47" s="133"/>
-      <c r="T47" s="133"/>
-      <c r="U47" s="133"/>
-      <c r="V47" s="133"/>
-      <c r="W47" s="133"/>
-      <c r="X47" s="133"/>
-      <c r="Y47" s="133"/>
-      <c r="Z47" s="133"/>
-      <c r="AA47" s="133"/>
-      <c r="AB47" s="133"/>
-      <c r="AC47" s="133"/>
-      <c r="AD47" s="133"/>
-      <c r="AE47" s="133"/>
-      <c r="AF47" s="134"/>
+      <c r="H47" s="242"/>
+      <c r="I47" s="242"/>
+      <c r="J47" s="242"/>
+      <c r="K47" s="242"/>
+      <c r="L47" s="242"/>
+      <c r="M47" s="242"/>
+      <c r="N47" s="242"/>
+      <c r="O47" s="242"/>
+      <c r="P47" s="242"/>
+      <c r="Q47" s="242"/>
+      <c r="R47" s="242"/>
+      <c r="S47" s="242"/>
+      <c r="T47" s="242"/>
+      <c r="U47" s="242"/>
+      <c r="V47" s="242"/>
+      <c r="W47" s="242"/>
+      <c r="X47" s="242"/>
+      <c r="Y47" s="242"/>
+      <c r="Z47" s="242"/>
+      <c r="AA47" s="242"/>
+      <c r="AB47" s="242"/>
+      <c r="AC47" s="242"/>
+      <c r="AD47" s="242"/>
+      <c r="AE47" s="242"/>
+      <c r="AF47" s="243"/>
       <c r="AJ47" s="73"/>
     </row>
     <row r="48" spans="1:37" s="3" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -5313,301 +5304,301 @@
       <c r="D49" s="77"/>
       <c r="E49" s="77"/>
       <c r="F49" s="78"/>
-      <c r="G49" s="91" t="s">
+      <c r="G49" s="278" t="s">
         <v>57</v>
       </c>
-      <c r="H49" s="92"/>
-      <c r="I49" s="92"/>
-      <c r="J49" s="92"/>
-      <c r="K49" s="92"/>
-      <c r="L49" s="92"/>
-      <c r="M49" s="92"/>
-      <c r="N49" s="92"/>
-      <c r="O49" s="92"/>
-      <c r="P49" s="92"/>
-      <c r="Q49" s="92"/>
-      <c r="R49" s="92"/>
-      <c r="S49" s="92"/>
-      <c r="T49" s="92"/>
-      <c r="U49" s="92"/>
-      <c r="V49" s="92"/>
-      <c r="W49" s="92"/>
-      <c r="X49" s="92"/>
-      <c r="Y49" s="92"/>
-      <c r="Z49" s="92"/>
-      <c r="AA49" s="92"/>
-      <c r="AB49" s="92"/>
-      <c r="AC49" s="92"/>
-      <c r="AD49" s="92"/>
-      <c r="AE49" s="92"/>
-      <c r="AF49" s="93"/>
+      <c r="H49" s="279"/>
+      <c r="I49" s="279"/>
+      <c r="J49" s="279"/>
+      <c r="K49" s="279"/>
+      <c r="L49" s="279"/>
+      <c r="M49" s="279"/>
+      <c r="N49" s="279"/>
+      <c r="O49" s="279"/>
+      <c r="P49" s="279"/>
+      <c r="Q49" s="279"/>
+      <c r="R49" s="279"/>
+      <c r="S49" s="279"/>
+      <c r="T49" s="279"/>
+      <c r="U49" s="279"/>
+      <c r="V49" s="279"/>
+      <c r="W49" s="279"/>
+      <c r="X49" s="279"/>
+      <c r="Y49" s="279"/>
+      <c r="Z49" s="279"/>
+      <c r="AA49" s="279"/>
+      <c r="AB49" s="279"/>
+      <c r="AC49" s="279"/>
+      <c r="AD49" s="279"/>
+      <c r="AE49" s="279"/>
+      <c r="AF49" s="280"/>
       <c r="AG49" s="76"/>
     </row>
     <row r="50" spans="1:33" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="B50" s="106" t="s">
+      <c r="B50" s="293" t="s">
         <v>38</v>
       </c>
-      <c r="C50" s="107"/>
-      <c r="D50" s="107"/>
-      <c r="E50" s="108"/>
+      <c r="C50" s="294"/>
+      <c r="D50" s="294"/>
+      <c r="E50" s="295"/>
       <c r="F50" s="78"/>
-      <c r="G50" s="94"/>
-      <c r="H50" s="95"/>
-      <c r="I50" s="95"/>
-      <c r="J50" s="95"/>
-      <c r="K50" s="95"/>
-      <c r="L50" s="95"/>
-      <c r="M50" s="95"/>
-      <c r="N50" s="95"/>
-      <c r="O50" s="95"/>
-      <c r="P50" s="95"/>
-      <c r="Q50" s="95"/>
-      <c r="R50" s="95"/>
-      <c r="S50" s="95"/>
-      <c r="T50" s="95"/>
-      <c r="U50" s="95"/>
-      <c r="V50" s="95"/>
-      <c r="W50" s="95"/>
-      <c r="X50" s="95"/>
-      <c r="Y50" s="95"/>
-      <c r="Z50" s="95"/>
-      <c r="AA50" s="95"/>
-      <c r="AB50" s="95"/>
-      <c r="AC50" s="95"/>
-      <c r="AD50" s="95"/>
-      <c r="AE50" s="95"/>
-      <c r="AF50" s="96"/>
+      <c r="G50" s="281"/>
+      <c r="H50" s="282"/>
+      <c r="I50" s="282"/>
+      <c r="J50" s="282"/>
+      <c r="K50" s="282"/>
+      <c r="L50" s="282"/>
+      <c r="M50" s="282"/>
+      <c r="N50" s="282"/>
+      <c r="O50" s="282"/>
+      <c r="P50" s="282"/>
+      <c r="Q50" s="282"/>
+      <c r="R50" s="282"/>
+      <c r="S50" s="282"/>
+      <c r="T50" s="282"/>
+      <c r="U50" s="282"/>
+      <c r="V50" s="282"/>
+      <c r="W50" s="282"/>
+      <c r="X50" s="282"/>
+      <c r="Y50" s="282"/>
+      <c r="Z50" s="282"/>
+      <c r="AA50" s="282"/>
+      <c r="AB50" s="282"/>
+      <c r="AC50" s="282"/>
+      <c r="AD50" s="282"/>
+      <c r="AE50" s="282"/>
+      <c r="AF50" s="283"/>
       <c r="AG50" s="76"/>
     </row>
     <row r="51" spans="1:33" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="109" t="s">
+      <c r="A51" s="296" t="s">
         <v>39</v>
       </c>
-      <c r="B51" s="112" t="s">
+      <c r="B51" s="299" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="114" t="s">
+      <c r="C51" s="301" t="s">
         <v>41</v>
       </c>
-      <c r="D51" s="115"/>
-      <c r="E51" s="116"/>
+      <c r="D51" s="302"/>
+      <c r="E51" s="303"/>
       <c r="F51" s="78"/>
-      <c r="G51" s="94"/>
-      <c r="H51" s="95"/>
-      <c r="I51" s="95"/>
-      <c r="J51" s="95"/>
-      <c r="K51" s="95"/>
-      <c r="L51" s="95"/>
-      <c r="M51" s="95"/>
-      <c r="N51" s="95"/>
-      <c r="O51" s="95"/>
-      <c r="P51" s="95"/>
-      <c r="Q51" s="95"/>
-      <c r="R51" s="95"/>
-      <c r="S51" s="95"/>
-      <c r="T51" s="95"/>
-      <c r="U51" s="95"/>
-      <c r="V51" s="95"/>
-      <c r="W51" s="95"/>
-      <c r="X51" s="95"/>
-      <c r="Y51" s="95"/>
-      <c r="Z51" s="95"/>
-      <c r="AA51" s="95"/>
-      <c r="AB51" s="95"/>
-      <c r="AC51" s="95"/>
-      <c r="AD51" s="95"/>
-      <c r="AE51" s="95"/>
-      <c r="AF51" s="96"/>
+      <c r="G51" s="281"/>
+      <c r="H51" s="282"/>
+      <c r="I51" s="282"/>
+      <c r="J51" s="282"/>
+      <c r="K51" s="282"/>
+      <c r="L51" s="282"/>
+      <c r="M51" s="282"/>
+      <c r="N51" s="282"/>
+      <c r="O51" s="282"/>
+      <c r="P51" s="282"/>
+      <c r="Q51" s="282"/>
+      <c r="R51" s="282"/>
+      <c r="S51" s="282"/>
+      <c r="T51" s="282"/>
+      <c r="U51" s="282"/>
+      <c r="V51" s="282"/>
+      <c r="W51" s="282"/>
+      <c r="X51" s="282"/>
+      <c r="Y51" s="282"/>
+      <c r="Z51" s="282"/>
+      <c r="AA51" s="282"/>
+      <c r="AB51" s="282"/>
+      <c r="AC51" s="282"/>
+      <c r="AD51" s="282"/>
+      <c r="AE51" s="282"/>
+      <c r="AF51" s="283"/>
       <c r="AG51" s="76"/>
     </row>
     <row r="52" spans="1:33" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="110"/>
-      <c r="B52" s="113"/>
-      <c r="C52" s="117"/>
-      <c r="D52" s="118"/>
-      <c r="E52" s="119"/>
+      <c r="A52" s="297"/>
+      <c r="B52" s="300"/>
+      <c r="C52" s="304"/>
+      <c r="D52" s="305"/>
+      <c r="E52" s="306"/>
       <c r="F52" s="78"/>
-      <c r="G52" s="94"/>
-      <c r="H52" s="95"/>
-      <c r="I52" s="95"/>
-      <c r="J52" s="95"/>
-      <c r="K52" s="95"/>
-      <c r="L52" s="95"/>
-      <c r="M52" s="95"/>
-      <c r="N52" s="95"/>
-      <c r="O52" s="95"/>
-      <c r="P52" s="95"/>
-      <c r="Q52" s="95"/>
-      <c r="R52" s="95"/>
-      <c r="S52" s="95"/>
-      <c r="T52" s="95"/>
-      <c r="U52" s="95"/>
-      <c r="V52" s="95"/>
-      <c r="W52" s="95"/>
-      <c r="X52" s="95"/>
-      <c r="Y52" s="95"/>
-      <c r="Z52" s="95"/>
-      <c r="AA52" s="95"/>
-      <c r="AB52" s="95"/>
-      <c r="AC52" s="95"/>
-      <c r="AD52" s="95"/>
-      <c r="AE52" s="95"/>
-      <c r="AF52" s="96"/>
+      <c r="G52" s="281"/>
+      <c r="H52" s="282"/>
+      <c r="I52" s="282"/>
+      <c r="J52" s="282"/>
+      <c r="K52" s="282"/>
+      <c r="L52" s="282"/>
+      <c r="M52" s="282"/>
+      <c r="N52" s="282"/>
+      <c r="O52" s="282"/>
+      <c r="P52" s="282"/>
+      <c r="Q52" s="282"/>
+      <c r="R52" s="282"/>
+      <c r="S52" s="282"/>
+      <c r="T52" s="282"/>
+      <c r="U52" s="282"/>
+      <c r="V52" s="282"/>
+      <c r="W52" s="282"/>
+      <c r="X52" s="282"/>
+      <c r="Y52" s="282"/>
+      <c r="Z52" s="282"/>
+      <c r="AA52" s="282"/>
+      <c r="AB52" s="282"/>
+      <c r="AC52" s="282"/>
+      <c r="AD52" s="282"/>
+      <c r="AE52" s="282"/>
+      <c r="AF52" s="283"/>
       <c r="AG52" s="76"/>
     </row>
     <row r="53" spans="1:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="110"/>
-      <c r="B53" s="112" t="s">
+      <c r="A53" s="297"/>
+      <c r="B53" s="299" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="114" t="s">
+      <c r="C53" s="301" t="s">
         <v>43</v>
       </c>
-      <c r="D53" s="115"/>
-      <c r="E53" s="116"/>
+      <c r="D53" s="302"/>
+      <c r="E53" s="303"/>
       <c r="F53" s="78"/>
-      <c r="G53" s="94"/>
-      <c r="H53" s="95"/>
-      <c r="I53" s="95"/>
-      <c r="J53" s="95"/>
-      <c r="K53" s="95"/>
-      <c r="L53" s="95"/>
-      <c r="M53" s="95"/>
-      <c r="N53" s="95"/>
-      <c r="O53" s="95"/>
-      <c r="P53" s="95"/>
-      <c r="Q53" s="95"/>
-      <c r="R53" s="95"/>
-      <c r="S53" s="95"/>
-      <c r="T53" s="95"/>
-      <c r="U53" s="95"/>
-      <c r="V53" s="95"/>
-      <c r="W53" s="95"/>
-      <c r="X53" s="95"/>
-      <c r="Y53" s="95"/>
-      <c r="Z53" s="95"/>
-      <c r="AA53" s="95"/>
-      <c r="AB53" s="95"/>
-      <c r="AC53" s="95"/>
-      <c r="AD53" s="95"/>
-      <c r="AE53" s="95"/>
-      <c r="AF53" s="96"/>
+      <c r="G53" s="281"/>
+      <c r="H53" s="282"/>
+      <c r="I53" s="282"/>
+      <c r="J53" s="282"/>
+      <c r="K53" s="282"/>
+      <c r="L53" s="282"/>
+      <c r="M53" s="282"/>
+      <c r="N53" s="282"/>
+      <c r="O53" s="282"/>
+      <c r="P53" s="282"/>
+      <c r="Q53" s="282"/>
+      <c r="R53" s="282"/>
+      <c r="S53" s="282"/>
+      <c r="T53" s="282"/>
+      <c r="U53" s="282"/>
+      <c r="V53" s="282"/>
+      <c r="W53" s="282"/>
+      <c r="X53" s="282"/>
+      <c r="Y53" s="282"/>
+      <c r="Z53" s="282"/>
+      <c r="AA53" s="282"/>
+      <c r="AB53" s="282"/>
+      <c r="AC53" s="282"/>
+      <c r="AD53" s="282"/>
+      <c r="AE53" s="282"/>
+      <c r="AF53" s="283"/>
       <c r="AG53" s="76"/>
     </row>
     <row r="54" spans="1:33" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="110"/>
-      <c r="B54" s="120"/>
-      <c r="C54" s="117"/>
-      <c r="D54" s="118"/>
-      <c r="E54" s="119"/>
+      <c r="A54" s="297"/>
+      <c r="B54" s="307"/>
+      <c r="C54" s="304"/>
+      <c r="D54" s="305"/>
+      <c r="E54" s="306"/>
       <c r="F54" s="78"/>
-      <c r="G54" s="97" t="s">
+      <c r="G54" s="284" t="s">
         <v>47</v>
       </c>
-      <c r="H54" s="98"/>
-      <c r="I54" s="98"/>
-      <c r="J54" s="98"/>
-      <c r="K54" s="98"/>
-      <c r="L54" s="98"/>
-      <c r="M54" s="98"/>
-      <c r="N54" s="98"/>
-      <c r="O54" s="98"/>
-      <c r="P54" s="98"/>
-      <c r="Q54" s="98"/>
-      <c r="R54" s="98"/>
-      <c r="S54" s="98"/>
-      <c r="T54" s="98"/>
-      <c r="U54" s="98"/>
-      <c r="V54" s="98"/>
-      <c r="W54" s="98"/>
-      <c r="X54" s="98"/>
-      <c r="Y54" s="98"/>
-      <c r="Z54" s="98"/>
-      <c r="AA54" s="98"/>
-      <c r="AB54" s="98"/>
-      <c r="AC54" s="98"/>
-      <c r="AD54" s="98"/>
-      <c r="AE54" s="98"/>
-      <c r="AF54" s="99"/>
+      <c r="H54" s="285"/>
+      <c r="I54" s="285"/>
+      <c r="J54" s="285"/>
+      <c r="K54" s="285"/>
+      <c r="L54" s="285"/>
+      <c r="M54" s="285"/>
+      <c r="N54" s="285"/>
+      <c r="O54" s="285"/>
+      <c r="P54" s="285"/>
+      <c r="Q54" s="285"/>
+      <c r="R54" s="285"/>
+      <c r="S54" s="285"/>
+      <c r="T54" s="285"/>
+      <c r="U54" s="285"/>
+      <c r="V54" s="285"/>
+      <c r="W54" s="285"/>
+      <c r="X54" s="285"/>
+      <c r="Y54" s="285"/>
+      <c r="Z54" s="285"/>
+      <c r="AA54" s="285"/>
+      <c r="AB54" s="285"/>
+      <c r="AC54" s="285"/>
+      <c r="AD54" s="285"/>
+      <c r="AE54" s="285"/>
+      <c r="AF54" s="286"/>
       <c r="AG54" s="76"/>
     </row>
     <row r="55" spans="1:33" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="110"/>
-      <c r="B55" s="121" t="s">
+      <c r="A55" s="297"/>
+      <c r="B55" s="308" t="s">
         <v>44</v>
       </c>
-      <c r="C55" s="123" t="s">
+      <c r="C55" s="310" t="s">
         <v>45</v>
       </c>
-      <c r="D55" s="124"/>
-      <c r="E55" s="125"/>
+      <c r="D55" s="311"/>
+      <c r="E55" s="312"/>
       <c r="F55" s="78"/>
-      <c r="G55" s="100"/>
-      <c r="H55" s="101"/>
-      <c r="I55" s="101"/>
-      <c r="J55" s="101"/>
-      <c r="K55" s="101"/>
-      <c r="L55" s="101"/>
-      <c r="M55" s="101"/>
-      <c r="N55" s="101"/>
-      <c r="O55" s="101"/>
-      <c r="P55" s="101"/>
-      <c r="Q55" s="101"/>
-      <c r="R55" s="101"/>
-      <c r="S55" s="101"/>
-      <c r="T55" s="101"/>
-      <c r="U55" s="101"/>
-      <c r="V55" s="101"/>
-      <c r="W55" s="101"/>
-      <c r="X55" s="101"/>
-      <c r="Y55" s="101"/>
-      <c r="Z55" s="101"/>
-      <c r="AA55" s="101"/>
-      <c r="AB55" s="101"/>
-      <c r="AC55" s="101"/>
-      <c r="AD55" s="101"/>
-      <c r="AE55" s="101"/>
-      <c r="AF55" s="102"/>
+      <c r="G55" s="287"/>
+      <c r="H55" s="288"/>
+      <c r="I55" s="288"/>
+      <c r="J55" s="288"/>
+      <c r="K55" s="288"/>
+      <c r="L55" s="288"/>
+      <c r="M55" s="288"/>
+      <c r="N55" s="288"/>
+      <c r="O55" s="288"/>
+      <c r="P55" s="288"/>
+      <c r="Q55" s="288"/>
+      <c r="R55" s="288"/>
+      <c r="S55" s="288"/>
+      <c r="T55" s="288"/>
+      <c r="U55" s="288"/>
+      <c r="V55" s="288"/>
+      <c r="W55" s="288"/>
+      <c r="X55" s="288"/>
+      <c r="Y55" s="288"/>
+      <c r="Z55" s="288"/>
+      <c r="AA55" s="288"/>
+      <c r="AB55" s="288"/>
+      <c r="AC55" s="288"/>
+      <c r="AD55" s="288"/>
+      <c r="AE55" s="288"/>
+      <c r="AF55" s="289"/>
       <c r="AG55" s="76"/>
     </row>
     <row r="56" spans="1:33" ht="30.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="111"/>
-      <c r="B56" s="122"/>
-      <c r="C56" s="117"/>
-      <c r="D56" s="118"/>
-      <c r="E56" s="119"/>
+      <c r="A56" s="298"/>
+      <c r="B56" s="309"/>
+      <c r="C56" s="304"/>
+      <c r="D56" s="305"/>
+      <c r="E56" s="306"/>
       <c r="F56" s="80"/>
-      <c r="G56" s="103" t="s">
+      <c r="G56" s="290" t="s">
         <v>48</v>
       </c>
-      <c r="H56" s="104"/>
-      <c r="I56" s="104"/>
-      <c r="J56" s="104"/>
-      <c r="K56" s="104"/>
-      <c r="L56" s="104"/>
-      <c r="M56" s="104"/>
-      <c r="N56" s="104"/>
-      <c r="O56" s="104"/>
-      <c r="P56" s="104"/>
-      <c r="Q56" s="104"/>
-      <c r="R56" s="104"/>
-      <c r="S56" s="104"/>
-      <c r="T56" s="104"/>
-      <c r="U56" s="104"/>
-      <c r="V56" s="104"/>
-      <c r="W56" s="104"/>
-      <c r="X56" s="104"/>
-      <c r="Y56" s="104"/>
-      <c r="Z56" s="104"/>
-      <c r="AA56" s="104"/>
-      <c r="AB56" s="104"/>
-      <c r="AC56" s="104"/>
-      <c r="AD56" s="104"/>
-      <c r="AE56" s="104"/>
-      <c r="AF56" s="105"/>
+      <c r="H56" s="291"/>
+      <c r="I56" s="291"/>
+      <c r="J56" s="291"/>
+      <c r="K56" s="291"/>
+      <c r="L56" s="291"/>
+      <c r="M56" s="291"/>
+      <c r="N56" s="291"/>
+      <c r="O56" s="291"/>
+      <c r="P56" s="291"/>
+      <c r="Q56" s="291"/>
+      <c r="R56" s="291"/>
+      <c r="S56" s="291"/>
+      <c r="T56" s="291"/>
+      <c r="U56" s="291"/>
+      <c r="V56" s="291"/>
+      <c r="W56" s="291"/>
+      <c r="X56" s="291"/>
+      <c r="Y56" s="291"/>
+      <c r="Z56" s="291"/>
+      <c r="AA56" s="291"/>
+      <c r="AB56" s="291"/>
+      <c r="AC56" s="291"/>
+      <c r="AD56" s="291"/>
+      <c r="AE56" s="291"/>
+      <c r="AF56" s="292"/>
     </row>
     <row r="57" spans="1:33" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="81" t="s">
@@ -5636,56 +5627,41 @@
     </row>
   </sheetData>
   <mergeCells count="109">
-    <mergeCell ref="Q42:AF42"/>
-    <mergeCell ref="U43:AF43"/>
-    <mergeCell ref="B46:F47"/>
-    <mergeCell ref="G46:AF46"/>
-    <mergeCell ref="T35:AF35"/>
-    <mergeCell ref="B37:F38"/>
-    <mergeCell ref="G37:AF37"/>
-    <mergeCell ref="G40:P41"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="S41:W41"/>
-    <mergeCell ref="G38:AF38"/>
-    <mergeCell ref="B28:F29"/>
-    <mergeCell ref="G28:AF28"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="J23:Q23"/>
-    <mergeCell ref="T23:AF23"/>
-    <mergeCell ref="G24:AF25"/>
-    <mergeCell ref="M26:U26"/>
-    <mergeCell ref="AA26:AF26"/>
-    <mergeCell ref="O27:U27"/>
-    <mergeCell ref="Y27:AF27"/>
-    <mergeCell ref="B22:F23"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:AF22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="H19:L19"/>
-    <mergeCell ref="O19:AF19"/>
-    <mergeCell ref="G20:T21"/>
-    <mergeCell ref="U21:X21"/>
-    <mergeCell ref="Y21:AF21"/>
-    <mergeCell ref="G16:P16"/>
-    <mergeCell ref="T9:W10"/>
-    <mergeCell ref="X9:AF10"/>
-    <mergeCell ref="G8:S8"/>
-    <mergeCell ref="G9:S10"/>
-    <mergeCell ref="U18:AF18"/>
-    <mergeCell ref="A8:C12"/>
-    <mergeCell ref="X7:AF8"/>
-    <mergeCell ref="T7:W8"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="G14:P14"/>
-    <mergeCell ref="Q14:V14"/>
-    <mergeCell ref="W14:AF14"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="X12:AF12"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:M11"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:R12"/>
+    <mergeCell ref="G49:AF53"/>
+    <mergeCell ref="G54:AF55"/>
+    <mergeCell ref="G56:AF56"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="A51:A56"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:E52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:E54"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:E56"/>
+    <mergeCell ref="A40:A47"/>
+    <mergeCell ref="B40:F41"/>
+    <mergeCell ref="G47:AF47"/>
+    <mergeCell ref="A31:A38"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="G36:AF36"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I34:N34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:N35"/>
+    <mergeCell ref="O35:S35"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="S31:Y31"/>
+    <mergeCell ref="B32:F33"/>
+    <mergeCell ref="G32:N33"/>
+    <mergeCell ref="O32:AF32"/>
+    <mergeCell ref="T33:V33"/>
+    <mergeCell ref="W33:AF33"/>
+    <mergeCell ref="B42:F43"/>
+    <mergeCell ref="G42:P43"/>
     <mergeCell ref="AD1:AF2"/>
     <mergeCell ref="C3:X4"/>
     <mergeCell ref="A13:F13"/>
@@ -5710,41 +5686,56 @@
     <mergeCell ref="G18:P18"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D8:F8"/>
-    <mergeCell ref="A40:A47"/>
-    <mergeCell ref="B40:F41"/>
-    <mergeCell ref="G47:AF47"/>
-    <mergeCell ref="A31:A38"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="G36:AF36"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="I34:N34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="I35:N35"/>
-    <mergeCell ref="O35:S35"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="S31:Y31"/>
-    <mergeCell ref="B32:F33"/>
-    <mergeCell ref="G32:N33"/>
-    <mergeCell ref="O32:AF32"/>
-    <mergeCell ref="T33:V33"/>
-    <mergeCell ref="W33:AF33"/>
-    <mergeCell ref="B42:F43"/>
-    <mergeCell ref="G42:P43"/>
-    <mergeCell ref="G49:AF53"/>
-    <mergeCell ref="G54:AF55"/>
-    <mergeCell ref="G56:AF56"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="A51:A56"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:E52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:E54"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:E56"/>
+    <mergeCell ref="A8:C12"/>
+    <mergeCell ref="X7:AF8"/>
+    <mergeCell ref="T7:W8"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="G14:P14"/>
+    <mergeCell ref="Q14:V14"/>
+    <mergeCell ref="W14:AF14"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="X12:AF12"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:M11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:R12"/>
+    <mergeCell ref="H19:L19"/>
+    <mergeCell ref="O19:AF19"/>
+    <mergeCell ref="G20:T21"/>
+    <mergeCell ref="U21:X21"/>
+    <mergeCell ref="Y21:AF21"/>
+    <mergeCell ref="G16:P16"/>
+    <mergeCell ref="T9:W10"/>
+    <mergeCell ref="X9:AF10"/>
+    <mergeCell ref="G8:S8"/>
+    <mergeCell ref="G9:S10"/>
+    <mergeCell ref="U18:AF18"/>
+    <mergeCell ref="B28:F29"/>
+    <mergeCell ref="G28:AF28"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="J23:Q23"/>
+    <mergeCell ref="T23:AF23"/>
+    <mergeCell ref="G24:AF25"/>
+    <mergeCell ref="M26:U26"/>
+    <mergeCell ref="AA26:AF26"/>
+    <mergeCell ref="O27:U27"/>
+    <mergeCell ref="Y27:AF27"/>
+    <mergeCell ref="B22:F23"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:AF22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="Q42:AF42"/>
+    <mergeCell ref="U43:AF43"/>
+    <mergeCell ref="B46:F47"/>
+    <mergeCell ref="G46:AF46"/>
+    <mergeCell ref="T35:AF35"/>
+    <mergeCell ref="B37:F38"/>
+    <mergeCell ref="G37:AF37"/>
+    <mergeCell ref="G40:P41"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="S41:W41"/>
+    <mergeCell ref="G38:AF38"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
